--- a/examples/auditoria-ejemplo.xlsx
+++ b/examples/auditoria-ejemplo.xlsx
@@ -427,19 +427,19 @@
         <v>2026-01-15</v>
       </c>
       <c r="B2" t="str">
-        <v>Cirugía</v>
+        <v>UCI</v>
       </c>
       <c r="C2" t="str">
-        <v>Diurno</v>
+        <v>Nocturno</v>
       </c>
       <c r="D2" t="str">
-        <v>Cambio de posición</v>
+        <v>Registro de escala</v>
       </c>
       <c r="E2" t="str">
-        <v>1</v>
-      </c>
-      <c r="F2">
-        <v>20</v>
+        <v>Sí</v>
+      </c>
+      <c r="F2" t="str">
+        <v>Bajo</v>
       </c>
       <c r="G2" t="str">
         <v>PAC-1000</v>
@@ -453,16 +453,16 @@
         <v>UCI</v>
       </c>
       <c r="C3" t="str">
-        <v>Diurno</v>
+        <v>Nocturno</v>
       </c>
       <c r="D3" t="str">
-        <v>Cambio de posición</v>
+        <v>Valoración de riesgo</v>
       </c>
       <c r="E3" t="str">
-        <v>Cumple</v>
+        <v>0</v>
       </c>
       <c r="F3">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="G3" t="str">
         <v>PAC-1001</v>
@@ -476,16 +476,16 @@
         <v>UCI</v>
       </c>
       <c r="C4" t="str">
-        <v>Diurno</v>
+        <v>Nocturno</v>
       </c>
       <c r="D4" t="str">
-        <v>Uso de superficie</v>
+        <v>Registro de escala</v>
       </c>
       <c r="E4" t="str">
-        <v>Sí</v>
+        <v>1</v>
       </c>
       <c r="F4">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="G4" t="str">
         <v>PAC-1002</v>
@@ -499,16 +499,16 @@
         <v>Cirugía</v>
       </c>
       <c r="C5" t="str">
-        <v>Nocturno</v>
+        <v>Diurno</v>
       </c>
       <c r="D5" t="str">
-        <v>Registro de escala</v>
+        <v>Uso de superficie</v>
       </c>
       <c r="E5" t="str">
-        <v>1</v>
+        <v>Cumple</v>
       </c>
       <c r="F5">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="G5" t="str">
         <v>PAC-1003</v>
@@ -528,10 +528,10 @@
         <v>Cambio de posición</v>
       </c>
       <c r="E6" t="str">
-        <v>1</v>
+        <v>Sí</v>
       </c>
       <c r="F6" t="str">
-        <v>Bajo</v>
+        <v>Medio</v>
       </c>
       <c r="G6" t="str">
         <v>PAC-1004</v>
@@ -542,13 +542,13 @@
         <v>2026-02-15</v>
       </c>
       <c r="B7" t="str">
-        <v>Medicina</v>
+        <v>Urgencia</v>
       </c>
       <c r="C7" t="str">
         <v>Diurno</v>
       </c>
       <c r="D7" t="str">
-        <v>Cambio de posición</v>
+        <v>Valoración de riesgo</v>
       </c>
       <c r="E7" t="str">
         <v>SI</v>
@@ -565,19 +565,19 @@
         <v>2026-03-15</v>
       </c>
       <c r="B8" t="str">
-        <v>Medicina</v>
+        <v>Urgencia</v>
       </c>
       <c r="C8" t="str">
         <v>Diurno</v>
       </c>
       <c r="D8" t="str">
-        <v>Registro de escala</v>
+        <v>Cambio de posición</v>
       </c>
       <c r="E8" t="str">
-        <v>1</v>
-      </c>
-      <c r="F8" t="str">
-        <v>Medio</v>
+        <v>Sí</v>
+      </c>
+      <c r="F8">
+        <v>20</v>
       </c>
       <c r="G8" t="str">
         <v>PAC-1006</v>
@@ -591,16 +591,16 @@
         <v>Medicina</v>
       </c>
       <c r="C9" t="str">
-        <v>Nocturno</v>
+        <v>Diurno</v>
       </c>
       <c r="D9" t="str">
-        <v>Registro de escala</v>
+        <v>Cambio de posición</v>
       </c>
       <c r="E9" t="str">
-        <v>Cumple</v>
-      </c>
-      <c r="F9">
-        <v>11</v>
+        <v>SI</v>
+      </c>
+      <c r="F9" t="str">
+        <v>Medio</v>
       </c>
       <c r="G9" t="str">
         <v>PAC-1007</v>
@@ -614,16 +614,16 @@
         <v>Cirugía</v>
       </c>
       <c r="C10" t="str">
-        <v>Nocturno</v>
+        <v>Diurno</v>
       </c>
       <c r="D10" t="str">
-        <v>Uso de superficie</v>
+        <v>Registro de escala</v>
       </c>
       <c r="E10" t="str">
-        <v>Cumple</v>
-      </c>
-      <c r="F10" t="str">
-        <v>Bajo</v>
+        <v>1</v>
+      </c>
+      <c r="F10">
+        <v>20</v>
       </c>
       <c r="G10" t="str">
         <v>PAC-1008</v>
@@ -640,13 +640,13 @@
         <v>Diurno</v>
       </c>
       <c r="D11" t="str">
-        <v>Registro de escala</v>
+        <v>Uso de superficie</v>
       </c>
       <c r="E11" t="str">
-        <v>Cumple</v>
+        <v>No cumple</v>
       </c>
       <c r="F11" t="str">
-        <v>Bajo</v>
+        <v>Alto</v>
       </c>
       <c r="G11" t="str">
         <v>PAC-1009</v>
@@ -660,16 +660,16 @@
         <v>Cirugía</v>
       </c>
       <c r="C12" t="str">
-        <v>Diurno</v>
+        <v>Nocturno</v>
       </c>
       <c r="D12" t="str">
-        <v>Registro de escala</v>
+        <v>Valoración de riesgo</v>
       </c>
       <c r="E12" t="str">
-        <v>SI</v>
+        <v>Cumple</v>
       </c>
       <c r="F12" t="str">
-        <v>Bajo</v>
+        <v>Medio</v>
       </c>
       <c r="G12" t="str">
         <v>PAC-1010</v>
@@ -680,19 +680,19 @@
         <v>2026-04-15</v>
       </c>
       <c r="B13" t="str">
-        <v>UCI</v>
+        <v>Cirugía</v>
       </c>
       <c r="C13" t="str">
-        <v>Nocturno</v>
+        <v>Diurno</v>
       </c>
       <c r="D13" t="str">
         <v>Uso de superficie</v>
       </c>
       <c r="E13" t="str">
-        <v>No aplica</v>
-      </c>
-      <c r="F13">
-        <v>11</v>
+        <v>Cumple</v>
+      </c>
+      <c r="F13" t="str">
+        <v>Bajo</v>
       </c>
       <c r="G13" t="str">
         <v>PAC-1011</v>
@@ -706,16 +706,16 @@
         <v>Medicina</v>
       </c>
       <c r="C14" t="str">
-        <v>Nocturno</v>
+        <v>Diurno</v>
       </c>
       <c r="D14" t="str">
-        <v>Cambio de posición</v>
+        <v>Uso de superficie</v>
       </c>
       <c r="E14" t="str">
-        <v>SI</v>
+        <v>No</v>
       </c>
       <c r="F14" t="str">
-        <v>Bajo</v>
+        <v>Medio</v>
       </c>
       <c r="G14" t="str">
         <v>PAC-1012</v>
@@ -726,13 +726,13 @@
         <v>2026-02-15</v>
       </c>
       <c r="B15" t="str">
-        <v>Medicina</v>
+        <v>UCI</v>
       </c>
       <c r="C15" t="str">
         <v>Diurno</v>
       </c>
       <c r="D15" t="str">
-        <v>Registro de escala</v>
+        <v>Cambio de posición</v>
       </c>
       <c r="E15" t="str">
         <v>Cumple</v>
@@ -755,13 +755,13 @@
         <v>Nocturno</v>
       </c>
       <c r="D16" t="str">
-        <v>Valoración de riesgo</v>
+        <v>Uso de superficie</v>
       </c>
       <c r="E16" t="str">
-        <v>No aplica</v>
-      </c>
-      <c r="F16" t="str">
-        <v>Bajo</v>
+        <v>Sí</v>
+      </c>
+      <c r="F16">
+        <v>20</v>
       </c>
       <c r="G16" t="str">
         <v>PAC-1014</v>
@@ -772,19 +772,19 @@
         <v>2026-04-15</v>
       </c>
       <c r="B17" t="str">
-        <v>UCI</v>
+        <v>Cirugía</v>
       </c>
       <c r="C17" t="str">
-        <v>Diurno</v>
+        <v>Nocturno</v>
       </c>
       <c r="D17" t="str">
         <v>Cambio de posición</v>
       </c>
       <c r="E17" t="str">
-        <v>Cumple</v>
+        <v>Sí</v>
       </c>
       <c r="F17">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="G17" t="str">
         <v>PAC-1015</v>
@@ -795,13 +795,13 @@
         <v>2026-01-15</v>
       </c>
       <c r="B18" t="str">
-        <v>Medicina</v>
+        <v>UCI</v>
       </c>
       <c r="C18" t="str">
-        <v>Diurno</v>
+        <v>Nocturno</v>
       </c>
       <c r="D18" t="str">
-        <v>Valoración de riesgo</v>
+        <v>Registro de escala</v>
       </c>
       <c r="E18" t="str">
         <v>Cumple</v>
@@ -818,19 +818,19 @@
         <v>2026-02-15</v>
       </c>
       <c r="B19" t="str">
-        <v>Medicina</v>
+        <v>Cirugía</v>
       </c>
       <c r="C19" t="str">
         <v>Diurno</v>
       </c>
       <c r="D19" t="str">
-        <v>Cambio de posición</v>
+        <v>Registro de escala</v>
       </c>
       <c r="E19" t="str">
-        <v>No cumple</v>
+        <v>Cumple</v>
       </c>
       <c r="F19" t="str">
-        <v>Alto</v>
+        <v>Bajo</v>
       </c>
       <c r="G19" t="str">
         <v>PAC-1017</v>
@@ -841,19 +841,19 @@
         <v>2026-03-15</v>
       </c>
       <c r="B20" t="str">
-        <v>Cirugía</v>
+        <v>UCI</v>
       </c>
       <c r="C20" t="str">
         <v>Nocturno</v>
       </c>
       <c r="D20" t="str">
-        <v>Cambio de posición</v>
+        <v>Uso de superficie</v>
       </c>
       <c r="E20" t="str">
-        <v>No</v>
-      </c>
-      <c r="F20" t="str">
-        <v>Medio</v>
+        <v>SI</v>
+      </c>
+      <c r="F20">
+        <v>11</v>
       </c>
       <c r="G20" t="str">
         <v>PAC-1018</v>
@@ -864,19 +864,19 @@
         <v>2026-04-15</v>
       </c>
       <c r="B21" t="str">
-        <v>Medicina</v>
+        <v>UCI</v>
       </c>
       <c r="C21" t="str">
-        <v>Nocturno</v>
+        <v>Diurno</v>
       </c>
       <c r="D21" t="str">
-        <v>Uso de superficie</v>
+        <v>Registro de escala</v>
       </c>
       <c r="E21" t="str">
-        <v>Cumple</v>
-      </c>
-      <c r="F21" t="str">
-        <v>Bajo</v>
+        <v>No cumple</v>
+      </c>
+      <c r="F21">
+        <v>20</v>
       </c>
       <c r="G21" t="str">
         <v>PAC-1019</v>
@@ -890,13 +890,13 @@
         <v>Cirugía</v>
       </c>
       <c r="C22" t="str">
-        <v>Diurno</v>
+        <v>Nocturno</v>
       </c>
       <c r="D22" t="str">
-        <v>Uso de superficie</v>
+        <v>Cambio de posición</v>
       </c>
       <c r="E22" t="str">
-        <v>Sí</v>
+        <v>0</v>
       </c>
       <c r="F22" t="str">
         <v>Bajo</v>
@@ -910,19 +910,19 @@
         <v>2026-02-15</v>
       </c>
       <c r="B23" t="str">
-        <v>UCI</v>
+        <v>Medicina</v>
       </c>
       <c r="C23" t="str">
-        <v>Diurno</v>
+        <v>Nocturno</v>
       </c>
       <c r="D23" t="str">
         <v>Cambio de posición</v>
       </c>
       <c r="E23" t="str">
-        <v>Cumple</v>
-      </c>
-      <c r="F23">
-        <v>11</v>
+        <v>SI</v>
+      </c>
+      <c r="F23" t="str">
+        <v>Medio</v>
       </c>
       <c r="G23" t="str">
         <v>PAC-1021</v>
@@ -933,19 +933,19 @@
         <v>2026-03-15</v>
       </c>
       <c r="B24" t="str">
-        <v>Urgencia</v>
+        <v>UCI</v>
       </c>
       <c r="C24" t="str">
         <v>Nocturno</v>
       </c>
       <c r="D24" t="str">
-        <v>Cambio de posición</v>
+        <v>Valoración de riesgo</v>
       </c>
       <c r="E24" t="str">
-        <v>Sí</v>
-      </c>
-      <c r="F24">
-        <v>11</v>
+        <v>SI</v>
+      </c>
+      <c r="F24" t="str">
+        <v>Alto</v>
       </c>
       <c r="G24" t="str">
         <v>PAC-1022</v>
@@ -956,19 +956,19 @@
         <v>2026-04-15</v>
       </c>
       <c r="B25" t="str">
-        <v>Cirugía</v>
+        <v>UCI</v>
       </c>
       <c r="C25" t="str">
         <v>Diurno</v>
       </c>
       <c r="D25" t="str">
-        <v>Cambio de posición</v>
+        <v>Valoración de riesgo</v>
       </c>
       <c r="E25" t="str">
-        <v>No aplica</v>
+        <v>Cumple</v>
       </c>
       <c r="F25" t="str">
-        <v>Medio</v>
+        <v>Bajo</v>
       </c>
       <c r="G25" t="str">
         <v>PAC-1023</v>
@@ -979,19 +979,19 @@
         <v>2026-01-15</v>
       </c>
       <c r="B26" t="str">
-        <v>Urgencia</v>
+        <v>Cirugía</v>
       </c>
       <c r="C26" t="str">
         <v>Nocturno</v>
       </c>
       <c r="D26" t="str">
-        <v>Valoración de riesgo</v>
+        <v>Registro de escala</v>
       </c>
       <c r="E26" t="str">
-        <v>No aplica</v>
+        <v>Cumple</v>
       </c>
       <c r="F26" t="str">
-        <v>Bajo</v>
+        <v>Medio</v>
       </c>
       <c r="G26" t="str">
         <v>PAC-1024</v>
@@ -1002,19 +1002,19 @@
         <v>2026-02-15</v>
       </c>
       <c r="B27" t="str">
-        <v>Urgencia</v>
+        <v>Cirugía</v>
       </c>
       <c r="C27" t="str">
         <v>Diurno</v>
       </c>
       <c r="D27" t="str">
-        <v>Registro de escala</v>
+        <v>Cambio de posición</v>
       </c>
       <c r="E27" t="str">
-        <v>Sí</v>
+        <v>No aplica</v>
       </c>
       <c r="F27">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="G27" t="str">
         <v>PAC-1025</v>
@@ -1025,7 +1025,7 @@
         <v>2026-03-15</v>
       </c>
       <c r="B28" t="str">
-        <v>UCI</v>
+        <v>Medicina</v>
       </c>
       <c r="C28" t="str">
         <v>Nocturno</v>
@@ -1034,10 +1034,10 @@
         <v>Uso de superficie</v>
       </c>
       <c r="E28" t="str">
-        <v>N/A</v>
+        <v>1</v>
       </c>
       <c r="F28" t="str">
-        <v>Medio</v>
+        <v>Alto</v>
       </c>
       <c r="G28" t="str">
         <v>PAC-1026</v>
@@ -1048,19 +1048,19 @@
         <v>2026-04-15</v>
       </c>
       <c r="B29" t="str">
-        <v>Urgencia</v>
+        <v>UCI</v>
       </c>
       <c r="C29" t="str">
-        <v>Nocturno</v>
+        <v>Diurno</v>
       </c>
       <c r="D29" t="str">
-        <v>Registro de escala</v>
+        <v>Valoración de riesgo</v>
       </c>
       <c r="E29" t="str">
-        <v>1</v>
+        <v>N/A</v>
       </c>
       <c r="F29" t="str">
-        <v>Bajo</v>
+        <v>Alto</v>
       </c>
       <c r="G29" t="str">
         <v>PAC-1027</v>
@@ -1071,19 +1071,19 @@
         <v>2026-01-15</v>
       </c>
       <c r="B30" t="str">
-        <v>Urgencia</v>
+        <v>Cirugía</v>
       </c>
       <c r="C30" t="str">
-        <v>Nocturno</v>
+        <v>Diurno</v>
       </c>
       <c r="D30" t="str">
-        <v>Cambio de posición</v>
+        <v>Valoración de riesgo</v>
       </c>
       <c r="E30" t="str">
-        <v>1</v>
-      </c>
-      <c r="F30">
-        <v>20</v>
+        <v>SI</v>
+      </c>
+      <c r="F30" t="str">
+        <v>Bajo</v>
       </c>
       <c r="G30" t="str">
         <v>PAC-1028</v>
@@ -1094,7 +1094,7 @@
         <v>2026-02-15</v>
       </c>
       <c r="B31" t="str">
-        <v>Cirugía</v>
+        <v>UCI</v>
       </c>
       <c r="C31" t="str">
         <v>Nocturno</v>
@@ -1103,7 +1103,7 @@
         <v>Cambio de posición</v>
       </c>
       <c r="E31" t="str">
-        <v>1</v>
+        <v>Sí</v>
       </c>
       <c r="F31">
         <v>20</v>
@@ -1120,16 +1120,16 @@
         <v>Cirugía</v>
       </c>
       <c r="C32" t="str">
-        <v>Diurno</v>
+        <v>Nocturno</v>
       </c>
       <c r="D32" t="str">
-        <v>Valoración de riesgo</v>
+        <v>Cambio de posición</v>
       </c>
       <c r="E32" t="str">
-        <v>SI</v>
-      </c>
-      <c r="F32">
-        <v>11</v>
+        <v>NO</v>
+      </c>
+      <c r="F32" t="str">
+        <v>Medio</v>
       </c>
       <c r="G32" t="str">
         <v>PAC-1030</v>
@@ -1140,19 +1140,19 @@
         <v>2026-04-15</v>
       </c>
       <c r="B33" t="str">
-        <v>Medicina</v>
+        <v>Urgencia</v>
       </c>
       <c r="C33" t="str">
-        <v>Diurno</v>
+        <v>Nocturno</v>
       </c>
       <c r="D33" t="str">
-        <v>Valoración de riesgo</v>
+        <v>Uso de superficie</v>
       </c>
       <c r="E33" t="str">
-        <v>Cumple</v>
-      </c>
-      <c r="F33" t="str">
-        <v>Medio</v>
+        <v>SI</v>
+      </c>
+      <c r="F33">
+        <v>20</v>
       </c>
       <c r="G33" t="str">
         <v>PAC-1031</v>
@@ -1163,16 +1163,16 @@
         <v>2026-01-15</v>
       </c>
       <c r="B34" t="str">
-        <v>Medicina</v>
+        <v>Cirugía</v>
       </c>
       <c r="C34" t="str">
-        <v>Nocturno</v>
+        <v>Diurno</v>
       </c>
       <c r="D34" t="str">
-        <v>Cambio de posición</v>
+        <v>Uso de superficie</v>
       </c>
       <c r="E34" t="str">
-        <v>SI</v>
+        <v>Cumple</v>
       </c>
       <c r="F34">
         <v>11</v>
@@ -1186,19 +1186,19 @@
         <v>2026-02-15</v>
       </c>
       <c r="B35" t="str">
-        <v>Cirugía</v>
+        <v>Medicina</v>
       </c>
       <c r="C35" t="str">
-        <v>Nocturno</v>
+        <v>Diurno</v>
       </c>
       <c r="D35" t="str">
-        <v>Uso de superficie</v>
+        <v>Valoración de riesgo</v>
       </c>
       <c r="E35" t="str">
-        <v>SI</v>
-      </c>
-      <c r="F35">
-        <v>11</v>
+        <v>1</v>
+      </c>
+      <c r="F35" t="str">
+        <v>Alto</v>
       </c>
       <c r="G35" t="str">
         <v>PAC-1033</v>
@@ -1209,19 +1209,19 @@
         <v>2026-03-15</v>
       </c>
       <c r="B36" t="str">
-        <v>UCI</v>
+        <v>Urgencia</v>
       </c>
       <c r="C36" t="str">
-        <v>Nocturno</v>
+        <v>Diurno</v>
       </c>
       <c r="D36" t="str">
-        <v>Registro de escala</v>
+        <v>Valoración de riesgo</v>
       </c>
       <c r="E36" t="str">
-        <v>No</v>
-      </c>
-      <c r="F36" t="str">
-        <v>Medio</v>
+        <v>Cumple</v>
+      </c>
+      <c r="F36">
+        <v>11</v>
       </c>
       <c r="G36" t="str">
         <v>PAC-1034</v>
@@ -1232,19 +1232,19 @@
         <v>2026-04-15</v>
       </c>
       <c r="B37" t="str">
-        <v>UCI</v>
+        <v>Medicina</v>
       </c>
       <c r="C37" t="str">
-        <v>Nocturno</v>
+        <v>Diurno</v>
       </c>
       <c r="D37" t="str">
         <v>Cambio de posición</v>
       </c>
       <c r="E37" t="str">
-        <v>1</v>
-      </c>
-      <c r="F37">
-        <v>11</v>
+        <v>SI</v>
+      </c>
+      <c r="F37" t="str">
+        <v>Alto</v>
       </c>
       <c r="G37" t="str">
         <v>PAC-1035</v>
@@ -1255,19 +1255,19 @@
         <v>2026-01-15</v>
       </c>
       <c r="B38" t="str">
-        <v>Urgencia</v>
+        <v>UCI</v>
       </c>
       <c r="C38" t="str">
         <v>Diurno</v>
       </c>
       <c r="D38" t="str">
-        <v>Cambio de posición</v>
+        <v>Valoración de riesgo</v>
       </c>
       <c r="E38" t="str">
-        <v>NO</v>
+        <v>Sí</v>
       </c>
       <c r="F38">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="G38" t="str">
         <v>PAC-1036</v>
@@ -1278,19 +1278,19 @@
         <v>2026-02-15</v>
       </c>
       <c r="B39" t="str">
-        <v>Medicina</v>
+        <v>Cirugía</v>
       </c>
       <c r="C39" t="str">
         <v>Diurno</v>
       </c>
       <c r="D39" t="str">
-        <v>Valoración de riesgo</v>
+        <v>Cambio de posición</v>
       </c>
       <c r="E39" t="str">
-        <v>No aplica</v>
-      </c>
-      <c r="F39" t="str">
-        <v>Alto</v>
+        <v>SI</v>
+      </c>
+      <c r="F39">
+        <v>20</v>
       </c>
       <c r="G39" t="str">
         <v>PAC-1037</v>
@@ -1307,13 +1307,13 @@
         <v>Diurno</v>
       </c>
       <c r="D40" t="str">
-        <v>Valoración de riesgo</v>
+        <v>Uso de superficie</v>
       </c>
       <c r="E40" t="str">
         <v>No cumple</v>
       </c>
-      <c r="F40">
-        <v>11</v>
+      <c r="F40" t="str">
+        <v>Medio</v>
       </c>
       <c r="G40" t="str">
         <v>PAC-1038</v>
@@ -1324,19 +1324,19 @@
         <v>2026-04-15</v>
       </c>
       <c r="B41" t="str">
-        <v>UCI</v>
+        <v>Medicina</v>
       </c>
       <c r="C41" t="str">
         <v>Diurno</v>
       </c>
       <c r="D41" t="str">
-        <v>Cambio de posición</v>
+        <v>Uso de superficie</v>
       </c>
       <c r="E41" t="str">
         <v>Cumple</v>
       </c>
-      <c r="F41">
-        <v>11</v>
+      <c r="F41" t="str">
+        <v>Bajo</v>
       </c>
       <c r="G41" t="str">
         <v>PAC-1039</v>
@@ -1347,19 +1347,19 @@
         <v>2026-01-15</v>
       </c>
       <c r="B42" t="str">
-        <v>UCI</v>
+        <v>Cirugía</v>
       </c>
       <c r="C42" t="str">
         <v>Nocturno</v>
       </c>
       <c r="D42" t="str">
-        <v>Cambio de posición</v>
+        <v>Registro de escala</v>
       </c>
       <c r="E42" t="str">
-        <v>No cumple</v>
-      </c>
-      <c r="F42" t="str">
-        <v>Alto</v>
+        <v>0</v>
+      </c>
+      <c r="F42">
+        <v>11</v>
       </c>
       <c r="G42" t="str">
         <v>PAC-1040</v>
@@ -1376,13 +1376,13 @@
         <v>Diurno</v>
       </c>
       <c r="D43" t="str">
-        <v>Valoración de riesgo</v>
+        <v>Registro de escala</v>
       </c>
       <c r="E43" t="str">
-        <v>No cumple</v>
-      </c>
-      <c r="F43">
-        <v>11</v>
+        <v>NO</v>
+      </c>
+      <c r="F43" t="str">
+        <v>Bajo</v>
       </c>
       <c r="G43" t="str">
         <v>PAC-1041</v>
@@ -1393,7 +1393,7 @@
         <v>2026-03-15</v>
       </c>
       <c r="B44" t="str">
-        <v>Medicina</v>
+        <v>Urgencia</v>
       </c>
       <c r="C44" t="str">
         <v>Nocturno</v>
@@ -1402,10 +1402,10 @@
         <v>Registro de escala</v>
       </c>
       <c r="E44" t="str">
-        <v>1</v>
-      </c>
-      <c r="F44">
-        <v>11</v>
+        <v>SI</v>
+      </c>
+      <c r="F44" t="str">
+        <v>Alto</v>
       </c>
       <c r="G44" t="str">
         <v>PAC-1042</v>
@@ -1416,19 +1416,19 @@
         <v>2026-04-15</v>
       </c>
       <c r="B45" t="str">
-        <v>Cirugía</v>
+        <v>Medicina</v>
       </c>
       <c r="C45" t="str">
         <v>Diurno</v>
       </c>
       <c r="D45" t="str">
-        <v>Valoración de riesgo</v>
+        <v>Cambio de posición</v>
       </c>
       <c r="E45" t="str">
-        <v>Cumple</v>
+        <v>1</v>
       </c>
       <c r="F45" t="str">
-        <v>Alto</v>
+        <v>Bajo</v>
       </c>
       <c r="G45" t="str">
         <v>PAC-1043</v>
@@ -1439,19 +1439,19 @@
         <v>2026-01-15</v>
       </c>
       <c r="B46" t="str">
-        <v>Cirugía</v>
+        <v>Medicina</v>
       </c>
       <c r="C46" t="str">
         <v>Nocturno</v>
       </c>
       <c r="D46" t="str">
-        <v>Uso de superficie</v>
+        <v>Valoración de riesgo</v>
       </c>
       <c r="E46" t="str">
-        <v>Cumple</v>
+        <v>No</v>
       </c>
       <c r="F46">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="G46" t="str">
         <v>PAC-1044</v>
@@ -1468,10 +1468,10 @@
         <v>Nocturno</v>
       </c>
       <c r="D47" t="str">
-        <v>Registro de escala</v>
+        <v>Uso de superficie</v>
       </c>
       <c r="E47" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F47">
         <v>11</v>
@@ -1488,16 +1488,16 @@
         <v>Cirugía</v>
       </c>
       <c r="C48" t="str">
-        <v>Nocturno</v>
+        <v>Diurno</v>
       </c>
       <c r="D48" t="str">
         <v>Registro de escala</v>
       </c>
       <c r="E48" t="str">
-        <v>NO</v>
-      </c>
-      <c r="F48" t="str">
-        <v>Bajo</v>
+        <v>Cumple</v>
+      </c>
+      <c r="F48">
+        <v>11</v>
       </c>
       <c r="G48" t="str">
         <v>PAC-1046</v>
@@ -1508,19 +1508,19 @@
         <v>2026-04-15</v>
       </c>
       <c r="B49" t="str">
-        <v>UCI</v>
+        <v>Urgencia</v>
       </c>
       <c r="C49" t="str">
         <v>Diurno</v>
       </c>
       <c r="D49" t="str">
-        <v>Registro de escala</v>
+        <v>Valoración de riesgo</v>
       </c>
       <c r="E49" t="str">
-        <v>SI</v>
-      </c>
-      <c r="F49">
-        <v>20</v>
+        <v>Cumple</v>
+      </c>
+      <c r="F49" t="str">
+        <v>Bajo</v>
       </c>
       <c r="G49" t="str">
         <v>PAC-1047</v>
@@ -1537,7 +1537,7 @@
         <v>Nocturno</v>
       </c>
       <c r="D50" t="str">
-        <v>Valoración de riesgo</v>
+        <v>Registro de escala</v>
       </c>
       <c r="E50" t="str">
         <v>1</v>
@@ -1554,19 +1554,19 @@
         <v>2026-02-15</v>
       </c>
       <c r="B51" t="str">
-        <v>Cirugía</v>
+        <v>UCI</v>
       </c>
       <c r="C51" t="str">
-        <v>Nocturno</v>
+        <v>Diurno</v>
       </c>
       <c r="D51" t="str">
-        <v>Registro de escala</v>
+        <v>Uso de superficie</v>
       </c>
       <c r="E51" t="str">
-        <v>Sí</v>
-      </c>
-      <c r="F51">
-        <v>20</v>
+        <v>1</v>
+      </c>
+      <c r="F51" t="str">
+        <v>Bajo</v>
       </c>
       <c r="G51" t="str">
         <v>PAC-1049</v>
@@ -1580,16 +1580,16 @@
         <v>Medicina</v>
       </c>
       <c r="C52" t="str">
-        <v>Nocturno</v>
+        <v>Diurno</v>
       </c>
       <c r="D52" t="str">
-        <v>Registro de escala</v>
+        <v>Valoración de riesgo</v>
       </c>
       <c r="E52" t="str">
-        <v>N/A</v>
-      </c>
-      <c r="F52" t="str">
-        <v>Bajo</v>
+        <v>Cumple</v>
+      </c>
+      <c r="F52">
+        <v>11</v>
       </c>
       <c r="G52" t="str">
         <v>PAC-1050</v>
@@ -1600,19 +1600,19 @@
         <v>2026-04-15</v>
       </c>
       <c r="B53" t="str">
-        <v>Cirugía</v>
+        <v>Urgencia</v>
       </c>
       <c r="C53" t="str">
         <v>Nocturno</v>
       </c>
       <c r="D53" t="str">
-        <v>Cambio de posición</v>
+        <v>Uso de superficie</v>
       </c>
       <c r="E53" t="str">
-        <v>No cumple</v>
-      </c>
-      <c r="F53" t="str">
-        <v>Medio</v>
+        <v>Sí</v>
+      </c>
+      <c r="F53">
+        <v>20</v>
       </c>
       <c r="G53" t="str">
         <v>PAC-1051</v>
@@ -1623,16 +1623,16 @@
         <v>2026-01-15</v>
       </c>
       <c r="B54" t="str">
-        <v>Urgencia</v>
+        <v>UCI</v>
       </c>
       <c r="C54" t="str">
         <v>Diurno</v>
       </c>
       <c r="D54" t="str">
-        <v>Valoración de riesgo</v>
+        <v>Cambio de posición</v>
       </c>
       <c r="E54" t="str">
-        <v>1</v>
+        <v>Sí</v>
       </c>
       <c r="F54" t="str">
         <v>Medio</v>
@@ -1652,13 +1652,13 @@
         <v>Diurno</v>
       </c>
       <c r="D55" t="str">
-        <v>Registro de escala</v>
+        <v>Cambio de posición</v>
       </c>
       <c r="E55" t="str">
-        <v>NO</v>
-      </c>
-      <c r="F55">
-        <v>11</v>
+        <v>0</v>
+      </c>
+      <c r="F55" t="str">
+        <v>Bajo</v>
       </c>
       <c r="G55" t="str">
         <v>PAC-1053</v>
@@ -1672,16 +1672,16 @@
         <v>Medicina</v>
       </c>
       <c r="C56" t="str">
-        <v>Nocturno</v>
+        <v>Diurno</v>
       </c>
       <c r="D56" t="str">
-        <v>Uso de superficie</v>
+        <v>Valoración de riesgo</v>
       </c>
       <c r="E56" t="str">
         <v>SI</v>
       </c>
-      <c r="F56">
-        <v>11</v>
+      <c r="F56" t="str">
+        <v>Bajo</v>
       </c>
       <c r="G56" t="str">
         <v>PAC-1054</v>
@@ -1695,16 +1695,16 @@
         <v>UCI</v>
       </c>
       <c r="C57" t="str">
-        <v>Nocturno</v>
+        <v>Diurno</v>
       </c>
       <c r="D57" t="str">
-        <v>Valoración de riesgo</v>
+        <v>Registro de escala</v>
       </c>
       <c r="E57" t="str">
-        <v>SI</v>
+        <v>Sí</v>
       </c>
       <c r="F57">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="G57" t="str">
         <v>PAC-1055</v>
@@ -1715,16 +1715,16 @@
         <v>2026-01-15</v>
       </c>
       <c r="B58" t="str">
-        <v>UCI</v>
+        <v>Urgencia</v>
       </c>
       <c r="C58" t="str">
         <v>Diurno</v>
       </c>
       <c r="D58" t="str">
-        <v>Uso de superficie</v>
+        <v>Valoración de riesgo</v>
       </c>
       <c r="E58" t="str">
-        <v>No</v>
+        <v>Cumple</v>
       </c>
       <c r="F58">
         <v>20</v>
@@ -1738,19 +1738,19 @@
         <v>2026-02-15</v>
       </c>
       <c r="B59" t="str">
-        <v>UCI</v>
+        <v>Urgencia</v>
       </c>
       <c r="C59" t="str">
-        <v>Nocturno</v>
+        <v>Diurno</v>
       </c>
       <c r="D59" t="str">
-        <v>Cambio de posición</v>
+        <v>Valoración de riesgo</v>
       </c>
       <c r="E59" t="str">
         <v>SI</v>
       </c>
-      <c r="F59" t="str">
-        <v>Alto</v>
+      <c r="F59">
+        <v>11</v>
       </c>
       <c r="G59" t="str">
         <v>PAC-1057</v>
@@ -1761,19 +1761,19 @@
         <v>2026-03-15</v>
       </c>
       <c r="B60" t="str">
-        <v>Cirugía</v>
+        <v>Urgencia</v>
       </c>
       <c r="C60" t="str">
         <v>Diurno</v>
       </c>
       <c r="D60" t="str">
-        <v>Valoración de riesgo</v>
+        <v>Cambio de posición</v>
       </c>
       <c r="E60" t="str">
-        <v>Cumple</v>
+        <v>No</v>
       </c>
       <c r="F60" t="str">
-        <v>Alto</v>
+        <v>Medio</v>
       </c>
       <c r="G60" t="str">
         <v>PAC-1058</v>
@@ -1784,19 +1784,19 @@
         <v>2026-04-15</v>
       </c>
       <c r="B61" t="str">
-        <v>Medicina</v>
+        <v>UCI</v>
       </c>
       <c r="C61" t="str">
-        <v>Diurno</v>
+        <v>Nocturno</v>
       </c>
       <c r="D61" t="str">
         <v>Valoración de riesgo</v>
       </c>
       <c r="E61" t="str">
-        <v>No cumple</v>
-      </c>
-      <c r="F61">
-        <v>11</v>
+        <v>No aplica</v>
+      </c>
+      <c r="F61" t="str">
+        <v>Alto</v>
       </c>
       <c r="G61" t="str">
         <v>PAC-1059</v>
@@ -1807,19 +1807,19 @@
         <v>2026-01-15</v>
       </c>
       <c r="B62" t="str">
-        <v>Urgencia</v>
+        <v>Medicina</v>
       </c>
       <c r="C62" t="str">
-        <v>Nocturno</v>
+        <v>Diurno</v>
       </c>
       <c r="D62" t="str">
-        <v>Cambio de posición</v>
+        <v>Valoración de riesgo</v>
       </c>
       <c r="E62" t="str">
         <v>Cumple</v>
       </c>
-      <c r="F62">
-        <v>20</v>
+      <c r="F62" t="str">
+        <v>Medio</v>
       </c>
       <c r="G62" t="str">
         <v>PAC-1060</v>
@@ -1830,19 +1830,19 @@
         <v>2026-02-15</v>
       </c>
       <c r="B63" t="str">
-        <v>UCI</v>
+        <v>Cirugía</v>
       </c>
       <c r="C63" t="str">
-        <v>Nocturno</v>
+        <v>Diurno</v>
       </c>
       <c r="D63" t="str">
         <v>Cambio de posición</v>
       </c>
       <c r="E63" t="str">
-        <v>0</v>
+        <v>Cumple</v>
       </c>
       <c r="F63">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="G63" t="str">
         <v>PAC-1061</v>
@@ -1853,10 +1853,10 @@
         <v>2026-03-15</v>
       </c>
       <c r="B64" t="str">
-        <v>Urgencia</v>
+        <v>Cirugía</v>
       </c>
       <c r="C64" t="str">
-        <v>Diurno</v>
+        <v>Nocturno</v>
       </c>
       <c r="D64" t="str">
         <v>Valoración de riesgo</v>
@@ -1864,8 +1864,8 @@
       <c r="E64" t="str">
         <v>Sí</v>
       </c>
-      <c r="F64" t="str">
-        <v>Alto</v>
+      <c r="F64">
+        <v>11</v>
       </c>
       <c r="G64" t="str">
         <v>PAC-1062</v>
@@ -1876,19 +1876,19 @@
         <v>2026-04-15</v>
       </c>
       <c r="B65" t="str">
-        <v>Medicina</v>
+        <v>Cirugía</v>
       </c>
       <c r="C65" t="str">
-        <v>Diurno</v>
+        <v>Nocturno</v>
       </c>
       <c r="D65" t="str">
-        <v>Valoración de riesgo</v>
+        <v>Registro de escala</v>
       </c>
       <c r="E65" t="str">
         <v>Cumple</v>
       </c>
       <c r="F65" t="str">
-        <v>Medio</v>
+        <v>Bajo</v>
       </c>
       <c r="G65" t="str">
         <v>PAC-1063</v>
@@ -1899,7 +1899,7 @@
         <v>2026-01-15</v>
       </c>
       <c r="B66" t="str">
-        <v>Cirugía</v>
+        <v>Medicina</v>
       </c>
       <c r="C66" t="str">
         <v>Nocturno</v>
@@ -1908,10 +1908,10 @@
         <v>Valoración de riesgo</v>
       </c>
       <c r="E66" t="str">
-        <v>NO</v>
+        <v>Cumple</v>
       </c>
       <c r="F66" t="str">
-        <v>Bajo</v>
+        <v>Alto</v>
       </c>
       <c r="G66" t="str">
         <v>PAC-1064</v>
@@ -1922,16 +1922,16 @@
         <v>2026-02-15</v>
       </c>
       <c r="B67" t="str">
-        <v>Cirugía</v>
+        <v>Urgencia</v>
       </c>
       <c r="C67" t="str">
-        <v>Nocturno</v>
+        <v>Diurno</v>
       </c>
       <c r="D67" t="str">
-        <v>Valoración de riesgo</v>
+        <v>Registro de escala</v>
       </c>
       <c r="E67" t="str">
-        <v>No</v>
+        <v>1</v>
       </c>
       <c r="F67" t="str">
         <v>Alto</v>
@@ -1945,19 +1945,19 @@
         <v>2026-03-15</v>
       </c>
       <c r="B68" t="str">
-        <v>Cirugía</v>
+        <v>Medicina</v>
       </c>
       <c r="C68" t="str">
-        <v>Nocturno</v>
+        <v>Diurno</v>
       </c>
       <c r="D68" t="str">
-        <v>Registro de escala</v>
+        <v>Cambio de posición</v>
       </c>
       <c r="E68" t="str">
-        <v>Sí</v>
+        <v>No aplica</v>
       </c>
       <c r="F68" t="str">
-        <v>Bajo</v>
+        <v>Medio</v>
       </c>
       <c r="G68" t="str">
         <v>PAC-1066</v>
@@ -1974,13 +1974,13 @@
         <v>Diurno</v>
       </c>
       <c r="D69" t="str">
-        <v>Cambio de posición</v>
+        <v>Uso de superficie</v>
       </c>
       <c r="E69" t="str">
         <v>SI</v>
       </c>
-      <c r="F69">
-        <v>20</v>
+      <c r="F69" t="str">
+        <v>Medio</v>
       </c>
       <c r="G69" t="str">
         <v>PAC-1067</v>
@@ -1991,19 +1991,19 @@
         <v>2026-01-15</v>
       </c>
       <c r="B70" t="str">
-        <v>UCI</v>
+        <v>Cirugía</v>
       </c>
       <c r="C70" t="str">
         <v>Diurno</v>
       </c>
       <c r="D70" t="str">
-        <v>Registro de escala</v>
+        <v>Cambio de posición</v>
       </c>
       <c r="E70" t="str">
-        <v>N/A</v>
-      </c>
-      <c r="F70">
-        <v>20</v>
+        <v>Cumple</v>
+      </c>
+      <c r="F70" t="str">
+        <v>Alto</v>
       </c>
       <c r="G70" t="str">
         <v>PAC-1068</v>
@@ -2020,13 +2020,13 @@
         <v>Diurno</v>
       </c>
       <c r="D71" t="str">
-        <v>Valoración de riesgo</v>
+        <v>Cambio de posición</v>
       </c>
       <c r="E71" t="str">
-        <v>No cumple</v>
-      </c>
-      <c r="F71">
-        <v>20</v>
+        <v>1</v>
+      </c>
+      <c r="F71" t="str">
+        <v>Bajo</v>
       </c>
       <c r="G71" t="str">
         <v>PAC-1069</v>
@@ -2037,19 +2037,19 @@
         <v>2026-03-15</v>
       </c>
       <c r="B72" t="str">
-        <v>Urgencia</v>
+        <v>Medicina</v>
       </c>
       <c r="C72" t="str">
-        <v>Nocturno</v>
+        <v>Diurno</v>
       </c>
       <c r="D72" t="str">
-        <v>Valoración de riesgo</v>
+        <v>Uso de superficie</v>
       </c>
       <c r="E72" t="str">
-        <v>No cumple</v>
+        <v>No aplica</v>
       </c>
       <c r="F72" t="str">
-        <v>Bajo</v>
+        <v>Alto</v>
       </c>
       <c r="G72" t="str">
         <v>PAC-1070</v>
@@ -2060,19 +2060,19 @@
         <v>2026-04-15</v>
       </c>
       <c r="B73" t="str">
-        <v>Cirugía</v>
+        <v>UCI</v>
       </c>
       <c r="C73" t="str">
         <v>Nocturno</v>
       </c>
       <c r="D73" t="str">
-        <v>Valoración de riesgo</v>
+        <v>Cambio de posición</v>
       </c>
       <c r="E73" t="str">
-        <v>SI</v>
-      </c>
-      <c r="F73" t="str">
-        <v>Medio</v>
+        <v>No aplica</v>
+      </c>
+      <c r="F73">
+        <v>20</v>
       </c>
       <c r="G73" t="str">
         <v>PAC-1071</v>
@@ -2083,19 +2083,19 @@
         <v>2026-01-15</v>
       </c>
       <c r="B74" t="str">
-        <v>Medicina</v>
+        <v>Cirugía</v>
       </c>
       <c r="C74" t="str">
-        <v>Nocturno</v>
+        <v>Diurno</v>
       </c>
       <c r="D74" t="str">
-        <v>Valoración de riesgo</v>
+        <v>Cambio de posición</v>
       </c>
       <c r="E74" t="str">
-        <v>Cumple</v>
-      </c>
-      <c r="F74" t="str">
-        <v>Bajo</v>
+        <v>1</v>
+      </c>
+      <c r="F74">
+        <v>20</v>
       </c>
       <c r="G74" t="str">
         <v>PAC-1072</v>
@@ -2106,19 +2106,19 @@
         <v>2026-02-15</v>
       </c>
       <c r="B75" t="str">
-        <v>Medicina</v>
+        <v>Urgencia</v>
       </c>
       <c r="C75" t="str">
-        <v>Nocturno</v>
+        <v>Diurno</v>
       </c>
       <c r="D75" t="str">
-        <v>Uso de superficie</v>
+        <v>Registro de escala</v>
       </c>
       <c r="E75" t="str">
-        <v>No cumple</v>
+        <v>Cumple</v>
       </c>
       <c r="F75" t="str">
-        <v>Alto</v>
+        <v>Medio</v>
       </c>
       <c r="G75" t="str">
         <v>PAC-1073</v>
@@ -2129,19 +2129,19 @@
         <v>2026-03-15</v>
       </c>
       <c r="B76" t="str">
-        <v>Urgencia</v>
+        <v>Medicina</v>
       </c>
       <c r="C76" t="str">
-        <v>Diurno</v>
+        <v>Nocturno</v>
       </c>
       <c r="D76" t="str">
-        <v>Uso de superficie</v>
+        <v>Cambio de posición</v>
       </c>
       <c r="E76" t="str">
-        <v>Sí</v>
-      </c>
-      <c r="F76" t="str">
-        <v>Medio</v>
+        <v>N/A</v>
+      </c>
+      <c r="F76">
+        <v>20</v>
       </c>
       <c r="G76" t="str">
         <v>PAC-1074</v>
@@ -2155,16 +2155,16 @@
         <v>Urgencia</v>
       </c>
       <c r="C77" t="str">
-        <v>Diurno</v>
+        <v>Nocturno</v>
       </c>
       <c r="D77" t="str">
         <v>Valoración de riesgo</v>
       </c>
       <c r="E77" t="str">
-        <v>1</v>
-      </c>
-      <c r="F77" t="str">
-        <v>Alto</v>
+        <v>SI</v>
+      </c>
+      <c r="F77">
+        <v>20</v>
       </c>
       <c r="G77" t="str">
         <v>PAC-1075</v>
@@ -2178,16 +2178,16 @@
         <v>Medicina</v>
       </c>
       <c r="C78" t="str">
-        <v>Diurno</v>
+        <v>Nocturno</v>
       </c>
       <c r="D78" t="str">
-        <v>Cambio de posición</v>
+        <v>Registro de escala</v>
       </c>
       <c r="E78" t="str">
-        <v>Cumple</v>
-      </c>
-      <c r="F78" t="str">
-        <v>Alto</v>
+        <v>No aplica</v>
+      </c>
+      <c r="F78">
+        <v>11</v>
       </c>
       <c r="G78" t="str">
         <v>PAC-1076</v>
@@ -2201,16 +2201,16 @@
         <v>Medicina</v>
       </c>
       <c r="C79" t="str">
-        <v>Diurno</v>
+        <v>Nocturno</v>
       </c>
       <c r="D79" t="str">
-        <v>Registro de escala</v>
+        <v>Cambio de posición</v>
       </c>
       <c r="E79" t="str">
-        <v>NO</v>
-      </c>
-      <c r="F79">
-        <v>20</v>
+        <v>1</v>
+      </c>
+      <c r="F79" t="str">
+        <v>Bajo</v>
       </c>
       <c r="G79" t="str">
         <v>PAC-1077</v>
@@ -2221,19 +2221,19 @@
         <v>2026-03-15</v>
       </c>
       <c r="B80" t="str">
-        <v>UCI</v>
+        <v>Medicina</v>
       </c>
       <c r="C80" t="str">
-        <v>Nocturno</v>
+        <v>Diurno</v>
       </c>
       <c r="D80" t="str">
         <v>Uso de superficie</v>
       </c>
       <c r="E80" t="str">
-        <v>Sí</v>
-      </c>
-      <c r="F80" t="str">
-        <v>Alto</v>
+        <v>Cumple</v>
+      </c>
+      <c r="F80">
+        <v>11</v>
       </c>
       <c r="G80" t="str">
         <v>PAC-1078</v>
@@ -2250,10 +2250,10 @@
         <v>Nocturno</v>
       </c>
       <c r="D81" t="str">
-        <v>Uso de superficie</v>
+        <v>Valoración de riesgo</v>
       </c>
       <c r="E81" t="str">
-        <v>1</v>
+        <v>Sí</v>
       </c>
       <c r="F81" t="str">
         <v>Alto</v>
@@ -2267,19 +2267,19 @@
         <v>2026-01-15</v>
       </c>
       <c r="B82" t="str">
-        <v>Urgencia</v>
+        <v>UCI</v>
       </c>
       <c r="C82" t="str">
-        <v>Diurno</v>
+        <v>Nocturno</v>
       </c>
       <c r="D82" t="str">
-        <v>Uso de superficie</v>
+        <v>Registro de escala</v>
       </c>
       <c r="E82" t="str">
         <v>1</v>
       </c>
       <c r="F82" t="str">
-        <v>Medio</v>
+        <v>Bajo</v>
       </c>
       <c r="G82" t="str">
         <v>PAC-1080</v>
@@ -2290,16 +2290,16 @@
         <v>2026-02-15</v>
       </c>
       <c r="B83" t="str">
-        <v>Medicina</v>
+        <v>UCI</v>
       </c>
       <c r="C83" t="str">
         <v>Diurno</v>
       </c>
       <c r="D83" t="str">
-        <v>Valoración de riesgo</v>
+        <v>Uso de superficie</v>
       </c>
       <c r="E83" t="str">
-        <v>SI</v>
+        <v>Cumple</v>
       </c>
       <c r="F83">
         <v>20</v>
@@ -2313,19 +2313,19 @@
         <v>2026-03-15</v>
       </c>
       <c r="B84" t="str">
-        <v>UCI</v>
+        <v>Cirugía</v>
       </c>
       <c r="C84" t="str">
         <v>Diurno</v>
       </c>
       <c r="D84" t="str">
-        <v>Cambio de posición</v>
+        <v>Valoración de riesgo</v>
       </c>
       <c r="E84" t="str">
-        <v>SI</v>
-      </c>
-      <c r="F84" t="str">
-        <v>Alto</v>
+        <v>1</v>
+      </c>
+      <c r="F84">
+        <v>20</v>
       </c>
       <c r="G84" t="str">
         <v>PAC-1082</v>
@@ -2336,16 +2336,16 @@
         <v>2026-04-15</v>
       </c>
       <c r="B85" t="str">
-        <v>Medicina</v>
+        <v>Cirugía</v>
       </c>
       <c r="C85" t="str">
         <v>Diurno</v>
       </c>
       <c r="D85" t="str">
-        <v>Valoración de riesgo</v>
+        <v>Uso de superficie</v>
       </c>
       <c r="E85" t="str">
-        <v>Sí</v>
+        <v>SI</v>
       </c>
       <c r="F85" t="str">
         <v>Medio</v>
@@ -2362,16 +2362,16 @@
         <v>Cirugía</v>
       </c>
       <c r="C86" t="str">
-        <v>Nocturno</v>
+        <v>Diurno</v>
       </c>
       <c r="D86" t="str">
-        <v>Cambio de posición</v>
+        <v>Registro de escala</v>
       </c>
       <c r="E86" t="str">
-        <v>1</v>
+        <v>N/A</v>
       </c>
       <c r="F86" t="str">
-        <v>Medio</v>
+        <v>Bajo</v>
       </c>
       <c r="G86" t="str">
         <v>PAC-1084</v>
@@ -2385,16 +2385,16 @@
         <v>Medicina</v>
       </c>
       <c r="C87" t="str">
-        <v>Diurno</v>
+        <v>Nocturno</v>
       </c>
       <c r="D87" t="str">
-        <v>Valoración de riesgo</v>
+        <v>Registro de escala</v>
       </c>
       <c r="E87" t="str">
-        <v>Cumple</v>
-      </c>
-      <c r="F87" t="str">
-        <v>Alto</v>
+        <v>Sí</v>
+      </c>
+      <c r="F87">
+        <v>11</v>
       </c>
       <c r="G87" t="str">
         <v>PAC-1085</v>
@@ -2414,7 +2414,7 @@
         <v>Registro de escala</v>
       </c>
       <c r="E88" t="str">
-        <v>Sí</v>
+        <v>SI</v>
       </c>
       <c r="F88" t="str">
         <v>Medio</v>
@@ -2428,19 +2428,19 @@
         <v>2026-04-15</v>
       </c>
       <c r="B89" t="str">
-        <v>Cirugía</v>
+        <v>UCI</v>
       </c>
       <c r="C89" t="str">
-        <v>Nocturno</v>
+        <v>Diurno</v>
       </c>
       <c r="D89" t="str">
-        <v>Uso de superficie</v>
+        <v>Cambio de posición</v>
       </c>
       <c r="E89" t="str">
-        <v>Sí</v>
-      </c>
-      <c r="F89" t="str">
-        <v>Alto</v>
+        <v>1</v>
+      </c>
+      <c r="F89">
+        <v>11</v>
       </c>
       <c r="G89" t="str">
         <v>PAC-1087</v>
@@ -2451,19 +2451,19 @@
         <v>2026-01-15</v>
       </c>
       <c r="B90" t="str">
-        <v>Cirugía</v>
+        <v>UCI</v>
       </c>
       <c r="C90" t="str">
         <v>Diurno</v>
       </c>
       <c r="D90" t="str">
-        <v>Cambio de posición</v>
+        <v>Valoración de riesgo</v>
       </c>
       <c r="E90" t="str">
         <v>SI</v>
       </c>
-      <c r="F90">
-        <v>20</v>
+      <c r="F90" t="str">
+        <v>Bajo</v>
       </c>
       <c r="G90" t="str">
         <v>PAC-1088</v>
@@ -2474,19 +2474,19 @@
         <v>2026-02-15</v>
       </c>
       <c r="B91" t="str">
-        <v>Cirugía</v>
+        <v>Medicina</v>
       </c>
       <c r="C91" t="str">
-        <v>Nocturno</v>
+        <v>Diurno</v>
       </c>
       <c r="D91" t="str">
-        <v>Cambio de posición</v>
+        <v>Valoración de riesgo</v>
       </c>
       <c r="E91" t="str">
-        <v>Cumple</v>
-      </c>
-      <c r="F91">
-        <v>20</v>
+        <v>SI</v>
+      </c>
+      <c r="F91" t="str">
+        <v>Medio</v>
       </c>
       <c r="G91" t="str">
         <v>PAC-1089</v>
@@ -2500,16 +2500,16 @@
         <v>Urgencia</v>
       </c>
       <c r="C92" t="str">
-        <v>Nocturno</v>
+        <v>Diurno</v>
       </c>
       <c r="D92" t="str">
-        <v>Valoración de riesgo</v>
+        <v>Uso de superficie</v>
       </c>
       <c r="E92" t="str">
-        <v>No cumple</v>
-      </c>
-      <c r="F92">
-        <v>20</v>
+        <v>Cumple</v>
+      </c>
+      <c r="F92" t="str">
+        <v>Medio</v>
       </c>
       <c r="G92" t="str">
         <v>PAC-1090</v>
@@ -2520,19 +2520,19 @@
         <v>2026-04-15</v>
       </c>
       <c r="B93" t="str">
-        <v>Cirugía</v>
+        <v>UCI</v>
       </c>
       <c r="C93" t="str">
         <v>Nocturno</v>
       </c>
       <c r="D93" t="str">
-        <v>Valoración de riesgo</v>
+        <v>Uso de superficie</v>
       </c>
       <c r="E93" t="str">
-        <v>Sí</v>
+        <v>SI</v>
       </c>
       <c r="F93">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="G93" t="str">
         <v>PAC-1091</v>
@@ -2543,16 +2543,16 @@
         <v>2026-01-15</v>
       </c>
       <c r="B94" t="str">
-        <v>Urgencia</v>
+        <v>Cirugía</v>
       </c>
       <c r="C94" t="str">
-        <v>Nocturno</v>
+        <v>Diurno</v>
       </c>
       <c r="D94" t="str">
-        <v>Uso de superficie</v>
+        <v>Valoración de riesgo</v>
       </c>
       <c r="E94" t="str">
-        <v>N/A</v>
+        <v>SI</v>
       </c>
       <c r="F94" t="str">
         <v>Medio</v>
@@ -2566,7 +2566,7 @@
         <v>2026-02-15</v>
       </c>
       <c r="B95" t="str">
-        <v>Cirugía</v>
+        <v>Medicina</v>
       </c>
       <c r="C95" t="str">
         <v>Nocturno</v>
@@ -2575,10 +2575,10 @@
         <v>Cambio de posición</v>
       </c>
       <c r="E95" t="str">
-        <v>Sí</v>
-      </c>
-      <c r="F95" t="str">
-        <v>Bajo</v>
+        <v>Cumple</v>
+      </c>
+      <c r="F95">
+        <v>11</v>
       </c>
       <c r="G95" t="str">
         <v>PAC-1093</v>
@@ -2595,10 +2595,10 @@
         <v>Nocturno</v>
       </c>
       <c r="D96" t="str">
-        <v>Cambio de posición</v>
+        <v>Valoración de riesgo</v>
       </c>
       <c r="E96" t="str">
-        <v>1</v>
+        <v>Sí</v>
       </c>
       <c r="F96" t="str">
         <v>Medio</v>
@@ -2612,19 +2612,19 @@
         <v>2026-04-15</v>
       </c>
       <c r="B97" t="str">
-        <v>UCI</v>
+        <v>Medicina</v>
       </c>
       <c r="C97" t="str">
-        <v>Diurno</v>
+        <v>Nocturno</v>
       </c>
       <c r="D97" t="str">
         <v>Cambio de posición</v>
       </c>
       <c r="E97" t="str">
-        <v>Sí</v>
+        <v>SI</v>
       </c>
       <c r="F97">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="G97" t="str">
         <v>PAC-1095</v>
@@ -2641,10 +2641,10 @@
         <v>Nocturno</v>
       </c>
       <c r="D98" t="str">
-        <v>Registro de escala</v>
+        <v>Valoración de riesgo</v>
       </c>
       <c r="E98" t="str">
-        <v>Cumple</v>
+        <v>NO</v>
       </c>
       <c r="F98" t="str">
         <v>Bajo</v>
@@ -2658,19 +2658,19 @@
         <v>2026-02-15</v>
       </c>
       <c r="B99" t="str">
-        <v>UCI</v>
+        <v>Urgencia</v>
       </c>
       <c r="C99" t="str">
-        <v>Nocturno</v>
+        <v>Diurno</v>
       </c>
       <c r="D99" t="str">
-        <v>Valoración de riesgo</v>
+        <v>Registro de escala</v>
       </c>
       <c r="E99" t="str">
-        <v>Cumple</v>
-      </c>
-      <c r="F99">
-        <v>20</v>
+        <v>Sí</v>
+      </c>
+      <c r="F99" t="str">
+        <v>Medio</v>
       </c>
       <c r="G99" t="str">
         <v>PAC-1097</v>
@@ -2681,16 +2681,16 @@
         <v>2026-03-15</v>
       </c>
       <c r="B100" t="str">
-        <v>UCI</v>
+        <v>Urgencia</v>
       </c>
       <c r="C100" t="str">
-        <v>Diurno</v>
+        <v>Nocturno</v>
       </c>
       <c r="D100" t="str">
-        <v>Uso de superficie</v>
+        <v>Valoración de riesgo</v>
       </c>
       <c r="E100" t="str">
-        <v>No</v>
+        <v>1</v>
       </c>
       <c r="F100" t="str">
         <v>Bajo</v>
@@ -2707,16 +2707,16 @@
         <v>Medicina</v>
       </c>
       <c r="C101" t="str">
-        <v>Diurno</v>
+        <v>Nocturno</v>
       </c>
       <c r="D101" t="str">
-        <v>Valoración de riesgo</v>
+        <v>Uso de superficie</v>
       </c>
       <c r="E101" t="str">
-        <v>Cumple</v>
-      </c>
-      <c r="F101" t="str">
-        <v>Medio</v>
+        <v>1</v>
+      </c>
+      <c r="F101">
+        <v>11</v>
       </c>
       <c r="G101" t="str">
         <v>PAC-1099</v>
@@ -2727,7 +2727,7 @@
         <v>2026-01-15</v>
       </c>
       <c r="B102" t="str">
-        <v>UCI</v>
+        <v>Urgencia</v>
       </c>
       <c r="C102" t="str">
         <v>Diurno</v>
@@ -2736,10 +2736,10 @@
         <v>Registro de escala</v>
       </c>
       <c r="E102" t="str">
-        <v>1</v>
+        <v>N/A</v>
       </c>
       <c r="F102" t="str">
-        <v>Bajo</v>
+        <v>Medio</v>
       </c>
       <c r="G102" t="str">
         <v>PAC-1100</v>
@@ -2750,19 +2750,19 @@
         <v>2026-02-15</v>
       </c>
       <c r="B103" t="str">
-        <v>Medicina</v>
+        <v>UCI</v>
       </c>
       <c r="C103" t="str">
-        <v>Nocturno</v>
+        <v>Diurno</v>
       </c>
       <c r="D103" t="str">
-        <v>Cambio de posición</v>
+        <v>Uso de superficie</v>
       </c>
       <c r="E103" t="str">
-        <v>No cumple</v>
-      </c>
-      <c r="F103">
-        <v>20</v>
+        <v>Cumple</v>
+      </c>
+      <c r="F103" t="str">
+        <v>Alto</v>
       </c>
       <c r="G103" t="str">
         <v>PAC-1101</v>
@@ -2773,7 +2773,7 @@
         <v>2026-03-15</v>
       </c>
       <c r="B104" t="str">
-        <v>UCI</v>
+        <v>Cirugía</v>
       </c>
       <c r="C104" t="str">
         <v>Nocturno</v>
@@ -2782,10 +2782,10 @@
         <v>Registro de escala</v>
       </c>
       <c r="E104" t="str">
-        <v>Sí</v>
-      </c>
-      <c r="F104">
-        <v>20</v>
+        <v>SI</v>
+      </c>
+      <c r="F104" t="str">
+        <v>Alto</v>
       </c>
       <c r="G104" t="str">
         <v>PAC-1102</v>
@@ -2796,19 +2796,19 @@
         <v>2026-04-15</v>
       </c>
       <c r="B105" t="str">
-        <v>Urgencia</v>
+        <v>UCI</v>
       </c>
       <c r="C105" t="str">
-        <v>Nocturno</v>
+        <v>Diurno</v>
       </c>
       <c r="D105" t="str">
         <v>Registro de escala</v>
       </c>
       <c r="E105" t="str">
-        <v>No</v>
+        <v>1</v>
       </c>
       <c r="F105" t="str">
-        <v>Medio</v>
+        <v>Bajo</v>
       </c>
       <c r="G105" t="str">
         <v>PAC-1103</v>
@@ -2825,13 +2825,13 @@
         <v>Nocturno</v>
       </c>
       <c r="D106" t="str">
-        <v>Cambio de posición</v>
+        <v>Valoración de riesgo</v>
       </c>
       <c r="E106" t="str">
-        <v>No cumple</v>
+        <v>0</v>
       </c>
       <c r="F106">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="G106" t="str">
         <v>PAC-1104</v>
@@ -2848,10 +2848,10 @@
         <v>Nocturno</v>
       </c>
       <c r="D107" t="str">
-        <v>Valoración de riesgo</v>
+        <v>Registro de escala</v>
       </c>
       <c r="E107" t="str">
-        <v>SI</v>
+        <v>No aplica</v>
       </c>
       <c r="F107">
         <v>11</v>
@@ -2865,19 +2865,19 @@
         <v>2026-03-15</v>
       </c>
       <c r="B108" t="str">
-        <v>UCI</v>
+        <v>Cirugía</v>
       </c>
       <c r="C108" t="str">
         <v>Diurno</v>
       </c>
       <c r="D108" t="str">
-        <v>Cambio de posición</v>
+        <v>Registro de escala</v>
       </c>
       <c r="E108" t="str">
-        <v>0</v>
+        <v>No cumple</v>
       </c>
       <c r="F108" t="str">
-        <v>Medio</v>
+        <v>Bajo</v>
       </c>
       <c r="G108" t="str">
         <v>PAC-1106</v>
@@ -2888,7 +2888,7 @@
         <v>2026-04-15</v>
       </c>
       <c r="B109" t="str">
-        <v>Urgencia</v>
+        <v>Medicina</v>
       </c>
       <c r="C109" t="str">
         <v>Diurno</v>
@@ -2897,7 +2897,7 @@
         <v>Registro de escala</v>
       </c>
       <c r="E109" t="str">
-        <v>Cumple</v>
+        <v>Sí</v>
       </c>
       <c r="F109">
         <v>20</v>
@@ -2911,19 +2911,19 @@
         <v>2026-01-15</v>
       </c>
       <c r="B110" t="str">
-        <v>Cirugía</v>
+        <v>Urgencia</v>
       </c>
       <c r="C110" t="str">
-        <v>Diurno</v>
+        <v>Nocturno</v>
       </c>
       <c r="D110" t="str">
-        <v>Valoración de riesgo</v>
+        <v>Uso de superficie</v>
       </c>
       <c r="E110" t="str">
-        <v>Cumple</v>
-      </c>
-      <c r="F110" t="str">
-        <v>Bajo</v>
+        <v>No</v>
+      </c>
+      <c r="F110">
+        <v>20</v>
       </c>
       <c r="G110" t="str">
         <v>PAC-1108</v>
@@ -2934,7 +2934,7 @@
         <v>2026-02-15</v>
       </c>
       <c r="B111" t="str">
-        <v>Urgencia</v>
+        <v>Cirugía</v>
       </c>
       <c r="C111" t="str">
         <v>Diurno</v>
@@ -2943,10 +2943,10 @@
         <v>Cambio de posición</v>
       </c>
       <c r="E111" t="str">
-        <v>SI</v>
-      </c>
-      <c r="F111">
-        <v>20</v>
+        <v>1</v>
+      </c>
+      <c r="F111" t="str">
+        <v>Bajo</v>
       </c>
       <c r="G111" t="str">
         <v>PAC-1109</v>
@@ -2957,19 +2957,19 @@
         <v>2026-03-15</v>
       </c>
       <c r="B112" t="str">
-        <v>Urgencia</v>
+        <v>UCI</v>
       </c>
       <c r="C112" t="str">
-        <v>Nocturno</v>
+        <v>Diurno</v>
       </c>
       <c r="D112" t="str">
-        <v>Registro de escala</v>
+        <v>Cambio de posición</v>
       </c>
       <c r="E112" t="str">
-        <v>Sí</v>
+        <v>Cumple</v>
       </c>
       <c r="F112" t="str">
-        <v>Alto</v>
+        <v>Bajo</v>
       </c>
       <c r="G112" t="str">
         <v>PAC-1110</v>
@@ -2980,7 +2980,7 @@
         <v>2026-04-15</v>
       </c>
       <c r="B113" t="str">
-        <v>Urgencia</v>
+        <v>Cirugía</v>
       </c>
       <c r="C113" t="str">
         <v>Diurno</v>
@@ -2989,10 +2989,10 @@
         <v>Registro de escala</v>
       </c>
       <c r="E113" t="str">
-        <v>NO</v>
-      </c>
-      <c r="F113">
-        <v>20</v>
+        <v>Cumple</v>
+      </c>
+      <c r="F113" t="str">
+        <v>Medio</v>
       </c>
       <c r="G113" t="str">
         <v>PAC-1111</v>
@@ -3003,16 +3003,16 @@
         <v>2026-01-15</v>
       </c>
       <c r="B114" t="str">
-        <v>Cirugía</v>
+        <v>UCI</v>
       </c>
       <c r="C114" t="str">
-        <v>Nocturno</v>
+        <v>Diurno</v>
       </c>
       <c r="D114" t="str">
-        <v>Cambio de posición</v>
+        <v>Registro de escala</v>
       </c>
       <c r="E114" t="str">
-        <v>1</v>
+        <v>Sí</v>
       </c>
       <c r="F114">
         <v>20</v>
@@ -3026,19 +3026,19 @@
         <v>2026-02-15</v>
       </c>
       <c r="B115" t="str">
-        <v>Medicina</v>
+        <v>Cirugía</v>
       </c>
       <c r="C115" t="str">
-        <v>Nocturno</v>
+        <v>Diurno</v>
       </c>
       <c r="D115" t="str">
         <v>Valoración de riesgo</v>
       </c>
       <c r="E115" t="str">
-        <v>0</v>
+        <v>Cumple</v>
       </c>
       <c r="F115" t="str">
-        <v>Bajo</v>
+        <v>Medio</v>
       </c>
       <c r="G115" t="str">
         <v>PAC-1113</v>
@@ -3049,16 +3049,16 @@
         <v>2026-03-15</v>
       </c>
       <c r="B116" t="str">
-        <v>Medicina</v>
+        <v>Urgencia</v>
       </c>
       <c r="C116" t="str">
         <v>Nocturno</v>
       </c>
       <c r="D116" t="str">
-        <v>Uso de superficie</v>
+        <v>Valoración de riesgo</v>
       </c>
       <c r="E116" t="str">
-        <v>Cumple</v>
+        <v>1</v>
       </c>
       <c r="F116" t="str">
         <v>Alto</v>
@@ -3078,13 +3078,13 @@
         <v>Nocturno</v>
       </c>
       <c r="D117" t="str">
-        <v>Uso de superficie</v>
+        <v>Cambio de posición</v>
       </c>
       <c r="E117" t="str">
-        <v>Cumple</v>
+        <v>0</v>
       </c>
       <c r="F117" t="str">
-        <v>Bajo</v>
+        <v>Alto</v>
       </c>
       <c r="G117" t="str">
         <v>PAC-1115</v>
@@ -3095,10 +3095,10 @@
         <v>2026-01-15</v>
       </c>
       <c r="B118" t="str">
-        <v>UCI</v>
+        <v>Cirugía</v>
       </c>
       <c r="C118" t="str">
-        <v>Nocturno</v>
+        <v>Diurno</v>
       </c>
       <c r="D118" t="str">
         <v>Valoración de riesgo</v>
@@ -3118,16 +3118,16 @@
         <v>2026-02-15</v>
       </c>
       <c r="B119" t="str">
-        <v>Cirugía</v>
+        <v>UCI</v>
       </c>
       <c r="C119" t="str">
-        <v>Diurno</v>
+        <v>Nocturno</v>
       </c>
       <c r="D119" t="str">
-        <v>Uso de superficie</v>
+        <v>Cambio de posición</v>
       </c>
       <c r="E119" t="str">
-        <v>Cumple</v>
+        <v>1</v>
       </c>
       <c r="F119">
         <v>11</v>
@@ -3141,19 +3141,19 @@
         <v>2026-03-15</v>
       </c>
       <c r="B120" t="str">
-        <v>Medicina</v>
+        <v>Cirugía</v>
       </c>
       <c r="C120" t="str">
         <v>Nocturno</v>
       </c>
       <c r="D120" t="str">
-        <v>Cambio de posición</v>
+        <v>Uso de superficie</v>
       </c>
       <c r="E120" t="str">
-        <v>No aplica</v>
+        <v>1</v>
       </c>
       <c r="F120" t="str">
-        <v>Medio</v>
+        <v>Alto</v>
       </c>
       <c r="G120" t="str">
         <v>PAC-1118</v>
@@ -3164,19 +3164,19 @@
         <v>2026-04-15</v>
       </c>
       <c r="B121" t="str">
-        <v>Medicina</v>
+        <v>Cirugía</v>
       </c>
       <c r="C121" t="str">
         <v>Nocturno</v>
       </c>
       <c r="D121" t="str">
-        <v>Valoración de riesgo</v>
+        <v>Uso de superficie</v>
       </c>
       <c r="E121" t="str">
-        <v>No aplica</v>
-      </c>
-      <c r="F121" t="str">
-        <v>Alto</v>
+        <v>1</v>
+      </c>
+      <c r="F121">
+        <v>11</v>
       </c>
       <c r="G121" t="str">
         <v>PAC-1119</v>
@@ -3196,10 +3196,10 @@
         <v>Valoración de riesgo</v>
       </c>
       <c r="E122" t="str">
-        <v>1</v>
-      </c>
-      <c r="F122">
-        <v>11</v>
+        <v>NO</v>
+      </c>
+      <c r="F122" t="str">
+        <v>Bajo</v>
       </c>
       <c r="G122" t="str">
         <v>PAC-1120</v>
@@ -3210,19 +3210,19 @@
         <v>2026-02-15</v>
       </c>
       <c r="B123" t="str">
-        <v>UCI</v>
+        <v>Cirugía</v>
       </c>
       <c r="C123" t="str">
-        <v>Nocturno</v>
+        <v>Diurno</v>
       </c>
       <c r="D123" t="str">
-        <v>Cambio de posición</v>
+        <v>Valoración de riesgo</v>
       </c>
       <c r="E123" t="str">
-        <v>Sí</v>
-      </c>
-      <c r="F123">
-        <v>11</v>
+        <v>1</v>
+      </c>
+      <c r="F123" t="str">
+        <v>Bajo</v>
       </c>
       <c r="G123" t="str">
         <v>PAC-1121</v>
@@ -3233,19 +3233,19 @@
         <v>2026-03-15</v>
       </c>
       <c r="B124" t="str">
-        <v>Urgencia</v>
+        <v>Medicina</v>
       </c>
       <c r="C124" t="str">
-        <v>Diurno</v>
+        <v>Nocturno</v>
       </c>
       <c r="D124" t="str">
         <v>Cambio de posición</v>
       </c>
       <c r="E124" t="str">
-        <v>NO</v>
-      </c>
-      <c r="F124">
-        <v>11</v>
+        <v>SI</v>
+      </c>
+      <c r="F124" t="str">
+        <v>Alto</v>
       </c>
       <c r="G124" t="str">
         <v>PAC-1122</v>
@@ -3262,13 +3262,13 @@
         <v>Diurno</v>
       </c>
       <c r="D125" t="str">
-        <v>Uso de superficie</v>
+        <v>Valoración de riesgo</v>
       </c>
       <c r="E125" t="str">
-        <v>Cumple</v>
-      </c>
-      <c r="F125">
-        <v>11</v>
+        <v>1</v>
+      </c>
+      <c r="F125" t="str">
+        <v>Medio</v>
       </c>
       <c r="G125" t="str">
         <v>PAC-1123</v>
@@ -3279,19 +3279,19 @@
         <v>2026-01-15</v>
       </c>
       <c r="B126" t="str">
-        <v>Cirugía</v>
+        <v>UCI</v>
       </c>
       <c r="C126" t="str">
         <v>Diurno</v>
       </c>
       <c r="D126" t="str">
-        <v>Cambio de posición</v>
+        <v>Registro de escala</v>
       </c>
       <c r="E126" t="str">
-        <v>N/A</v>
-      </c>
-      <c r="F126">
-        <v>11</v>
+        <v>1</v>
+      </c>
+      <c r="F126" t="str">
+        <v>Medio</v>
       </c>
       <c r="G126" t="str">
         <v>PAC-1124</v>
@@ -3302,19 +3302,19 @@
         <v>2026-02-15</v>
       </c>
       <c r="B127" t="str">
-        <v>Cirugía</v>
+        <v>UCI</v>
       </c>
       <c r="C127" t="str">
-        <v>Nocturno</v>
+        <v>Diurno</v>
       </c>
       <c r="D127" t="str">
-        <v>Valoración de riesgo</v>
+        <v>Uso de superficie</v>
       </c>
       <c r="E127" t="str">
-        <v>Cumple</v>
+        <v>0</v>
       </c>
       <c r="F127" t="str">
-        <v>Bajo</v>
+        <v>Alto</v>
       </c>
       <c r="G127" t="str">
         <v>PAC-1125</v>
@@ -3331,13 +3331,13 @@
         <v>Nocturno</v>
       </c>
       <c r="D128" t="str">
-        <v>Valoración de riesgo</v>
+        <v>Cambio de posición</v>
       </c>
       <c r="E128" t="str">
-        <v>Sí</v>
-      </c>
-      <c r="F128" t="str">
-        <v>Medio</v>
+        <v>SI</v>
+      </c>
+      <c r="F128">
+        <v>11</v>
       </c>
       <c r="G128" t="str">
         <v>PAC-1126</v>
@@ -3348,19 +3348,19 @@
         <v>2026-04-15</v>
       </c>
       <c r="B129" t="str">
-        <v>UCI</v>
+        <v>Medicina</v>
       </c>
       <c r="C129" t="str">
-        <v>Diurno</v>
+        <v>Nocturno</v>
       </c>
       <c r="D129" t="str">
-        <v>Cambio de posición</v>
+        <v>Valoración de riesgo</v>
       </c>
       <c r="E129" t="str">
-        <v>Cumple</v>
+        <v>No</v>
       </c>
       <c r="F129" t="str">
-        <v>Alto</v>
+        <v>Bajo</v>
       </c>
       <c r="G129" t="str">
         <v>PAC-1127</v>
@@ -3377,13 +3377,13 @@
         <v>Nocturno</v>
       </c>
       <c r="D130" t="str">
-        <v>Registro de escala</v>
+        <v>Valoración de riesgo</v>
       </c>
       <c r="E130" t="str">
-        <v>SI</v>
-      </c>
-      <c r="F130">
-        <v>20</v>
+        <v>Sí</v>
+      </c>
+      <c r="F130" t="str">
+        <v>Medio</v>
       </c>
       <c r="G130" t="str">
         <v>PAC-1128</v>
@@ -3394,19 +3394,19 @@
         <v>2026-02-15</v>
       </c>
       <c r="B131" t="str">
-        <v>UCI</v>
+        <v>Medicina</v>
       </c>
       <c r="C131" t="str">
         <v>Nocturno</v>
       </c>
       <c r="D131" t="str">
-        <v>Uso de superficie</v>
+        <v>Registro de escala</v>
       </c>
       <c r="E131" t="str">
-        <v>Sí</v>
+        <v>N/A</v>
       </c>
       <c r="F131" t="str">
-        <v>Alto</v>
+        <v>Medio</v>
       </c>
       <c r="G131" t="str">
         <v>PAC-1129</v>
@@ -3417,7 +3417,7 @@
         <v>2026-03-15</v>
       </c>
       <c r="B132" t="str">
-        <v>Medicina</v>
+        <v>Urgencia</v>
       </c>
       <c r="C132" t="str">
         <v>Nocturno</v>
@@ -3426,10 +3426,10 @@
         <v>Valoración de riesgo</v>
       </c>
       <c r="E132" t="str">
-        <v>Cumple</v>
-      </c>
-      <c r="F132">
-        <v>11</v>
+        <v>N/A</v>
+      </c>
+      <c r="F132" t="str">
+        <v>Bajo</v>
       </c>
       <c r="G132" t="str">
         <v>PAC-1130</v>
@@ -3440,19 +3440,19 @@
         <v>2026-04-15</v>
       </c>
       <c r="B133" t="str">
-        <v>Medicina</v>
+        <v>UCI</v>
       </c>
       <c r="C133" t="str">
-        <v>Nocturno</v>
+        <v>Diurno</v>
       </c>
       <c r="D133" t="str">
-        <v>Valoración de riesgo</v>
+        <v>Cambio de posición</v>
       </c>
       <c r="E133" t="str">
-        <v>Cumple</v>
-      </c>
-      <c r="F133" t="str">
-        <v>Bajo</v>
+        <v>No aplica</v>
+      </c>
+      <c r="F133">
+        <v>11</v>
       </c>
       <c r="G133" t="str">
         <v>PAC-1131</v>
@@ -3469,13 +3469,13 @@
         <v>Diurno</v>
       </c>
       <c r="D134" t="str">
-        <v>Valoración de riesgo</v>
+        <v>Cambio de posición</v>
       </c>
       <c r="E134" t="str">
-        <v>SI</v>
-      </c>
-      <c r="F134" t="str">
-        <v>Medio</v>
+        <v>No aplica</v>
+      </c>
+      <c r="F134">
+        <v>20</v>
       </c>
       <c r="G134" t="str">
         <v>PAC-1132</v>
@@ -3486,19 +3486,19 @@
         <v>2026-02-15</v>
       </c>
       <c r="B135" t="str">
-        <v>UCI</v>
+        <v>Urgencia</v>
       </c>
       <c r="C135" t="str">
         <v>Diurno</v>
       </c>
       <c r="D135" t="str">
-        <v>Valoración de riesgo</v>
+        <v>Cambio de posición</v>
       </c>
       <c r="E135" t="str">
-        <v>SI</v>
+        <v>Sí</v>
       </c>
       <c r="F135" t="str">
-        <v>Bajo</v>
+        <v>Alto</v>
       </c>
       <c r="G135" t="str">
         <v>PAC-1133</v>
@@ -3512,16 +3512,16 @@
         <v>UCI</v>
       </c>
       <c r="C136" t="str">
-        <v>Diurno</v>
+        <v>Nocturno</v>
       </c>
       <c r="D136" t="str">
-        <v>Registro de escala</v>
+        <v>Cambio de posición</v>
       </c>
       <c r="E136" t="str">
-        <v>1</v>
+        <v>N/A</v>
       </c>
       <c r="F136" t="str">
-        <v>Bajo</v>
+        <v>Alto</v>
       </c>
       <c r="G136" t="str">
         <v>PAC-1134</v>
@@ -3532,19 +3532,19 @@
         <v>2026-04-15</v>
       </c>
       <c r="B137" t="str">
-        <v>Cirugía</v>
+        <v>Medicina</v>
       </c>
       <c r="C137" t="str">
-        <v>Diurno</v>
+        <v>Nocturno</v>
       </c>
       <c r="D137" t="str">
-        <v>Valoración de riesgo</v>
+        <v>Cambio de posición</v>
       </c>
       <c r="E137" t="str">
         <v>SI</v>
       </c>
       <c r="F137" t="str">
-        <v>Alto</v>
+        <v>Medio</v>
       </c>
       <c r="G137" t="str">
         <v>PAC-1135</v>
@@ -3555,7 +3555,7 @@
         <v>2026-01-15</v>
       </c>
       <c r="B138" t="str">
-        <v>UCI</v>
+        <v>Urgencia</v>
       </c>
       <c r="C138" t="str">
         <v>Diurno</v>
@@ -3564,10 +3564,10 @@
         <v>Cambio de posición</v>
       </c>
       <c r="E138" t="str">
-        <v>Sí</v>
-      </c>
-      <c r="F138">
-        <v>11</v>
+        <v>SI</v>
+      </c>
+      <c r="F138" t="str">
+        <v>Bajo</v>
       </c>
       <c r="G138" t="str">
         <v>PAC-1136</v>
@@ -3578,19 +3578,19 @@
         <v>2026-02-15</v>
       </c>
       <c r="B139" t="str">
-        <v>Cirugía</v>
+        <v>UCI</v>
       </c>
       <c r="C139" t="str">
-        <v>Diurno</v>
+        <v>Nocturno</v>
       </c>
       <c r="D139" t="str">
-        <v>Uso de superficie</v>
+        <v>Valoración de riesgo</v>
       </c>
       <c r="E139" t="str">
         <v>1</v>
       </c>
       <c r="F139">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="G139" t="str">
         <v>PAC-1137</v>
@@ -3601,19 +3601,19 @@
         <v>2026-03-15</v>
       </c>
       <c r="B140" t="str">
-        <v>Cirugía</v>
+        <v>Medicina</v>
       </c>
       <c r="C140" t="str">
-        <v>Nocturno</v>
+        <v>Diurno</v>
       </c>
       <c r="D140" t="str">
         <v>Valoración de riesgo</v>
       </c>
       <c r="E140" t="str">
-        <v>No aplica</v>
+        <v>Cumple</v>
       </c>
       <c r="F140" t="str">
-        <v>Medio</v>
+        <v>Bajo</v>
       </c>
       <c r="G140" t="str">
         <v>PAC-1138</v>
@@ -3624,19 +3624,19 @@
         <v>2026-04-15</v>
       </c>
       <c r="B141" t="str">
-        <v>UCI</v>
+        <v>Urgencia</v>
       </c>
       <c r="C141" t="str">
-        <v>Diurno</v>
+        <v>Nocturno</v>
       </c>
       <c r="D141" t="str">
-        <v>Uso de superficie</v>
+        <v>Registro de escala</v>
       </c>
       <c r="E141" t="str">
-        <v>Sí</v>
-      </c>
-      <c r="F141" t="str">
-        <v>Alto</v>
+        <v>0</v>
+      </c>
+      <c r="F141">
+        <v>11</v>
       </c>
       <c r="G141" t="str">
         <v>PAC-1139</v>
@@ -3647,7 +3647,7 @@
         <v>2026-01-15</v>
       </c>
       <c r="B142" t="str">
-        <v>Medicina</v>
+        <v>UCI</v>
       </c>
       <c r="C142" t="str">
         <v>Diurno</v>
@@ -3656,10 +3656,10 @@
         <v>Cambio de posición</v>
       </c>
       <c r="E142" t="str">
-        <v>SI</v>
-      </c>
-      <c r="F142" t="str">
-        <v>Medio</v>
+        <v>Cumple</v>
+      </c>
+      <c r="F142">
+        <v>11</v>
       </c>
       <c r="G142" t="str">
         <v>PAC-1140</v>
@@ -3673,16 +3673,16 @@
         <v>Medicina</v>
       </c>
       <c r="C143" t="str">
-        <v>Nocturno</v>
+        <v>Diurno</v>
       </c>
       <c r="D143" t="str">
-        <v>Uso de superficie</v>
+        <v>Registro de escala</v>
       </c>
       <c r="E143" t="str">
         <v>Cumple</v>
       </c>
       <c r="F143">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="G143" t="str">
         <v>PAC-1141</v>
@@ -3693,19 +3693,19 @@
         <v>2026-03-15</v>
       </c>
       <c r="B144" t="str">
-        <v>UCI</v>
+        <v>Cirugía</v>
       </c>
       <c r="C144" t="str">
-        <v>Diurno</v>
+        <v>Nocturno</v>
       </c>
       <c r="D144" t="str">
-        <v>Valoración de riesgo</v>
+        <v>Cambio de posición</v>
       </c>
       <c r="E144" t="str">
-        <v>No cumple</v>
-      </c>
-      <c r="F144" t="str">
-        <v>Alto</v>
+        <v>Sí</v>
+      </c>
+      <c r="F144">
+        <v>11</v>
       </c>
       <c r="G144" t="str">
         <v>PAC-1142</v>
@@ -3722,13 +3722,13 @@
         <v>Nocturno</v>
       </c>
       <c r="D145" t="str">
-        <v>Cambio de posición</v>
+        <v>Registro de escala</v>
       </c>
       <c r="E145" t="str">
-        <v>No cumple</v>
-      </c>
-      <c r="F145" t="str">
-        <v>Alto</v>
+        <v>1</v>
+      </c>
+      <c r="F145">
+        <v>11</v>
       </c>
       <c r="G145" t="str">
         <v>PAC-1143</v>
@@ -3739,19 +3739,19 @@
         <v>2026-01-15</v>
       </c>
       <c r="B146" t="str">
-        <v>Medicina</v>
+        <v>UCI</v>
       </c>
       <c r="C146" t="str">
         <v>Nocturno</v>
       </c>
       <c r="D146" t="str">
-        <v>Uso de superficie</v>
+        <v>Valoración de riesgo</v>
       </c>
       <c r="E146" t="str">
-        <v>SI</v>
-      </c>
-      <c r="F146">
-        <v>11</v>
+        <v>0</v>
+      </c>
+      <c r="F146" t="str">
+        <v>Alto</v>
       </c>
       <c r="G146" t="str">
         <v>PAC-1144</v>
@@ -3768,10 +3768,10 @@
         <v>Nocturno</v>
       </c>
       <c r="D147" t="str">
-        <v>Registro de escala</v>
+        <v>Valoración de riesgo</v>
       </c>
       <c r="E147" t="str">
-        <v>SI</v>
+        <v>Cumple</v>
       </c>
       <c r="F147" t="str">
         <v>Bajo</v>
@@ -3785,7 +3785,7 @@
         <v>2026-03-15</v>
       </c>
       <c r="B148" t="str">
-        <v>Cirugía</v>
+        <v>UCI</v>
       </c>
       <c r="C148" t="str">
         <v>Diurno</v>
@@ -3794,7 +3794,7 @@
         <v>Cambio de posición</v>
       </c>
       <c r="E148" t="str">
-        <v>Cumple</v>
+        <v>Sí</v>
       </c>
       <c r="F148" t="str">
         <v>Alto</v>
@@ -3808,7 +3808,7 @@
         <v>2026-04-15</v>
       </c>
       <c r="B149" t="str">
-        <v>Cirugía</v>
+        <v>Medicina</v>
       </c>
       <c r="C149" t="str">
         <v>Nocturno</v>
@@ -3817,7 +3817,7 @@
         <v>Registro de escala</v>
       </c>
       <c r="E149" t="str">
-        <v>SI</v>
+        <v>0</v>
       </c>
       <c r="F149">
         <v>11</v>
@@ -3831,16 +3831,16 @@
         <v>2026-01-15</v>
       </c>
       <c r="B150" t="str">
-        <v>Urgencia</v>
+        <v>UCI</v>
       </c>
       <c r="C150" t="str">
         <v>Nocturno</v>
       </c>
       <c r="D150" t="str">
-        <v>Valoración de riesgo</v>
+        <v>Cambio de posición</v>
       </c>
       <c r="E150" t="str">
-        <v>Cumple</v>
+        <v>Sí</v>
       </c>
       <c r="F150" t="str">
         <v>Medio</v>
@@ -3854,19 +3854,19 @@
         <v>2026-02-15</v>
       </c>
       <c r="B151" t="str">
-        <v>Urgencia</v>
+        <v>Cirugía</v>
       </c>
       <c r="C151" t="str">
-        <v>Nocturno</v>
+        <v>Diurno</v>
       </c>
       <c r="D151" t="str">
-        <v>Registro de escala</v>
+        <v>Cambio de posición</v>
       </c>
       <c r="E151" t="str">
-        <v>SI</v>
-      </c>
-      <c r="F151">
-        <v>20</v>
+        <v>1</v>
+      </c>
+      <c r="F151" t="str">
+        <v>Alto</v>
       </c>
       <c r="G151" t="str">
         <v>PAC-1149</v>
@@ -3877,16 +3877,16 @@
         <v>2026-03-15</v>
       </c>
       <c r="B152" t="str">
-        <v>Cirugía</v>
+        <v>Medicina</v>
       </c>
       <c r="C152" t="str">
         <v>Diurno</v>
       </c>
       <c r="D152" t="str">
-        <v>Cambio de posición</v>
+        <v>Uso de superficie</v>
       </c>
       <c r="E152" t="str">
-        <v>Cumple</v>
+        <v>Sí</v>
       </c>
       <c r="F152" t="str">
         <v>Bajo</v>
@@ -3900,19 +3900,19 @@
         <v>2026-04-15</v>
       </c>
       <c r="B153" t="str">
-        <v>Medicina</v>
+        <v>UCI</v>
       </c>
       <c r="C153" t="str">
         <v>Nocturno</v>
       </c>
       <c r="D153" t="str">
-        <v>Valoración de riesgo</v>
+        <v>Cambio de posición</v>
       </c>
       <c r="E153" t="str">
-        <v>No cumple</v>
-      </c>
-      <c r="F153">
-        <v>20</v>
+        <v>1</v>
+      </c>
+      <c r="F153" t="str">
+        <v>Medio</v>
       </c>
       <c r="G153" t="str">
         <v>PAC-1151</v>
@@ -3923,19 +3923,19 @@
         <v>2026-01-15</v>
       </c>
       <c r="B154" t="str">
-        <v>UCI</v>
+        <v>Medicina</v>
       </c>
       <c r="C154" t="str">
         <v>Diurno</v>
       </c>
       <c r="D154" t="str">
-        <v>Cambio de posición</v>
+        <v>Registro de escala</v>
       </c>
       <c r="E154" t="str">
-        <v>Sí</v>
-      </c>
-      <c r="F154">
-        <v>20</v>
+        <v>1</v>
+      </c>
+      <c r="F154" t="str">
+        <v>Bajo</v>
       </c>
       <c r="G154" t="str">
         <v>PAC-1152</v>
@@ -3946,19 +3946,19 @@
         <v>2026-02-15</v>
       </c>
       <c r="B155" t="str">
-        <v>Medicina</v>
+        <v>Urgencia</v>
       </c>
       <c r="C155" t="str">
         <v>Nocturno</v>
       </c>
       <c r="D155" t="str">
-        <v>Valoración de riesgo</v>
+        <v>Uso de superficie</v>
       </c>
       <c r="E155" t="str">
-        <v>SI</v>
-      </c>
-      <c r="F155" t="str">
-        <v>Bajo</v>
+        <v>NO</v>
+      </c>
+      <c r="F155">
+        <v>20</v>
       </c>
       <c r="G155" t="str">
         <v>PAC-1153</v>
@@ -3969,19 +3969,19 @@
         <v>2026-03-15</v>
       </c>
       <c r="B156" t="str">
-        <v>Medicina</v>
+        <v>Urgencia</v>
       </c>
       <c r="C156" t="str">
-        <v>Diurno</v>
+        <v>Nocturno</v>
       </c>
       <c r="D156" t="str">
         <v>Registro de escala</v>
       </c>
       <c r="E156" t="str">
-        <v>1</v>
+        <v>SI</v>
       </c>
       <c r="F156" t="str">
-        <v>Alto</v>
+        <v>Bajo</v>
       </c>
       <c r="G156" t="str">
         <v>PAC-1154</v>
@@ -3992,19 +3992,19 @@
         <v>2026-04-15</v>
       </c>
       <c r="B157" t="str">
-        <v>UCI</v>
+        <v>Cirugía</v>
       </c>
       <c r="C157" t="str">
-        <v>Diurno</v>
+        <v>Nocturno</v>
       </c>
       <c r="D157" t="str">
         <v>Uso de superficie</v>
       </c>
       <c r="E157" t="str">
-        <v>No cumple</v>
-      </c>
-      <c r="F157">
-        <v>20</v>
+        <v>SI</v>
+      </c>
+      <c r="F157" t="str">
+        <v>Medio</v>
       </c>
       <c r="G157" t="str">
         <v>PAC-1155</v>
@@ -4015,19 +4015,19 @@
         <v>2026-01-15</v>
       </c>
       <c r="B158" t="str">
-        <v>Medicina</v>
+        <v>Urgencia</v>
       </c>
       <c r="C158" t="str">
-        <v>Diurno</v>
+        <v>Nocturno</v>
       </c>
       <c r="D158" t="str">
-        <v>Cambio de posición</v>
+        <v>Registro de escala</v>
       </c>
       <c r="E158" t="str">
         <v>Cumple</v>
       </c>
-      <c r="F158" t="str">
-        <v>Alto</v>
+      <c r="F158">
+        <v>20</v>
       </c>
       <c r="G158" t="str">
         <v>PAC-1156</v>
@@ -4038,19 +4038,19 @@
         <v>2026-02-15</v>
       </c>
       <c r="B159" t="str">
-        <v>UCI</v>
+        <v>Cirugía</v>
       </c>
       <c r="C159" t="str">
-        <v>Nocturno</v>
+        <v>Diurno</v>
       </c>
       <c r="D159" t="str">
-        <v>Valoración de riesgo</v>
+        <v>Uso de superficie</v>
       </c>
       <c r="E159" t="str">
-        <v>Sí</v>
-      </c>
-      <c r="F159">
-        <v>20</v>
+        <v>SI</v>
+      </c>
+      <c r="F159" t="str">
+        <v>Medio</v>
       </c>
       <c r="G159" t="str">
         <v>PAC-1157</v>
@@ -4061,16 +4061,16 @@
         <v>2026-03-15</v>
       </c>
       <c r="B160" t="str">
-        <v>UCI</v>
+        <v>Cirugía</v>
       </c>
       <c r="C160" t="str">
-        <v>Diurno</v>
+        <v>Nocturno</v>
       </c>
       <c r="D160" t="str">
         <v>Valoración de riesgo</v>
       </c>
       <c r="E160" t="str">
-        <v>Cumple</v>
+        <v>No cumple</v>
       </c>
       <c r="F160" t="str">
         <v>Medio</v>
@@ -4084,7 +4084,7 @@
         <v>2026-04-15</v>
       </c>
       <c r="B161" t="str">
-        <v>Cirugía</v>
+        <v>Urgencia</v>
       </c>
       <c r="C161" t="str">
         <v>Diurno</v>
@@ -4093,10 +4093,10 @@
         <v>Valoración de riesgo</v>
       </c>
       <c r="E161" t="str">
-        <v>SI</v>
+        <v>1</v>
       </c>
       <c r="F161" t="str">
-        <v>Bajo</v>
+        <v>Medio</v>
       </c>
       <c r="G161" t="str">
         <v>PAC-1159</v>

--- a/examples/auditoria-ejemplo.xlsx
+++ b/examples/auditoria-ejemplo.xlsx
@@ -427,19 +427,19 @@
         <v>2026-01-15</v>
       </c>
       <c r="B2" t="str">
-        <v>UCI</v>
+        <v>Urgencia</v>
       </c>
       <c r="C2" t="str">
         <v>Nocturno</v>
       </c>
       <c r="D2" t="str">
-        <v>Registro de escala</v>
+        <v>Uso de superficie</v>
       </c>
       <c r="E2" t="str">
-        <v>Sí</v>
+        <v>SI</v>
       </c>
       <c r="F2" t="str">
-        <v>Bajo</v>
+        <v>Medio</v>
       </c>
       <c r="G2" t="str">
         <v>PAC-1000</v>
@@ -450,19 +450,19 @@
         <v>2026-02-15</v>
       </c>
       <c r="B3" t="str">
-        <v>UCI</v>
+        <v>Cirugía</v>
       </c>
       <c r="C3" t="str">
         <v>Nocturno</v>
       </c>
       <c r="D3" t="str">
-        <v>Valoración de riesgo</v>
+        <v>Registro de escala</v>
       </c>
       <c r="E3" t="str">
-        <v>0</v>
-      </c>
-      <c r="F3">
-        <v>11</v>
+        <v>Cumple</v>
+      </c>
+      <c r="F3" t="str">
+        <v>Alto</v>
       </c>
       <c r="G3" t="str">
         <v>PAC-1001</v>
@@ -473,19 +473,19 @@
         <v>2026-03-15</v>
       </c>
       <c r="B4" t="str">
-        <v>UCI</v>
+        <v>Medicina</v>
       </c>
       <c r="C4" t="str">
         <v>Nocturno</v>
       </c>
       <c r="D4" t="str">
-        <v>Registro de escala</v>
+        <v>Valoración de riesgo</v>
       </c>
       <c r="E4" t="str">
-        <v>1</v>
-      </c>
-      <c r="F4">
-        <v>20</v>
+        <v>Cumple</v>
+      </c>
+      <c r="F4" t="str">
+        <v>Bajo</v>
       </c>
       <c r="G4" t="str">
         <v>PAC-1002</v>
@@ -496,19 +496,19 @@
         <v>2026-04-15</v>
       </c>
       <c r="B5" t="str">
-        <v>Cirugía</v>
+        <v>Medicina</v>
       </c>
       <c r="C5" t="str">
-        <v>Diurno</v>
+        <v>Nocturno</v>
       </c>
       <c r="D5" t="str">
-        <v>Uso de superficie</v>
+        <v>Cambio de posición</v>
       </c>
       <c r="E5" t="str">
-        <v>Cumple</v>
-      </c>
-      <c r="F5">
-        <v>20</v>
+        <v>Sí</v>
+      </c>
+      <c r="F5" t="str">
+        <v>Alto</v>
       </c>
       <c r="G5" t="str">
         <v>PAC-1003</v>
@@ -525,13 +525,13 @@
         <v>Diurno</v>
       </c>
       <c r="D6" t="str">
-        <v>Cambio de posición</v>
+        <v>Valoración de riesgo</v>
       </c>
       <c r="E6" t="str">
-        <v>Sí</v>
+        <v>1</v>
       </c>
       <c r="F6" t="str">
-        <v>Medio</v>
+        <v>Bajo</v>
       </c>
       <c r="G6" t="str">
         <v>PAC-1004</v>
@@ -548,13 +548,13 @@
         <v>Diurno</v>
       </c>
       <c r="D7" t="str">
-        <v>Valoración de riesgo</v>
+        <v>Uso de superficie</v>
       </c>
       <c r="E7" t="str">
-        <v>SI</v>
+        <v>N/A</v>
       </c>
       <c r="F7">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="G7" t="str">
         <v>PAC-1005</v>
@@ -571,13 +571,13 @@
         <v>Diurno</v>
       </c>
       <c r="D8" t="str">
-        <v>Cambio de posición</v>
+        <v>Valoración de riesgo</v>
       </c>
       <c r="E8" t="str">
-        <v>Sí</v>
-      </c>
-      <c r="F8">
-        <v>20</v>
+        <v>1</v>
+      </c>
+      <c r="F8" t="str">
+        <v>Medio</v>
       </c>
       <c r="G8" t="str">
         <v>PAC-1006</v>
@@ -600,7 +600,7 @@
         <v>SI</v>
       </c>
       <c r="F9" t="str">
-        <v>Medio</v>
+        <v>Alto</v>
       </c>
       <c r="G9" t="str">
         <v>PAC-1007</v>
@@ -614,7 +614,7 @@
         <v>Cirugía</v>
       </c>
       <c r="C10" t="str">
-        <v>Diurno</v>
+        <v>Nocturno</v>
       </c>
       <c r="D10" t="str">
         <v>Registro de escala</v>
@@ -634,19 +634,19 @@
         <v>2026-02-15</v>
       </c>
       <c r="B11" t="str">
-        <v>UCI</v>
+        <v>Cirugía</v>
       </c>
       <c r="C11" t="str">
-        <v>Diurno</v>
+        <v>Nocturno</v>
       </c>
       <c r="D11" t="str">
-        <v>Uso de superficie</v>
+        <v>Valoración de riesgo</v>
       </c>
       <c r="E11" t="str">
-        <v>No cumple</v>
+        <v>Sí</v>
       </c>
       <c r="F11" t="str">
-        <v>Alto</v>
+        <v>Medio</v>
       </c>
       <c r="G11" t="str">
         <v>PAC-1009</v>
@@ -657,19 +657,19 @@
         <v>2026-03-15</v>
       </c>
       <c r="B12" t="str">
-        <v>Cirugía</v>
+        <v>Medicina</v>
       </c>
       <c r="C12" t="str">
         <v>Nocturno</v>
       </c>
       <c r="D12" t="str">
-        <v>Valoración de riesgo</v>
+        <v>Cambio de posición</v>
       </c>
       <c r="E12" t="str">
-        <v>Cumple</v>
+        <v>Sí</v>
       </c>
       <c r="F12" t="str">
-        <v>Medio</v>
+        <v>Alto</v>
       </c>
       <c r="G12" t="str">
         <v>PAC-1010</v>
@@ -680,19 +680,19 @@
         <v>2026-04-15</v>
       </c>
       <c r="B13" t="str">
-        <v>Cirugía</v>
+        <v>Medicina</v>
       </c>
       <c r="C13" t="str">
         <v>Diurno</v>
       </c>
       <c r="D13" t="str">
-        <v>Uso de superficie</v>
+        <v>Registro de escala</v>
       </c>
       <c r="E13" t="str">
         <v>Cumple</v>
       </c>
       <c r="F13" t="str">
-        <v>Bajo</v>
+        <v>Medio</v>
       </c>
       <c r="G13" t="str">
         <v>PAC-1011</v>
@@ -712,10 +712,10 @@
         <v>Uso de superficie</v>
       </c>
       <c r="E14" t="str">
-        <v>No</v>
+        <v>SI</v>
       </c>
       <c r="F14" t="str">
-        <v>Medio</v>
+        <v>Alto</v>
       </c>
       <c r="G14" t="str">
         <v>PAC-1012</v>
@@ -729,16 +729,16 @@
         <v>UCI</v>
       </c>
       <c r="C15" t="str">
-        <v>Diurno</v>
+        <v>Nocturno</v>
       </c>
       <c r="D15" t="str">
         <v>Cambio de posición</v>
       </c>
       <c r="E15" t="str">
-        <v>Cumple</v>
-      </c>
-      <c r="F15">
-        <v>20</v>
+        <v>N/A</v>
+      </c>
+      <c r="F15" t="str">
+        <v>Bajo</v>
       </c>
       <c r="G15" t="str">
         <v>PAC-1013</v>
@@ -749,19 +749,19 @@
         <v>2026-03-15</v>
       </c>
       <c r="B16" t="str">
-        <v>Cirugía</v>
+        <v>Urgencia</v>
       </c>
       <c r="C16" t="str">
-        <v>Nocturno</v>
+        <v>Diurno</v>
       </c>
       <c r="D16" t="str">
-        <v>Uso de superficie</v>
+        <v>Registro de escala</v>
       </c>
       <c r="E16" t="str">
-        <v>Sí</v>
+        <v>0</v>
       </c>
       <c r="F16">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="G16" t="str">
         <v>PAC-1014</v>
@@ -781,10 +781,10 @@
         <v>Cambio de posición</v>
       </c>
       <c r="E17" t="str">
-        <v>Sí</v>
-      </c>
-      <c r="F17">
-        <v>11</v>
+        <v>SI</v>
+      </c>
+      <c r="F17" t="str">
+        <v>Alto</v>
       </c>
       <c r="G17" t="str">
         <v>PAC-1015</v>
@@ -795,19 +795,19 @@
         <v>2026-01-15</v>
       </c>
       <c r="B18" t="str">
-        <v>UCI</v>
+        <v>Medicina</v>
       </c>
       <c r="C18" t="str">
         <v>Nocturno</v>
       </c>
       <c r="D18" t="str">
-        <v>Registro de escala</v>
+        <v>Cambio de posición</v>
       </c>
       <c r="E18" t="str">
-        <v>Cumple</v>
-      </c>
-      <c r="F18" t="str">
-        <v>Bajo</v>
+        <v>SI</v>
+      </c>
+      <c r="F18">
+        <v>11</v>
       </c>
       <c r="G18" t="str">
         <v>PAC-1016</v>
@@ -818,10 +818,10 @@
         <v>2026-02-15</v>
       </c>
       <c r="B19" t="str">
-        <v>Cirugía</v>
+        <v>UCI</v>
       </c>
       <c r="C19" t="str">
-        <v>Diurno</v>
+        <v>Nocturno</v>
       </c>
       <c r="D19" t="str">
         <v>Registro de escala</v>
@@ -841,19 +841,19 @@
         <v>2026-03-15</v>
       </c>
       <c r="B20" t="str">
-        <v>UCI</v>
+        <v>Cirugía</v>
       </c>
       <c r="C20" t="str">
-        <v>Nocturno</v>
+        <v>Diurno</v>
       </c>
       <c r="D20" t="str">
-        <v>Uso de superficie</v>
+        <v>Cambio de posición</v>
       </c>
       <c r="E20" t="str">
-        <v>SI</v>
-      </c>
-      <c r="F20">
-        <v>11</v>
+        <v>1</v>
+      </c>
+      <c r="F20" t="str">
+        <v>Medio</v>
       </c>
       <c r="G20" t="str">
         <v>PAC-1018</v>
@@ -864,19 +864,19 @@
         <v>2026-04-15</v>
       </c>
       <c r="B21" t="str">
-        <v>UCI</v>
+        <v>Medicina</v>
       </c>
       <c r="C21" t="str">
-        <v>Diurno</v>
+        <v>Nocturno</v>
       </c>
       <c r="D21" t="str">
-        <v>Registro de escala</v>
+        <v>Cambio de posición</v>
       </c>
       <c r="E21" t="str">
-        <v>No cumple</v>
-      </c>
-      <c r="F21">
-        <v>20</v>
+        <v>Cumple</v>
+      </c>
+      <c r="F21" t="str">
+        <v>Alto</v>
       </c>
       <c r="G21" t="str">
         <v>PAC-1019</v>
@@ -890,13 +890,13 @@
         <v>Cirugía</v>
       </c>
       <c r="C22" t="str">
-        <v>Nocturno</v>
+        <v>Diurno</v>
       </c>
       <c r="D22" t="str">
-        <v>Cambio de posición</v>
+        <v>Registro de escala</v>
       </c>
       <c r="E22" t="str">
-        <v>0</v>
+        <v>Cumple</v>
       </c>
       <c r="F22" t="str">
         <v>Bajo</v>
@@ -910,19 +910,19 @@
         <v>2026-02-15</v>
       </c>
       <c r="B23" t="str">
-        <v>Medicina</v>
+        <v>Urgencia</v>
       </c>
       <c r="C23" t="str">
         <v>Nocturno</v>
       </c>
       <c r="D23" t="str">
-        <v>Cambio de posición</v>
+        <v>Valoración de riesgo</v>
       </c>
       <c r="E23" t="str">
         <v>SI</v>
       </c>
       <c r="F23" t="str">
-        <v>Medio</v>
+        <v>Alto</v>
       </c>
       <c r="G23" t="str">
         <v>PAC-1021</v>
@@ -936,16 +936,16 @@
         <v>UCI</v>
       </c>
       <c r="C24" t="str">
-        <v>Nocturno</v>
+        <v>Diurno</v>
       </c>
       <c r="D24" t="str">
         <v>Valoración de riesgo</v>
       </c>
       <c r="E24" t="str">
-        <v>SI</v>
+        <v>Sí</v>
       </c>
       <c r="F24" t="str">
-        <v>Alto</v>
+        <v>Medio</v>
       </c>
       <c r="G24" t="str">
         <v>PAC-1022</v>
@@ -956,16 +956,16 @@
         <v>2026-04-15</v>
       </c>
       <c r="B25" t="str">
-        <v>UCI</v>
+        <v>Medicina</v>
       </c>
       <c r="C25" t="str">
-        <v>Diurno</v>
+        <v>Nocturno</v>
       </c>
       <c r="D25" t="str">
-        <v>Valoración de riesgo</v>
+        <v>Cambio de posición</v>
       </c>
       <c r="E25" t="str">
-        <v>Cumple</v>
+        <v>Sí</v>
       </c>
       <c r="F25" t="str">
         <v>Bajo</v>
@@ -979,19 +979,19 @@
         <v>2026-01-15</v>
       </c>
       <c r="B26" t="str">
-        <v>Cirugía</v>
+        <v>Urgencia</v>
       </c>
       <c r="C26" t="str">
-        <v>Nocturno</v>
+        <v>Diurno</v>
       </c>
       <c r="D26" t="str">
-        <v>Registro de escala</v>
+        <v>Cambio de posición</v>
       </c>
       <c r="E26" t="str">
-        <v>Cumple</v>
-      </c>
-      <c r="F26" t="str">
-        <v>Medio</v>
+        <v>1</v>
+      </c>
+      <c r="F26">
+        <v>11</v>
       </c>
       <c r="G26" t="str">
         <v>PAC-1024</v>
@@ -1002,7 +1002,7 @@
         <v>2026-02-15</v>
       </c>
       <c r="B27" t="str">
-        <v>Cirugía</v>
+        <v>Urgencia</v>
       </c>
       <c r="C27" t="str">
         <v>Diurno</v>
@@ -1011,10 +1011,10 @@
         <v>Cambio de posición</v>
       </c>
       <c r="E27" t="str">
-        <v>No aplica</v>
-      </c>
-      <c r="F27">
-        <v>20</v>
+        <v>Cumple</v>
+      </c>
+      <c r="F27" t="str">
+        <v>Bajo</v>
       </c>
       <c r="G27" t="str">
         <v>PAC-1025</v>
@@ -1025,10 +1025,10 @@
         <v>2026-03-15</v>
       </c>
       <c r="B28" t="str">
-        <v>Medicina</v>
+        <v>UCI</v>
       </c>
       <c r="C28" t="str">
-        <v>Nocturno</v>
+        <v>Diurno</v>
       </c>
       <c r="D28" t="str">
         <v>Uso de superficie</v>
@@ -1036,8 +1036,8 @@
       <c r="E28" t="str">
         <v>1</v>
       </c>
-      <c r="F28" t="str">
-        <v>Alto</v>
+      <c r="F28">
+        <v>20</v>
       </c>
       <c r="G28" t="str">
         <v>PAC-1026</v>
@@ -1048,19 +1048,19 @@
         <v>2026-04-15</v>
       </c>
       <c r="B29" t="str">
-        <v>UCI</v>
+        <v>Cirugía</v>
       </c>
       <c r="C29" t="str">
-        <v>Diurno</v>
+        <v>Nocturno</v>
       </c>
       <c r="D29" t="str">
-        <v>Valoración de riesgo</v>
+        <v>Cambio de posición</v>
       </c>
       <c r="E29" t="str">
-        <v>N/A</v>
-      </c>
-      <c r="F29" t="str">
-        <v>Alto</v>
+        <v>Sí</v>
+      </c>
+      <c r="F29">
+        <v>11</v>
       </c>
       <c r="G29" t="str">
         <v>PAC-1027</v>
@@ -1074,16 +1074,16 @@
         <v>Cirugía</v>
       </c>
       <c r="C30" t="str">
-        <v>Diurno</v>
+        <v>Nocturno</v>
       </c>
       <c r="D30" t="str">
         <v>Valoración de riesgo</v>
       </c>
       <c r="E30" t="str">
-        <v>SI</v>
-      </c>
-      <c r="F30" t="str">
-        <v>Bajo</v>
+        <v>0</v>
+      </c>
+      <c r="F30">
+        <v>20</v>
       </c>
       <c r="G30" t="str">
         <v>PAC-1028</v>
@@ -1094,13 +1094,13 @@
         <v>2026-02-15</v>
       </c>
       <c r="B31" t="str">
-        <v>UCI</v>
+        <v>Urgencia</v>
       </c>
       <c r="C31" t="str">
-        <v>Nocturno</v>
+        <v>Diurno</v>
       </c>
       <c r="D31" t="str">
-        <v>Cambio de posición</v>
+        <v>Uso de superficie</v>
       </c>
       <c r="E31" t="str">
         <v>Sí</v>
@@ -1117,16 +1117,16 @@
         <v>2026-03-15</v>
       </c>
       <c r="B32" t="str">
-        <v>Cirugía</v>
+        <v>Urgencia</v>
       </c>
       <c r="C32" t="str">
-        <v>Nocturno</v>
+        <v>Diurno</v>
       </c>
       <c r="D32" t="str">
-        <v>Cambio de posición</v>
+        <v>Uso de superficie</v>
       </c>
       <c r="E32" t="str">
-        <v>NO</v>
+        <v>Cumple</v>
       </c>
       <c r="F32" t="str">
         <v>Medio</v>
@@ -1143,16 +1143,16 @@
         <v>Urgencia</v>
       </c>
       <c r="C33" t="str">
-        <v>Nocturno</v>
+        <v>Diurno</v>
       </c>
       <c r="D33" t="str">
-        <v>Uso de superficie</v>
+        <v>Valoración de riesgo</v>
       </c>
       <c r="E33" t="str">
-        <v>SI</v>
-      </c>
-      <c r="F33">
-        <v>20</v>
+        <v>NO</v>
+      </c>
+      <c r="F33" t="str">
+        <v>Alto</v>
       </c>
       <c r="G33" t="str">
         <v>PAC-1031</v>
@@ -1163,19 +1163,19 @@
         <v>2026-01-15</v>
       </c>
       <c r="B34" t="str">
-        <v>Cirugía</v>
+        <v>Urgencia</v>
       </c>
       <c r="C34" t="str">
         <v>Diurno</v>
       </c>
       <c r="D34" t="str">
-        <v>Uso de superficie</v>
+        <v>Cambio de posición</v>
       </c>
       <c r="E34" t="str">
-        <v>Cumple</v>
+        <v>No</v>
       </c>
       <c r="F34">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="G34" t="str">
         <v>PAC-1032</v>
@@ -1186,19 +1186,19 @@
         <v>2026-02-15</v>
       </c>
       <c r="B35" t="str">
-        <v>Medicina</v>
+        <v>UCI</v>
       </c>
       <c r="C35" t="str">
         <v>Diurno</v>
       </c>
       <c r="D35" t="str">
-        <v>Valoración de riesgo</v>
+        <v>Uso de superficie</v>
       </c>
       <c r="E35" t="str">
-        <v>1</v>
+        <v>NO</v>
       </c>
       <c r="F35" t="str">
-        <v>Alto</v>
+        <v>Bajo</v>
       </c>
       <c r="G35" t="str">
         <v>PAC-1033</v>
@@ -1218,10 +1218,10 @@
         <v>Valoración de riesgo</v>
       </c>
       <c r="E36" t="str">
-        <v>Cumple</v>
-      </c>
-      <c r="F36">
-        <v>11</v>
+        <v>Sí</v>
+      </c>
+      <c r="F36" t="str">
+        <v>Bajo</v>
       </c>
       <c r="G36" t="str">
         <v>PAC-1034</v>
@@ -1232,19 +1232,19 @@
         <v>2026-04-15</v>
       </c>
       <c r="B37" t="str">
-        <v>Medicina</v>
+        <v>Urgencia</v>
       </c>
       <c r="C37" t="str">
-        <v>Diurno</v>
+        <v>Nocturno</v>
       </c>
       <c r="D37" t="str">
-        <v>Cambio de posición</v>
+        <v>Valoración de riesgo</v>
       </c>
       <c r="E37" t="str">
-        <v>SI</v>
+        <v>NO</v>
       </c>
       <c r="F37" t="str">
-        <v>Alto</v>
+        <v>Medio</v>
       </c>
       <c r="G37" t="str">
         <v>PAC-1035</v>
@@ -1255,19 +1255,19 @@
         <v>2026-01-15</v>
       </c>
       <c r="B38" t="str">
-        <v>UCI</v>
+        <v>Cirugía</v>
       </c>
       <c r="C38" t="str">
         <v>Diurno</v>
       </c>
       <c r="D38" t="str">
-        <v>Valoración de riesgo</v>
+        <v>Cambio de posición</v>
       </c>
       <c r="E38" t="str">
-        <v>Sí</v>
-      </c>
-      <c r="F38">
-        <v>11</v>
+        <v>No aplica</v>
+      </c>
+      <c r="F38" t="str">
+        <v>Medio</v>
       </c>
       <c r="G38" t="str">
         <v>PAC-1036</v>
@@ -1278,19 +1278,19 @@
         <v>2026-02-15</v>
       </c>
       <c r="B39" t="str">
-        <v>Cirugía</v>
+        <v>Medicina</v>
       </c>
       <c r="C39" t="str">
-        <v>Diurno</v>
+        <v>Nocturno</v>
       </c>
       <c r="D39" t="str">
-        <v>Cambio de posición</v>
+        <v>Valoración de riesgo</v>
       </c>
       <c r="E39" t="str">
-        <v>SI</v>
-      </c>
-      <c r="F39">
-        <v>20</v>
+        <v>1</v>
+      </c>
+      <c r="F39" t="str">
+        <v>Bajo</v>
       </c>
       <c r="G39" t="str">
         <v>PAC-1037</v>
@@ -1301,19 +1301,19 @@
         <v>2026-03-15</v>
       </c>
       <c r="B40" t="str">
-        <v>UCI</v>
+        <v>Cirugía</v>
       </c>
       <c r="C40" t="str">
         <v>Diurno</v>
       </c>
       <c r="D40" t="str">
-        <v>Uso de superficie</v>
+        <v>Valoración de riesgo</v>
       </c>
       <c r="E40" t="str">
-        <v>No cumple</v>
+        <v>Sí</v>
       </c>
       <c r="F40" t="str">
-        <v>Medio</v>
+        <v>Bajo</v>
       </c>
       <c r="G40" t="str">
         <v>PAC-1038</v>
@@ -1327,13 +1327,13 @@
         <v>Medicina</v>
       </c>
       <c r="C41" t="str">
-        <v>Diurno</v>
+        <v>Nocturno</v>
       </c>
       <c r="D41" t="str">
-        <v>Uso de superficie</v>
+        <v>Registro de escala</v>
       </c>
       <c r="E41" t="str">
-        <v>Cumple</v>
+        <v>Sí</v>
       </c>
       <c r="F41" t="str">
         <v>Bajo</v>
@@ -1347,7 +1347,7 @@
         <v>2026-01-15</v>
       </c>
       <c r="B42" t="str">
-        <v>Cirugía</v>
+        <v>Medicina</v>
       </c>
       <c r="C42" t="str">
         <v>Nocturno</v>
@@ -1356,10 +1356,10 @@
         <v>Registro de escala</v>
       </c>
       <c r="E42" t="str">
-        <v>0</v>
-      </c>
-      <c r="F42">
-        <v>11</v>
+        <v>NO</v>
+      </c>
+      <c r="F42" t="str">
+        <v>Alto</v>
       </c>
       <c r="G42" t="str">
         <v>PAC-1040</v>
@@ -1370,19 +1370,19 @@
         <v>2026-02-15</v>
       </c>
       <c r="B43" t="str">
-        <v>Urgencia</v>
+        <v>UCI</v>
       </c>
       <c r="C43" t="str">
         <v>Diurno</v>
       </c>
       <c r="D43" t="str">
-        <v>Registro de escala</v>
+        <v>Valoración de riesgo</v>
       </c>
       <c r="E43" t="str">
-        <v>NO</v>
+        <v>No aplica</v>
       </c>
       <c r="F43" t="str">
-        <v>Bajo</v>
+        <v>Medio</v>
       </c>
       <c r="G43" t="str">
         <v>PAC-1041</v>
@@ -1393,19 +1393,19 @@
         <v>2026-03-15</v>
       </c>
       <c r="B44" t="str">
-        <v>Urgencia</v>
+        <v>Medicina</v>
       </c>
       <c r="C44" t="str">
-        <v>Nocturno</v>
+        <v>Diurno</v>
       </c>
       <c r="D44" t="str">
-        <v>Registro de escala</v>
+        <v>Uso de superficie</v>
       </c>
       <c r="E44" t="str">
-        <v>SI</v>
+        <v>NO</v>
       </c>
       <c r="F44" t="str">
-        <v>Alto</v>
+        <v>Medio</v>
       </c>
       <c r="G44" t="str">
         <v>PAC-1042</v>
@@ -1416,19 +1416,19 @@
         <v>2026-04-15</v>
       </c>
       <c r="B45" t="str">
-        <v>Medicina</v>
+        <v>UCI</v>
       </c>
       <c r="C45" t="str">
         <v>Diurno</v>
       </c>
       <c r="D45" t="str">
-        <v>Cambio de posición</v>
+        <v>Registro de escala</v>
       </c>
       <c r="E45" t="str">
         <v>1</v>
       </c>
       <c r="F45" t="str">
-        <v>Bajo</v>
+        <v>Alto</v>
       </c>
       <c r="G45" t="str">
         <v>PAC-1043</v>
@@ -1442,16 +1442,16 @@
         <v>Medicina</v>
       </c>
       <c r="C46" t="str">
-        <v>Nocturno</v>
+        <v>Diurno</v>
       </c>
       <c r="D46" t="str">
-        <v>Valoración de riesgo</v>
+        <v>Uso de superficie</v>
       </c>
       <c r="E46" t="str">
-        <v>No</v>
-      </c>
-      <c r="F46">
-        <v>20</v>
+        <v>1</v>
+      </c>
+      <c r="F46" t="str">
+        <v>Alto</v>
       </c>
       <c r="G46" t="str">
         <v>PAC-1044</v>
@@ -1471,10 +1471,10 @@
         <v>Uso de superficie</v>
       </c>
       <c r="E47" t="str">
-        <v>1</v>
+        <v>Sí</v>
       </c>
       <c r="F47">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="G47" t="str">
         <v>PAC-1045</v>
@@ -1485,16 +1485,16 @@
         <v>2026-03-15</v>
       </c>
       <c r="B48" t="str">
-        <v>Cirugía</v>
+        <v>Urgencia</v>
       </c>
       <c r="C48" t="str">
         <v>Diurno</v>
       </c>
       <c r="D48" t="str">
-        <v>Registro de escala</v>
+        <v>Valoración de riesgo</v>
       </c>
       <c r="E48" t="str">
-        <v>Cumple</v>
+        <v>No aplica</v>
       </c>
       <c r="F48">
         <v>11</v>
@@ -1508,7 +1508,7 @@
         <v>2026-04-15</v>
       </c>
       <c r="B49" t="str">
-        <v>Urgencia</v>
+        <v>Cirugía</v>
       </c>
       <c r="C49" t="str">
         <v>Diurno</v>
@@ -1517,10 +1517,10 @@
         <v>Valoración de riesgo</v>
       </c>
       <c r="E49" t="str">
-        <v>Cumple</v>
+        <v>Sí</v>
       </c>
       <c r="F49" t="str">
-        <v>Bajo</v>
+        <v>Alto</v>
       </c>
       <c r="G49" t="str">
         <v>PAC-1047</v>
@@ -1531,16 +1531,16 @@
         <v>2026-01-15</v>
       </c>
       <c r="B50" t="str">
-        <v>Cirugía</v>
+        <v>UCI</v>
       </c>
       <c r="C50" t="str">
         <v>Nocturno</v>
       </c>
       <c r="D50" t="str">
-        <v>Registro de escala</v>
+        <v>Cambio de posición</v>
       </c>
       <c r="E50" t="str">
-        <v>1</v>
+        <v>Cumple</v>
       </c>
       <c r="F50" t="str">
         <v>Medio</v>
@@ -1557,16 +1557,16 @@
         <v>UCI</v>
       </c>
       <c r="C51" t="str">
-        <v>Diurno</v>
+        <v>Nocturno</v>
       </c>
       <c r="D51" t="str">
         <v>Uso de superficie</v>
       </c>
       <c r="E51" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F51" t="str">
-        <v>Bajo</v>
+        <v>Alto</v>
       </c>
       <c r="G51" t="str">
         <v>PAC-1049</v>
@@ -1577,16 +1577,16 @@
         <v>2026-03-15</v>
       </c>
       <c r="B52" t="str">
-        <v>Medicina</v>
+        <v>Urgencia</v>
       </c>
       <c r="C52" t="str">
-        <v>Diurno</v>
+        <v>Nocturno</v>
       </c>
       <c r="D52" t="str">
         <v>Valoración de riesgo</v>
       </c>
       <c r="E52" t="str">
-        <v>Cumple</v>
+        <v>0</v>
       </c>
       <c r="F52">
         <v>11</v>
@@ -1603,13 +1603,13 @@
         <v>Urgencia</v>
       </c>
       <c r="C53" t="str">
-        <v>Nocturno</v>
+        <v>Diurno</v>
       </c>
       <c r="D53" t="str">
-        <v>Uso de superficie</v>
+        <v>Cambio de posición</v>
       </c>
       <c r="E53" t="str">
-        <v>Sí</v>
+        <v>Cumple</v>
       </c>
       <c r="F53">
         <v>20</v>
@@ -1623,19 +1623,19 @@
         <v>2026-01-15</v>
       </c>
       <c r="B54" t="str">
-        <v>UCI</v>
+        <v>Urgencia</v>
       </c>
       <c r="C54" t="str">
-        <v>Diurno</v>
+        <v>Nocturno</v>
       </c>
       <c r="D54" t="str">
         <v>Cambio de posición</v>
       </c>
       <c r="E54" t="str">
-        <v>Sí</v>
+        <v>N/A</v>
       </c>
       <c r="F54" t="str">
-        <v>Medio</v>
+        <v>Alto</v>
       </c>
       <c r="G54" t="str">
         <v>PAC-1052</v>
@@ -1649,16 +1649,16 @@
         <v>Cirugía</v>
       </c>
       <c r="C55" t="str">
-        <v>Diurno</v>
+        <v>Nocturno</v>
       </c>
       <c r="D55" t="str">
-        <v>Cambio de posición</v>
+        <v>Valoración de riesgo</v>
       </c>
       <c r="E55" t="str">
-        <v>0</v>
-      </c>
-      <c r="F55" t="str">
-        <v>Bajo</v>
+        <v>No</v>
+      </c>
+      <c r="F55">
+        <v>11</v>
       </c>
       <c r="G55" t="str">
         <v>PAC-1053</v>
@@ -1669,19 +1669,19 @@
         <v>2026-03-15</v>
       </c>
       <c r="B56" t="str">
-        <v>Medicina</v>
+        <v>UCI</v>
       </c>
       <c r="C56" t="str">
-        <v>Diurno</v>
+        <v>Nocturno</v>
       </c>
       <c r="D56" t="str">
-        <v>Valoración de riesgo</v>
+        <v>Uso de superficie</v>
       </c>
       <c r="E56" t="str">
-        <v>SI</v>
-      </c>
-      <c r="F56" t="str">
-        <v>Bajo</v>
+        <v>N/A</v>
+      </c>
+      <c r="F56">
+        <v>20</v>
       </c>
       <c r="G56" t="str">
         <v>PAC-1054</v>
@@ -1698,13 +1698,13 @@
         <v>Diurno</v>
       </c>
       <c r="D57" t="str">
-        <v>Registro de escala</v>
+        <v>Valoración de riesgo</v>
       </c>
       <c r="E57" t="str">
-        <v>Sí</v>
-      </c>
-      <c r="F57">
-        <v>20</v>
+        <v>Cumple</v>
+      </c>
+      <c r="F57" t="str">
+        <v>Medio</v>
       </c>
       <c r="G57" t="str">
         <v>PAC-1055</v>
@@ -1721,10 +1721,10 @@
         <v>Diurno</v>
       </c>
       <c r="D58" t="str">
-        <v>Valoración de riesgo</v>
+        <v>Registro de escala</v>
       </c>
       <c r="E58" t="str">
-        <v>Cumple</v>
+        <v>SI</v>
       </c>
       <c r="F58">
         <v>20</v>
@@ -1738,19 +1738,19 @@
         <v>2026-02-15</v>
       </c>
       <c r="B59" t="str">
-        <v>Urgencia</v>
+        <v>Medicina</v>
       </c>
       <c r="C59" t="str">
-        <v>Diurno</v>
+        <v>Nocturno</v>
       </c>
       <c r="D59" t="str">
-        <v>Valoración de riesgo</v>
+        <v>Uso de superficie</v>
       </c>
       <c r="E59" t="str">
         <v>SI</v>
       </c>
-      <c r="F59">
-        <v>11</v>
+      <c r="F59" t="str">
+        <v>Bajo</v>
       </c>
       <c r="G59" t="str">
         <v>PAC-1057</v>
@@ -1761,19 +1761,19 @@
         <v>2026-03-15</v>
       </c>
       <c r="B60" t="str">
-        <v>Urgencia</v>
+        <v>Medicina</v>
       </c>
       <c r="C60" t="str">
         <v>Diurno</v>
       </c>
       <c r="D60" t="str">
-        <v>Cambio de posición</v>
+        <v>Valoración de riesgo</v>
       </c>
       <c r="E60" t="str">
-        <v>No</v>
+        <v>N/A</v>
       </c>
       <c r="F60" t="str">
-        <v>Medio</v>
+        <v>Alto</v>
       </c>
       <c r="G60" t="str">
         <v>PAC-1058</v>
@@ -1784,19 +1784,19 @@
         <v>2026-04-15</v>
       </c>
       <c r="B61" t="str">
-        <v>UCI</v>
+        <v>Medicina</v>
       </c>
       <c r="C61" t="str">
-        <v>Nocturno</v>
+        <v>Diurno</v>
       </c>
       <c r="D61" t="str">
-        <v>Valoración de riesgo</v>
+        <v>Registro de escala</v>
       </c>
       <c r="E61" t="str">
-        <v>No aplica</v>
+        <v>No</v>
       </c>
       <c r="F61" t="str">
-        <v>Alto</v>
+        <v>Medio</v>
       </c>
       <c r="G61" t="str">
         <v>PAC-1059</v>
@@ -1807,19 +1807,19 @@
         <v>2026-01-15</v>
       </c>
       <c r="B62" t="str">
-        <v>Medicina</v>
+        <v>UCI</v>
       </c>
       <c r="C62" t="str">
-        <v>Diurno</v>
+        <v>Nocturno</v>
       </c>
       <c r="D62" t="str">
-        <v>Valoración de riesgo</v>
+        <v>Uso de superficie</v>
       </c>
       <c r="E62" t="str">
-        <v>Cumple</v>
-      </c>
-      <c r="F62" t="str">
-        <v>Medio</v>
+        <v>Sí</v>
+      </c>
+      <c r="F62">
+        <v>20</v>
       </c>
       <c r="G62" t="str">
         <v>PAC-1060</v>
@@ -1839,10 +1839,10 @@
         <v>Cambio de posición</v>
       </c>
       <c r="E63" t="str">
-        <v>Cumple</v>
-      </c>
-      <c r="F63">
-        <v>20</v>
+        <v>No</v>
+      </c>
+      <c r="F63" t="str">
+        <v>Medio</v>
       </c>
       <c r="G63" t="str">
         <v>PAC-1061</v>
@@ -1853,16 +1853,16 @@
         <v>2026-03-15</v>
       </c>
       <c r="B64" t="str">
-        <v>Cirugía</v>
+        <v>UCI</v>
       </c>
       <c r="C64" t="str">
         <v>Nocturno</v>
       </c>
       <c r="D64" t="str">
-        <v>Valoración de riesgo</v>
+        <v>Registro de escala</v>
       </c>
       <c r="E64" t="str">
-        <v>Sí</v>
+        <v>Cumple</v>
       </c>
       <c r="F64">
         <v>11</v>
@@ -1876,19 +1876,19 @@
         <v>2026-04-15</v>
       </c>
       <c r="B65" t="str">
-        <v>Cirugía</v>
+        <v>Urgencia</v>
       </c>
       <c r="C65" t="str">
         <v>Nocturno</v>
       </c>
       <c r="D65" t="str">
-        <v>Registro de escala</v>
+        <v>Cambio de posición</v>
       </c>
       <c r="E65" t="str">
-        <v>Cumple</v>
+        <v>No</v>
       </c>
       <c r="F65" t="str">
-        <v>Bajo</v>
+        <v>Alto</v>
       </c>
       <c r="G65" t="str">
         <v>PAC-1063</v>
@@ -1899,19 +1899,19 @@
         <v>2026-01-15</v>
       </c>
       <c r="B66" t="str">
-        <v>Medicina</v>
+        <v>Urgencia</v>
       </c>
       <c r="C66" t="str">
-        <v>Nocturno</v>
+        <v>Diurno</v>
       </c>
       <c r="D66" t="str">
-        <v>Valoración de riesgo</v>
+        <v>Cambio de posición</v>
       </c>
       <c r="E66" t="str">
-        <v>Cumple</v>
-      </c>
-      <c r="F66" t="str">
-        <v>Alto</v>
+        <v>1</v>
+      </c>
+      <c r="F66">
+        <v>11</v>
       </c>
       <c r="G66" t="str">
         <v>PAC-1064</v>
@@ -1922,16 +1922,16 @@
         <v>2026-02-15</v>
       </c>
       <c r="B67" t="str">
-        <v>Urgencia</v>
+        <v>UCI</v>
       </c>
       <c r="C67" t="str">
         <v>Diurno</v>
       </c>
       <c r="D67" t="str">
-        <v>Registro de escala</v>
+        <v>Valoración de riesgo</v>
       </c>
       <c r="E67" t="str">
-        <v>1</v>
+        <v>Sí</v>
       </c>
       <c r="F67" t="str">
         <v>Alto</v>
@@ -1945,19 +1945,19 @@
         <v>2026-03-15</v>
       </c>
       <c r="B68" t="str">
-        <v>Medicina</v>
+        <v>Urgencia</v>
       </c>
       <c r="C68" t="str">
         <v>Diurno</v>
       </c>
       <c r="D68" t="str">
-        <v>Cambio de posición</v>
+        <v>Registro de escala</v>
       </c>
       <c r="E68" t="str">
-        <v>No aplica</v>
-      </c>
-      <c r="F68" t="str">
-        <v>Medio</v>
+        <v>Sí</v>
+      </c>
+      <c r="F68">
+        <v>20</v>
       </c>
       <c r="G68" t="str">
         <v>PAC-1066</v>
@@ -1968,19 +1968,19 @@
         <v>2026-04-15</v>
       </c>
       <c r="B69" t="str">
-        <v>UCI</v>
+        <v>Medicina</v>
       </c>
       <c r="C69" t="str">
-        <v>Diurno</v>
+        <v>Nocturno</v>
       </c>
       <c r="D69" t="str">
-        <v>Uso de superficie</v>
+        <v>Cambio de posición</v>
       </c>
       <c r="E69" t="str">
-        <v>SI</v>
+        <v>Sí</v>
       </c>
       <c r="F69" t="str">
-        <v>Medio</v>
+        <v>Alto</v>
       </c>
       <c r="G69" t="str">
         <v>PAC-1067</v>
@@ -1991,19 +1991,19 @@
         <v>2026-01-15</v>
       </c>
       <c r="B70" t="str">
-        <v>Cirugía</v>
+        <v>Medicina</v>
       </c>
       <c r="C70" t="str">
         <v>Diurno</v>
       </c>
       <c r="D70" t="str">
-        <v>Cambio de posición</v>
+        <v>Valoración de riesgo</v>
       </c>
       <c r="E70" t="str">
         <v>Cumple</v>
       </c>
-      <c r="F70" t="str">
-        <v>Alto</v>
+      <c r="F70">
+        <v>11</v>
       </c>
       <c r="G70" t="str">
         <v>PAC-1068</v>
@@ -2023,10 +2023,10 @@
         <v>Cambio de posición</v>
       </c>
       <c r="E71" t="str">
-        <v>1</v>
-      </c>
-      <c r="F71" t="str">
-        <v>Bajo</v>
+        <v>Cumple</v>
+      </c>
+      <c r="F71">
+        <v>20</v>
       </c>
       <c r="G71" t="str">
         <v>PAC-1069</v>
@@ -2037,19 +2037,19 @@
         <v>2026-03-15</v>
       </c>
       <c r="B72" t="str">
-        <v>Medicina</v>
+        <v>Urgencia</v>
       </c>
       <c r="C72" t="str">
-        <v>Diurno</v>
+        <v>Nocturno</v>
       </c>
       <c r="D72" t="str">
         <v>Uso de superficie</v>
       </c>
       <c r="E72" t="str">
-        <v>No aplica</v>
-      </c>
-      <c r="F72" t="str">
-        <v>Alto</v>
+        <v>Cumple</v>
+      </c>
+      <c r="F72">
+        <v>11</v>
       </c>
       <c r="G72" t="str">
         <v>PAC-1070</v>
@@ -2063,13 +2063,13 @@
         <v>UCI</v>
       </c>
       <c r="C73" t="str">
-        <v>Nocturno</v>
+        <v>Diurno</v>
       </c>
       <c r="D73" t="str">
-        <v>Cambio de posición</v>
+        <v>Registro de escala</v>
       </c>
       <c r="E73" t="str">
-        <v>No aplica</v>
+        <v>1</v>
       </c>
       <c r="F73">
         <v>20</v>
@@ -2083,19 +2083,19 @@
         <v>2026-01-15</v>
       </c>
       <c r="B74" t="str">
-        <v>Cirugía</v>
+        <v>Urgencia</v>
       </c>
       <c r="C74" t="str">
         <v>Diurno</v>
       </c>
       <c r="D74" t="str">
-        <v>Cambio de posición</v>
+        <v>Valoración de riesgo</v>
       </c>
       <c r="E74" t="str">
         <v>1</v>
       </c>
-      <c r="F74">
-        <v>20</v>
+      <c r="F74" t="str">
+        <v>Alto</v>
       </c>
       <c r="G74" t="str">
         <v>PAC-1072</v>
@@ -2109,16 +2109,16 @@
         <v>Urgencia</v>
       </c>
       <c r="C75" t="str">
-        <v>Diurno</v>
+        <v>Nocturno</v>
       </c>
       <c r="D75" t="str">
-        <v>Registro de escala</v>
+        <v>Cambio de posición</v>
       </c>
       <c r="E75" t="str">
-        <v>Cumple</v>
+        <v>Sí</v>
       </c>
       <c r="F75" t="str">
-        <v>Medio</v>
+        <v>Alto</v>
       </c>
       <c r="G75" t="str">
         <v>PAC-1073</v>
@@ -2129,19 +2129,19 @@
         <v>2026-03-15</v>
       </c>
       <c r="B76" t="str">
-        <v>Medicina</v>
+        <v>UCI</v>
       </c>
       <c r="C76" t="str">
-        <v>Nocturno</v>
+        <v>Diurno</v>
       </c>
       <c r="D76" t="str">
-        <v>Cambio de posición</v>
+        <v>Registro de escala</v>
       </c>
       <c r="E76" t="str">
-        <v>N/A</v>
-      </c>
-      <c r="F76">
-        <v>20</v>
+        <v>Sí</v>
+      </c>
+      <c r="F76" t="str">
+        <v>Medio</v>
       </c>
       <c r="G76" t="str">
         <v>PAC-1074</v>
@@ -2152,16 +2152,16 @@
         <v>2026-04-15</v>
       </c>
       <c r="B77" t="str">
-        <v>Urgencia</v>
+        <v>Medicina</v>
       </c>
       <c r="C77" t="str">
-        <v>Nocturno</v>
+        <v>Diurno</v>
       </c>
       <c r="D77" t="str">
-        <v>Valoración de riesgo</v>
+        <v>Registro de escala</v>
       </c>
       <c r="E77" t="str">
-        <v>SI</v>
+        <v>Sí</v>
       </c>
       <c r="F77">
         <v>20</v>
@@ -2175,19 +2175,19 @@
         <v>2026-01-15</v>
       </c>
       <c r="B78" t="str">
-        <v>Medicina</v>
+        <v>UCI</v>
       </c>
       <c r="C78" t="str">
-        <v>Nocturno</v>
+        <v>Diurno</v>
       </c>
       <c r="D78" t="str">
-        <v>Registro de escala</v>
+        <v>Valoración de riesgo</v>
       </c>
       <c r="E78" t="str">
-        <v>No aplica</v>
-      </c>
-      <c r="F78">
-        <v>11</v>
+        <v>SI</v>
+      </c>
+      <c r="F78" t="str">
+        <v>Medio</v>
       </c>
       <c r="G78" t="str">
         <v>PAC-1076</v>
@@ -2198,7 +2198,7 @@
         <v>2026-02-15</v>
       </c>
       <c r="B79" t="str">
-        <v>Medicina</v>
+        <v>Cirugía</v>
       </c>
       <c r="C79" t="str">
         <v>Nocturno</v>
@@ -2221,19 +2221,19 @@
         <v>2026-03-15</v>
       </c>
       <c r="B80" t="str">
-        <v>Medicina</v>
+        <v>Urgencia</v>
       </c>
       <c r="C80" t="str">
-        <v>Diurno</v>
+        <v>Nocturno</v>
       </c>
       <c r="D80" t="str">
-        <v>Uso de superficie</v>
+        <v>Valoración de riesgo</v>
       </c>
       <c r="E80" t="str">
-        <v>Cumple</v>
+        <v>1</v>
       </c>
       <c r="F80">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="G80" t="str">
         <v>PAC-1078</v>
@@ -2244,19 +2244,19 @@
         <v>2026-04-15</v>
       </c>
       <c r="B81" t="str">
-        <v>Urgencia</v>
+        <v>Medicina</v>
       </c>
       <c r="C81" t="str">
-        <v>Nocturno</v>
+        <v>Diurno</v>
       </c>
       <c r="D81" t="str">
-        <v>Valoración de riesgo</v>
+        <v>Uso de superficie</v>
       </c>
       <c r="E81" t="str">
         <v>Sí</v>
       </c>
-      <c r="F81" t="str">
-        <v>Alto</v>
+      <c r="F81">
+        <v>11</v>
       </c>
       <c r="G81" t="str">
         <v>PAC-1079</v>
@@ -2267,16 +2267,16 @@
         <v>2026-01-15</v>
       </c>
       <c r="B82" t="str">
-        <v>UCI</v>
+        <v>Medicina</v>
       </c>
       <c r="C82" t="str">
-        <v>Nocturno</v>
+        <v>Diurno</v>
       </c>
       <c r="D82" t="str">
-        <v>Registro de escala</v>
+        <v>Uso de superficie</v>
       </c>
       <c r="E82" t="str">
-        <v>1</v>
+        <v>No cumple</v>
       </c>
       <c r="F82" t="str">
         <v>Bajo</v>
@@ -2290,19 +2290,19 @@
         <v>2026-02-15</v>
       </c>
       <c r="B83" t="str">
-        <v>UCI</v>
+        <v>Urgencia</v>
       </c>
       <c r="C83" t="str">
-        <v>Diurno</v>
+        <v>Nocturno</v>
       </c>
       <c r="D83" t="str">
-        <v>Uso de superficie</v>
+        <v>Valoración de riesgo</v>
       </c>
       <c r="E83" t="str">
-        <v>Cumple</v>
-      </c>
-      <c r="F83">
-        <v>20</v>
+        <v>No</v>
+      </c>
+      <c r="F83" t="str">
+        <v>Medio</v>
       </c>
       <c r="G83" t="str">
         <v>PAC-1081</v>
@@ -2313,13 +2313,13 @@
         <v>2026-03-15</v>
       </c>
       <c r="B84" t="str">
-        <v>Cirugía</v>
+        <v>Urgencia</v>
       </c>
       <c r="C84" t="str">
         <v>Diurno</v>
       </c>
       <c r="D84" t="str">
-        <v>Valoración de riesgo</v>
+        <v>Registro de escala</v>
       </c>
       <c r="E84" t="str">
         <v>1</v>
@@ -2336,19 +2336,19 @@
         <v>2026-04-15</v>
       </c>
       <c r="B85" t="str">
-        <v>Cirugía</v>
+        <v>Urgencia</v>
       </c>
       <c r="C85" t="str">
         <v>Diurno</v>
       </c>
       <c r="D85" t="str">
-        <v>Uso de superficie</v>
+        <v>Valoración de riesgo</v>
       </c>
       <c r="E85" t="str">
-        <v>SI</v>
-      </c>
-      <c r="F85" t="str">
-        <v>Medio</v>
+        <v>No cumple</v>
+      </c>
+      <c r="F85">
+        <v>20</v>
       </c>
       <c r="G85" t="str">
         <v>PAC-1083</v>
@@ -2359,7 +2359,7 @@
         <v>2026-01-15</v>
       </c>
       <c r="B86" t="str">
-        <v>Cirugía</v>
+        <v>UCI</v>
       </c>
       <c r="C86" t="str">
         <v>Diurno</v>
@@ -2368,10 +2368,10 @@
         <v>Registro de escala</v>
       </c>
       <c r="E86" t="str">
-        <v>N/A</v>
-      </c>
-      <c r="F86" t="str">
-        <v>Bajo</v>
+        <v>SI</v>
+      </c>
+      <c r="F86">
+        <v>11</v>
       </c>
       <c r="G86" t="str">
         <v>PAC-1084</v>
@@ -2382,16 +2382,16 @@
         <v>2026-02-15</v>
       </c>
       <c r="B87" t="str">
-        <v>Medicina</v>
+        <v>Urgencia</v>
       </c>
       <c r="C87" t="str">
         <v>Nocturno</v>
       </c>
       <c r="D87" t="str">
-        <v>Registro de escala</v>
+        <v>Uso de superficie</v>
       </c>
       <c r="E87" t="str">
-        <v>Sí</v>
+        <v>1</v>
       </c>
       <c r="F87">
         <v>11</v>
@@ -2405,19 +2405,19 @@
         <v>2026-03-15</v>
       </c>
       <c r="B88" t="str">
-        <v>Urgencia</v>
+        <v>Medicina</v>
       </c>
       <c r="C88" t="str">
-        <v>Diurno</v>
+        <v>Nocturno</v>
       </c>
       <c r="D88" t="str">
         <v>Registro de escala</v>
       </c>
       <c r="E88" t="str">
-        <v>SI</v>
-      </c>
-      <c r="F88" t="str">
-        <v>Medio</v>
+        <v>Cumple</v>
+      </c>
+      <c r="F88">
+        <v>11</v>
       </c>
       <c r="G88" t="str">
         <v>PAC-1086</v>
@@ -2428,19 +2428,19 @@
         <v>2026-04-15</v>
       </c>
       <c r="B89" t="str">
-        <v>UCI</v>
+        <v>Medicina</v>
       </c>
       <c r="C89" t="str">
-        <v>Diurno</v>
+        <v>Nocturno</v>
       </c>
       <c r="D89" t="str">
-        <v>Cambio de posición</v>
+        <v>Registro de escala</v>
       </c>
       <c r="E89" t="str">
-        <v>1</v>
+        <v>No aplica</v>
       </c>
       <c r="F89">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="G89" t="str">
         <v>PAC-1087</v>
@@ -2451,16 +2451,16 @@
         <v>2026-01-15</v>
       </c>
       <c r="B90" t="str">
-        <v>UCI</v>
+        <v>Urgencia</v>
       </c>
       <c r="C90" t="str">
-        <v>Diurno</v>
+        <v>Nocturno</v>
       </c>
       <c r="D90" t="str">
         <v>Valoración de riesgo</v>
       </c>
       <c r="E90" t="str">
-        <v>SI</v>
+        <v>1</v>
       </c>
       <c r="F90" t="str">
         <v>Bajo</v>
@@ -2474,7 +2474,7 @@
         <v>2026-02-15</v>
       </c>
       <c r="B91" t="str">
-        <v>Medicina</v>
+        <v>Urgencia</v>
       </c>
       <c r="C91" t="str">
         <v>Diurno</v>
@@ -2483,7 +2483,7 @@
         <v>Valoración de riesgo</v>
       </c>
       <c r="E91" t="str">
-        <v>SI</v>
+        <v>Sí</v>
       </c>
       <c r="F91" t="str">
         <v>Medio</v>
@@ -2497,19 +2497,19 @@
         <v>2026-03-15</v>
       </c>
       <c r="B92" t="str">
-        <v>Urgencia</v>
+        <v>Medicina</v>
       </c>
       <c r="C92" t="str">
         <v>Diurno</v>
       </c>
       <c r="D92" t="str">
-        <v>Uso de superficie</v>
+        <v>Registro de escala</v>
       </c>
       <c r="E92" t="str">
-        <v>Cumple</v>
+        <v>SI</v>
       </c>
       <c r="F92" t="str">
-        <v>Medio</v>
+        <v>Alto</v>
       </c>
       <c r="G92" t="str">
         <v>PAC-1090</v>
@@ -2520,19 +2520,19 @@
         <v>2026-04-15</v>
       </c>
       <c r="B93" t="str">
-        <v>UCI</v>
+        <v>Cirugía</v>
       </c>
       <c r="C93" t="str">
         <v>Nocturno</v>
       </c>
       <c r="D93" t="str">
-        <v>Uso de superficie</v>
+        <v>Cambio de posición</v>
       </c>
       <c r="E93" t="str">
-        <v>SI</v>
-      </c>
-      <c r="F93">
-        <v>11</v>
+        <v>No aplica</v>
+      </c>
+      <c r="F93" t="str">
+        <v>Alto</v>
       </c>
       <c r="G93" t="str">
         <v>PAC-1091</v>
@@ -2549,10 +2549,10 @@
         <v>Diurno</v>
       </c>
       <c r="D94" t="str">
-        <v>Valoración de riesgo</v>
+        <v>Cambio de posición</v>
       </c>
       <c r="E94" t="str">
-        <v>SI</v>
+        <v>Cumple</v>
       </c>
       <c r="F94" t="str">
         <v>Medio</v>
@@ -2566,19 +2566,19 @@
         <v>2026-02-15</v>
       </c>
       <c r="B95" t="str">
-        <v>Medicina</v>
+        <v>Cirugía</v>
       </c>
       <c r="C95" t="str">
         <v>Nocturno</v>
       </c>
       <c r="D95" t="str">
-        <v>Cambio de posición</v>
+        <v>Registro de escala</v>
       </c>
       <c r="E95" t="str">
-        <v>Cumple</v>
-      </c>
-      <c r="F95">
-        <v>11</v>
+        <v>SI</v>
+      </c>
+      <c r="F95" t="str">
+        <v>Bajo</v>
       </c>
       <c r="G95" t="str">
         <v>PAC-1093</v>
@@ -2595,10 +2595,10 @@
         <v>Nocturno</v>
       </c>
       <c r="D96" t="str">
-        <v>Valoración de riesgo</v>
+        <v>Cambio de posición</v>
       </c>
       <c r="E96" t="str">
-        <v>Sí</v>
+        <v>Cumple</v>
       </c>
       <c r="F96" t="str">
         <v>Medio</v>
@@ -2612,19 +2612,19 @@
         <v>2026-04-15</v>
       </c>
       <c r="B97" t="str">
-        <v>Medicina</v>
+        <v>Urgencia</v>
       </c>
       <c r="C97" t="str">
-        <v>Nocturno</v>
+        <v>Diurno</v>
       </c>
       <c r="D97" t="str">
         <v>Cambio de posición</v>
       </c>
       <c r="E97" t="str">
-        <v>SI</v>
-      </c>
-      <c r="F97">
-        <v>20</v>
+        <v>No cumple</v>
+      </c>
+      <c r="F97" t="str">
+        <v>Medio</v>
       </c>
       <c r="G97" t="str">
         <v>PAC-1095</v>
@@ -2635,7 +2635,7 @@
         <v>2026-01-15</v>
       </c>
       <c r="B98" t="str">
-        <v>Cirugía</v>
+        <v>UCI</v>
       </c>
       <c r="C98" t="str">
         <v>Nocturno</v>
@@ -2644,10 +2644,10 @@
         <v>Valoración de riesgo</v>
       </c>
       <c r="E98" t="str">
-        <v>NO</v>
-      </c>
-      <c r="F98" t="str">
-        <v>Bajo</v>
+        <v>SI</v>
+      </c>
+      <c r="F98">
+        <v>20</v>
       </c>
       <c r="G98" t="str">
         <v>PAC-1096</v>
@@ -2667,10 +2667,10 @@
         <v>Registro de escala</v>
       </c>
       <c r="E99" t="str">
-        <v>Sí</v>
-      </c>
-      <c r="F99" t="str">
-        <v>Medio</v>
+        <v>N/A</v>
+      </c>
+      <c r="F99">
+        <v>11</v>
       </c>
       <c r="G99" t="str">
         <v>PAC-1097</v>
@@ -2681,19 +2681,19 @@
         <v>2026-03-15</v>
       </c>
       <c r="B100" t="str">
-        <v>Urgencia</v>
+        <v>Medicina</v>
       </c>
       <c r="C100" t="str">
-        <v>Nocturno</v>
+        <v>Diurno</v>
       </c>
       <c r="D100" t="str">
-        <v>Valoración de riesgo</v>
+        <v>Registro de escala</v>
       </c>
       <c r="E100" t="str">
-        <v>1</v>
+        <v>No aplica</v>
       </c>
       <c r="F100" t="str">
-        <v>Bajo</v>
+        <v>Alto</v>
       </c>
       <c r="G100" t="str">
         <v>PAC-1098</v>
@@ -2704,19 +2704,19 @@
         <v>2026-04-15</v>
       </c>
       <c r="B101" t="str">
-        <v>Medicina</v>
+        <v>Urgencia</v>
       </c>
       <c r="C101" t="str">
-        <v>Nocturno</v>
+        <v>Diurno</v>
       </c>
       <c r="D101" t="str">
-        <v>Uso de superficie</v>
+        <v>Valoración de riesgo</v>
       </c>
       <c r="E101" t="str">
         <v>1</v>
       </c>
-      <c r="F101">
-        <v>11</v>
+      <c r="F101" t="str">
+        <v>Medio</v>
       </c>
       <c r="G101" t="str">
         <v>PAC-1099</v>
@@ -2727,7 +2727,7 @@
         <v>2026-01-15</v>
       </c>
       <c r="B102" t="str">
-        <v>Urgencia</v>
+        <v>Cirugía</v>
       </c>
       <c r="C102" t="str">
         <v>Diurno</v>
@@ -2736,7 +2736,7 @@
         <v>Registro de escala</v>
       </c>
       <c r="E102" t="str">
-        <v>N/A</v>
+        <v>Cumple</v>
       </c>
       <c r="F102" t="str">
         <v>Medio</v>
@@ -2750,16 +2750,16 @@
         <v>2026-02-15</v>
       </c>
       <c r="B103" t="str">
-        <v>UCI</v>
+        <v>Urgencia</v>
       </c>
       <c r="C103" t="str">
-        <v>Diurno</v>
+        <v>Nocturno</v>
       </c>
       <c r="D103" t="str">
         <v>Uso de superficie</v>
       </c>
       <c r="E103" t="str">
-        <v>Cumple</v>
+        <v>No aplica</v>
       </c>
       <c r="F103" t="str">
         <v>Alto</v>
@@ -2773,16 +2773,16 @@
         <v>2026-03-15</v>
       </c>
       <c r="B104" t="str">
-        <v>Cirugía</v>
+        <v>Urgencia</v>
       </c>
       <c r="C104" t="str">
-        <v>Nocturno</v>
+        <v>Diurno</v>
       </c>
       <c r="D104" t="str">
-        <v>Registro de escala</v>
+        <v>Cambio de posición</v>
       </c>
       <c r="E104" t="str">
-        <v>SI</v>
+        <v>Cumple</v>
       </c>
       <c r="F104" t="str">
         <v>Alto</v>
@@ -2796,16 +2796,16 @@
         <v>2026-04-15</v>
       </c>
       <c r="B105" t="str">
-        <v>UCI</v>
+        <v>Urgencia</v>
       </c>
       <c r="C105" t="str">
-        <v>Diurno</v>
+        <v>Nocturno</v>
       </c>
       <c r="D105" t="str">
-        <v>Registro de escala</v>
+        <v>Uso de superficie</v>
       </c>
       <c r="E105" t="str">
-        <v>1</v>
+        <v>Cumple</v>
       </c>
       <c r="F105" t="str">
         <v>Bajo</v>
@@ -2819,19 +2819,19 @@
         <v>2026-01-15</v>
       </c>
       <c r="B106" t="str">
-        <v>Urgencia</v>
+        <v>Cirugía</v>
       </c>
       <c r="C106" t="str">
         <v>Nocturno</v>
       </c>
       <c r="D106" t="str">
-        <v>Valoración de riesgo</v>
+        <v>Uso de superficie</v>
       </c>
       <c r="E106" t="str">
-        <v>0</v>
+        <v>SI</v>
       </c>
       <c r="F106">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="G106" t="str">
         <v>PAC-1104</v>
@@ -2842,16 +2842,16 @@
         <v>2026-02-15</v>
       </c>
       <c r="B107" t="str">
-        <v>Cirugía</v>
+        <v>Urgencia</v>
       </c>
       <c r="C107" t="str">
         <v>Nocturno</v>
       </c>
       <c r="D107" t="str">
-        <v>Registro de escala</v>
+        <v>Uso de superficie</v>
       </c>
       <c r="E107" t="str">
-        <v>No aplica</v>
+        <v>NO</v>
       </c>
       <c r="F107">
         <v>11</v>
@@ -2865,19 +2865,19 @@
         <v>2026-03-15</v>
       </c>
       <c r="B108" t="str">
-        <v>Cirugía</v>
+        <v>UCI</v>
       </c>
       <c r="C108" t="str">
-        <v>Diurno</v>
+        <v>Nocturno</v>
       </c>
       <c r="D108" t="str">
         <v>Registro de escala</v>
       </c>
       <c r="E108" t="str">
-        <v>No cumple</v>
-      </c>
-      <c r="F108" t="str">
-        <v>Bajo</v>
+        <v>0</v>
+      </c>
+      <c r="F108">
+        <v>20</v>
       </c>
       <c r="G108" t="str">
         <v>PAC-1106</v>
@@ -2894,10 +2894,10 @@
         <v>Diurno</v>
       </c>
       <c r="D109" t="str">
-        <v>Registro de escala</v>
+        <v>Uso de superficie</v>
       </c>
       <c r="E109" t="str">
-        <v>Sí</v>
+        <v>N/A</v>
       </c>
       <c r="F109">
         <v>20</v>
@@ -2911,19 +2911,19 @@
         <v>2026-01-15</v>
       </c>
       <c r="B110" t="str">
-        <v>Urgencia</v>
+        <v>UCI</v>
       </c>
       <c r="C110" t="str">
         <v>Nocturno</v>
       </c>
       <c r="D110" t="str">
-        <v>Uso de superficie</v>
+        <v>Registro de escala</v>
       </c>
       <c r="E110" t="str">
-        <v>No</v>
+        <v>Sí</v>
       </c>
       <c r="F110">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="G110" t="str">
         <v>PAC-1108</v>
@@ -2937,16 +2937,16 @@
         <v>Cirugía</v>
       </c>
       <c r="C111" t="str">
-        <v>Diurno</v>
+        <v>Nocturno</v>
       </c>
       <c r="D111" t="str">
-        <v>Cambio de posición</v>
+        <v>Uso de superficie</v>
       </c>
       <c r="E111" t="str">
-        <v>1</v>
+        <v>No</v>
       </c>
       <c r="F111" t="str">
-        <v>Bajo</v>
+        <v>Alto</v>
       </c>
       <c r="G111" t="str">
         <v>PAC-1109</v>
@@ -2957,19 +2957,19 @@
         <v>2026-03-15</v>
       </c>
       <c r="B112" t="str">
-        <v>UCI</v>
+        <v>Medicina</v>
       </c>
       <c r="C112" t="str">
-        <v>Diurno</v>
+        <v>Nocturno</v>
       </c>
       <c r="D112" t="str">
-        <v>Cambio de posición</v>
+        <v>Registro de escala</v>
       </c>
       <c r="E112" t="str">
-        <v>Cumple</v>
+        <v>1</v>
       </c>
       <c r="F112" t="str">
-        <v>Bajo</v>
+        <v>Medio</v>
       </c>
       <c r="G112" t="str">
         <v>PAC-1110</v>
@@ -2980,7 +2980,7 @@
         <v>2026-04-15</v>
       </c>
       <c r="B113" t="str">
-        <v>Cirugía</v>
+        <v>Urgencia</v>
       </c>
       <c r="C113" t="str">
         <v>Diurno</v>
@@ -2989,10 +2989,10 @@
         <v>Registro de escala</v>
       </c>
       <c r="E113" t="str">
-        <v>Cumple</v>
-      </c>
-      <c r="F113" t="str">
-        <v>Medio</v>
+        <v>NO</v>
+      </c>
+      <c r="F113">
+        <v>11</v>
       </c>
       <c r="G113" t="str">
         <v>PAC-1111</v>
@@ -3009,10 +3009,10 @@
         <v>Diurno</v>
       </c>
       <c r="D114" t="str">
-        <v>Registro de escala</v>
+        <v>Valoración de riesgo</v>
       </c>
       <c r="E114" t="str">
-        <v>Sí</v>
+        <v>No aplica</v>
       </c>
       <c r="F114">
         <v>20</v>
@@ -3026,19 +3026,19 @@
         <v>2026-02-15</v>
       </c>
       <c r="B115" t="str">
-        <v>Cirugía</v>
+        <v>Urgencia</v>
       </c>
       <c r="C115" t="str">
-        <v>Diurno</v>
+        <v>Nocturno</v>
       </c>
       <c r="D115" t="str">
-        <v>Valoración de riesgo</v>
+        <v>Uso de superficie</v>
       </c>
       <c r="E115" t="str">
         <v>Cumple</v>
       </c>
-      <c r="F115" t="str">
-        <v>Medio</v>
+      <c r="F115">
+        <v>11</v>
       </c>
       <c r="G115" t="str">
         <v>PAC-1113</v>
@@ -3049,7 +3049,7 @@
         <v>2026-03-15</v>
       </c>
       <c r="B116" t="str">
-        <v>Urgencia</v>
+        <v>Medicina</v>
       </c>
       <c r="C116" t="str">
         <v>Nocturno</v>
@@ -3058,10 +3058,10 @@
         <v>Valoración de riesgo</v>
       </c>
       <c r="E116" t="str">
-        <v>1</v>
+        <v>NO</v>
       </c>
       <c r="F116" t="str">
-        <v>Alto</v>
+        <v>Medio</v>
       </c>
       <c r="G116" t="str">
         <v>PAC-1114</v>
@@ -3072,19 +3072,19 @@
         <v>2026-04-15</v>
       </c>
       <c r="B117" t="str">
-        <v>Medicina</v>
+        <v>Urgencia</v>
       </c>
       <c r="C117" t="str">
         <v>Nocturno</v>
       </c>
       <c r="D117" t="str">
-        <v>Cambio de posición</v>
+        <v>Registro de escala</v>
       </c>
       <c r="E117" t="str">
-        <v>0</v>
-      </c>
-      <c r="F117" t="str">
-        <v>Alto</v>
+        <v>1</v>
+      </c>
+      <c r="F117">
+        <v>20</v>
       </c>
       <c r="G117" t="str">
         <v>PAC-1115</v>
@@ -3095,16 +3095,16 @@
         <v>2026-01-15</v>
       </c>
       <c r="B118" t="str">
-        <v>Cirugía</v>
+        <v>Urgencia</v>
       </c>
       <c r="C118" t="str">
-        <v>Diurno</v>
+        <v>Nocturno</v>
       </c>
       <c r="D118" t="str">
-        <v>Valoración de riesgo</v>
+        <v>Registro de escala</v>
       </c>
       <c r="E118" t="str">
-        <v>Cumple</v>
+        <v>SI</v>
       </c>
       <c r="F118" t="str">
         <v>Bajo</v>
@@ -3118,19 +3118,19 @@
         <v>2026-02-15</v>
       </c>
       <c r="B119" t="str">
-        <v>UCI</v>
+        <v>Medicina</v>
       </c>
       <c r="C119" t="str">
-        <v>Nocturno</v>
+        <v>Diurno</v>
       </c>
       <c r="D119" t="str">
-        <v>Cambio de posición</v>
+        <v>Registro de escala</v>
       </c>
       <c r="E119" t="str">
-        <v>1</v>
-      </c>
-      <c r="F119">
-        <v>11</v>
+        <v>Cumple</v>
+      </c>
+      <c r="F119" t="str">
+        <v>Medio</v>
       </c>
       <c r="G119" t="str">
         <v>PAC-1117</v>
@@ -3141,7 +3141,7 @@
         <v>2026-03-15</v>
       </c>
       <c r="B120" t="str">
-        <v>Cirugía</v>
+        <v>Urgencia</v>
       </c>
       <c r="C120" t="str">
         <v>Nocturno</v>
@@ -3150,10 +3150,10 @@
         <v>Uso de superficie</v>
       </c>
       <c r="E120" t="str">
-        <v>1</v>
-      </c>
-      <c r="F120" t="str">
-        <v>Alto</v>
+        <v>No cumple</v>
+      </c>
+      <c r="F120">
+        <v>11</v>
       </c>
       <c r="G120" t="str">
         <v>PAC-1118</v>
@@ -3170,13 +3170,13 @@
         <v>Nocturno</v>
       </c>
       <c r="D121" t="str">
-        <v>Uso de superficie</v>
+        <v>Valoración de riesgo</v>
       </c>
       <c r="E121" t="str">
-        <v>1</v>
-      </c>
-      <c r="F121">
-        <v>11</v>
+        <v>Cumple</v>
+      </c>
+      <c r="F121" t="str">
+        <v>Medio</v>
       </c>
       <c r="G121" t="str">
         <v>PAC-1119</v>
@@ -3187,19 +3187,19 @@
         <v>2026-01-15</v>
       </c>
       <c r="B122" t="str">
-        <v>Cirugía</v>
+        <v>UCI</v>
       </c>
       <c r="C122" t="str">
-        <v>Nocturno</v>
+        <v>Diurno</v>
       </c>
       <c r="D122" t="str">
-        <v>Valoración de riesgo</v>
+        <v>Cambio de posición</v>
       </c>
       <c r="E122" t="str">
-        <v>NO</v>
+        <v>Sí</v>
       </c>
       <c r="F122" t="str">
-        <v>Bajo</v>
+        <v>Alto</v>
       </c>
       <c r="G122" t="str">
         <v>PAC-1120</v>
@@ -3210,19 +3210,19 @@
         <v>2026-02-15</v>
       </c>
       <c r="B123" t="str">
-        <v>Cirugía</v>
+        <v>UCI</v>
       </c>
       <c r="C123" t="str">
         <v>Diurno</v>
       </c>
       <c r="D123" t="str">
-        <v>Valoración de riesgo</v>
+        <v>Uso de superficie</v>
       </c>
       <c r="E123" t="str">
-        <v>1</v>
+        <v>No</v>
       </c>
       <c r="F123" t="str">
-        <v>Bajo</v>
+        <v>Alto</v>
       </c>
       <c r="G123" t="str">
         <v>PAC-1121</v>
@@ -3233,19 +3233,19 @@
         <v>2026-03-15</v>
       </c>
       <c r="B124" t="str">
-        <v>Medicina</v>
+        <v>UCI</v>
       </c>
       <c r="C124" t="str">
-        <v>Nocturno</v>
+        <v>Diurno</v>
       </c>
       <c r="D124" t="str">
         <v>Cambio de posición</v>
       </c>
       <c r="E124" t="str">
-        <v>SI</v>
+        <v>N/A</v>
       </c>
       <c r="F124" t="str">
-        <v>Alto</v>
+        <v>Medio</v>
       </c>
       <c r="G124" t="str">
         <v>PAC-1122</v>
@@ -3256,16 +3256,16 @@
         <v>2026-04-15</v>
       </c>
       <c r="B125" t="str">
-        <v>UCI</v>
+        <v>Cirugía</v>
       </c>
       <c r="C125" t="str">
         <v>Diurno</v>
       </c>
       <c r="D125" t="str">
-        <v>Valoración de riesgo</v>
+        <v>Registro de escala</v>
       </c>
       <c r="E125" t="str">
-        <v>1</v>
+        <v>SI</v>
       </c>
       <c r="F125" t="str">
         <v>Medio</v>
@@ -3288,10 +3288,10 @@
         <v>Registro de escala</v>
       </c>
       <c r="E126" t="str">
-        <v>1</v>
+        <v>N/A</v>
       </c>
       <c r="F126" t="str">
-        <v>Medio</v>
+        <v>Alto</v>
       </c>
       <c r="G126" t="str">
         <v>PAC-1124</v>
@@ -3302,16 +3302,16 @@
         <v>2026-02-15</v>
       </c>
       <c r="B127" t="str">
-        <v>UCI</v>
+        <v>Medicina</v>
       </c>
       <c r="C127" t="str">
         <v>Diurno</v>
       </c>
       <c r="D127" t="str">
-        <v>Uso de superficie</v>
+        <v>Cambio de posición</v>
       </c>
       <c r="E127" t="str">
-        <v>0</v>
+        <v>SI</v>
       </c>
       <c r="F127" t="str">
         <v>Alto</v>
@@ -3325,7 +3325,7 @@
         <v>2026-03-15</v>
       </c>
       <c r="B128" t="str">
-        <v>Cirugía</v>
+        <v>Medicina</v>
       </c>
       <c r="C128" t="str">
         <v>Nocturno</v>
@@ -3334,10 +3334,10 @@
         <v>Cambio de posición</v>
       </c>
       <c r="E128" t="str">
-        <v>SI</v>
-      </c>
-      <c r="F128">
-        <v>11</v>
+        <v>Cumple</v>
+      </c>
+      <c r="F128" t="str">
+        <v>Alto</v>
       </c>
       <c r="G128" t="str">
         <v>PAC-1126</v>
@@ -3348,19 +3348,19 @@
         <v>2026-04-15</v>
       </c>
       <c r="B129" t="str">
-        <v>Medicina</v>
+        <v>Cirugía</v>
       </c>
       <c r="C129" t="str">
-        <v>Nocturno</v>
+        <v>Diurno</v>
       </c>
       <c r="D129" t="str">
-        <v>Valoración de riesgo</v>
+        <v>Registro de escala</v>
       </c>
       <c r="E129" t="str">
-        <v>No</v>
+        <v>SI</v>
       </c>
       <c r="F129" t="str">
-        <v>Bajo</v>
+        <v>Medio</v>
       </c>
       <c r="G129" t="str">
         <v>PAC-1127</v>
@@ -3374,16 +3374,16 @@
         <v>Cirugía</v>
       </c>
       <c r="C130" t="str">
-        <v>Nocturno</v>
+        <v>Diurno</v>
       </c>
       <c r="D130" t="str">
         <v>Valoración de riesgo</v>
       </c>
       <c r="E130" t="str">
-        <v>Sí</v>
+        <v>Cumple</v>
       </c>
       <c r="F130" t="str">
-        <v>Medio</v>
+        <v>Alto</v>
       </c>
       <c r="G130" t="str">
         <v>PAC-1128</v>
@@ -3394,19 +3394,19 @@
         <v>2026-02-15</v>
       </c>
       <c r="B131" t="str">
-        <v>Medicina</v>
+        <v>Urgencia</v>
       </c>
       <c r="C131" t="str">
         <v>Nocturno</v>
       </c>
       <c r="D131" t="str">
-        <v>Registro de escala</v>
+        <v>Valoración de riesgo</v>
       </c>
       <c r="E131" t="str">
-        <v>N/A</v>
-      </c>
-      <c r="F131" t="str">
-        <v>Medio</v>
+        <v>SI</v>
+      </c>
+      <c r="F131">
+        <v>20</v>
       </c>
       <c r="G131" t="str">
         <v>PAC-1129</v>
@@ -3423,13 +3423,13 @@
         <v>Nocturno</v>
       </c>
       <c r="D132" t="str">
-        <v>Valoración de riesgo</v>
+        <v>Cambio de posición</v>
       </c>
       <c r="E132" t="str">
-        <v>N/A</v>
+        <v>Cumple</v>
       </c>
       <c r="F132" t="str">
-        <v>Bajo</v>
+        <v>Alto</v>
       </c>
       <c r="G132" t="str">
         <v>PAC-1130</v>
@@ -3440,19 +3440,19 @@
         <v>2026-04-15</v>
       </c>
       <c r="B133" t="str">
-        <v>UCI</v>
+        <v>Medicina</v>
       </c>
       <c r="C133" t="str">
-        <v>Diurno</v>
+        <v>Nocturno</v>
       </c>
       <c r="D133" t="str">
-        <v>Cambio de posición</v>
+        <v>Uso de superficie</v>
       </c>
       <c r="E133" t="str">
-        <v>No aplica</v>
+        <v>Cumple</v>
       </c>
       <c r="F133">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="G133" t="str">
         <v>PAC-1131</v>
@@ -3463,19 +3463,19 @@
         <v>2026-01-15</v>
       </c>
       <c r="B134" t="str">
-        <v>Cirugía</v>
+        <v>Medicina</v>
       </c>
       <c r="C134" t="str">
-        <v>Diurno</v>
+        <v>Nocturno</v>
       </c>
       <c r="D134" t="str">
-        <v>Cambio de posición</v>
+        <v>Uso de superficie</v>
       </c>
       <c r="E134" t="str">
-        <v>No aplica</v>
+        <v>0</v>
       </c>
       <c r="F134">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="G134" t="str">
         <v>PAC-1132</v>
@@ -3489,16 +3489,16 @@
         <v>Urgencia</v>
       </c>
       <c r="C135" t="str">
-        <v>Diurno</v>
+        <v>Nocturno</v>
       </c>
       <c r="D135" t="str">
-        <v>Cambio de posición</v>
+        <v>Valoración de riesgo</v>
       </c>
       <c r="E135" t="str">
         <v>Sí</v>
       </c>
-      <c r="F135" t="str">
-        <v>Alto</v>
+      <c r="F135">
+        <v>11</v>
       </c>
       <c r="G135" t="str">
         <v>PAC-1133</v>
@@ -3509,19 +3509,19 @@
         <v>2026-03-15</v>
       </c>
       <c r="B136" t="str">
-        <v>UCI</v>
+        <v>Cirugía</v>
       </c>
       <c r="C136" t="str">
-        <v>Nocturno</v>
+        <v>Diurno</v>
       </c>
       <c r="D136" t="str">
         <v>Cambio de posición</v>
       </c>
       <c r="E136" t="str">
-        <v>N/A</v>
-      </c>
-      <c r="F136" t="str">
-        <v>Alto</v>
+        <v>Cumple</v>
+      </c>
+      <c r="F136">
+        <v>20</v>
       </c>
       <c r="G136" t="str">
         <v>PAC-1134</v>
@@ -3532,19 +3532,19 @@
         <v>2026-04-15</v>
       </c>
       <c r="B137" t="str">
-        <v>Medicina</v>
+        <v>Urgencia</v>
       </c>
       <c r="C137" t="str">
-        <v>Nocturno</v>
+        <v>Diurno</v>
       </c>
       <c r="D137" t="str">
-        <v>Cambio de posición</v>
+        <v>Uso de superficie</v>
       </c>
       <c r="E137" t="str">
-        <v>SI</v>
+        <v>Cumple</v>
       </c>
       <c r="F137" t="str">
-        <v>Medio</v>
+        <v>Bajo</v>
       </c>
       <c r="G137" t="str">
         <v>PAC-1135</v>
@@ -3555,19 +3555,19 @@
         <v>2026-01-15</v>
       </c>
       <c r="B138" t="str">
-        <v>Urgencia</v>
+        <v>Cirugía</v>
       </c>
       <c r="C138" t="str">
-        <v>Diurno</v>
+        <v>Nocturno</v>
       </c>
       <c r="D138" t="str">
-        <v>Cambio de posición</v>
+        <v>Registro de escala</v>
       </c>
       <c r="E138" t="str">
         <v>SI</v>
       </c>
       <c r="F138" t="str">
-        <v>Bajo</v>
+        <v>Medio</v>
       </c>
       <c r="G138" t="str">
         <v>PAC-1136</v>
@@ -3578,19 +3578,19 @@
         <v>2026-02-15</v>
       </c>
       <c r="B139" t="str">
-        <v>UCI</v>
+        <v>Urgencia</v>
       </c>
       <c r="C139" t="str">
         <v>Nocturno</v>
       </c>
       <c r="D139" t="str">
-        <v>Valoración de riesgo</v>
+        <v>Cambio de posición</v>
       </c>
       <c r="E139" t="str">
         <v>1</v>
       </c>
-      <c r="F139">
-        <v>11</v>
+      <c r="F139" t="str">
+        <v>Alto</v>
       </c>
       <c r="G139" t="str">
         <v>PAC-1137</v>
@@ -3601,19 +3601,19 @@
         <v>2026-03-15</v>
       </c>
       <c r="B140" t="str">
-        <v>Medicina</v>
+        <v>Urgencia</v>
       </c>
       <c r="C140" t="str">
-        <v>Diurno</v>
+        <v>Nocturno</v>
       </c>
       <c r="D140" t="str">
         <v>Valoración de riesgo</v>
       </c>
       <c r="E140" t="str">
-        <v>Cumple</v>
+        <v>NO</v>
       </c>
       <c r="F140" t="str">
-        <v>Bajo</v>
+        <v>Medio</v>
       </c>
       <c r="G140" t="str">
         <v>PAC-1138</v>
@@ -3624,19 +3624,19 @@
         <v>2026-04-15</v>
       </c>
       <c r="B141" t="str">
-        <v>Urgencia</v>
+        <v>Medicina</v>
       </c>
       <c r="C141" t="str">
         <v>Nocturno</v>
       </c>
       <c r="D141" t="str">
-        <v>Registro de escala</v>
+        <v>Uso de superficie</v>
       </c>
       <c r="E141" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F141">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="G141" t="str">
         <v>PAC-1139</v>
@@ -3647,16 +3647,16 @@
         <v>2026-01-15</v>
       </c>
       <c r="B142" t="str">
-        <v>UCI</v>
+        <v>Medicina</v>
       </c>
       <c r="C142" t="str">
         <v>Diurno</v>
       </c>
       <c r="D142" t="str">
-        <v>Cambio de posición</v>
+        <v>Uso de superficie</v>
       </c>
       <c r="E142" t="str">
-        <v>Cumple</v>
+        <v>Sí</v>
       </c>
       <c r="F142">
         <v>11</v>
@@ -3670,19 +3670,19 @@
         <v>2026-02-15</v>
       </c>
       <c r="B143" t="str">
-        <v>Medicina</v>
+        <v>Cirugía</v>
       </c>
       <c r="C143" t="str">
-        <v>Diurno</v>
+        <v>Nocturno</v>
       </c>
       <c r="D143" t="str">
-        <v>Registro de escala</v>
+        <v>Uso de superficie</v>
       </c>
       <c r="E143" t="str">
-        <v>Cumple</v>
-      </c>
-      <c r="F143">
-        <v>11</v>
+        <v>NO</v>
+      </c>
+      <c r="F143" t="str">
+        <v>Bajo</v>
       </c>
       <c r="G143" t="str">
         <v>PAC-1141</v>
@@ -3693,19 +3693,19 @@
         <v>2026-03-15</v>
       </c>
       <c r="B144" t="str">
-        <v>Cirugía</v>
+        <v>Medicina</v>
       </c>
       <c r="C144" t="str">
         <v>Nocturno</v>
       </c>
       <c r="D144" t="str">
-        <v>Cambio de posición</v>
+        <v>Uso de superficie</v>
       </c>
       <c r="E144" t="str">
         <v>Sí</v>
       </c>
-      <c r="F144">
-        <v>11</v>
+      <c r="F144" t="str">
+        <v>Alto</v>
       </c>
       <c r="G144" t="str">
         <v>PAC-1142</v>
@@ -3722,13 +3722,13 @@
         <v>Nocturno</v>
       </c>
       <c r="D145" t="str">
-        <v>Registro de escala</v>
+        <v>Cambio de posición</v>
       </c>
       <c r="E145" t="str">
         <v>1</v>
       </c>
-      <c r="F145">
-        <v>11</v>
+      <c r="F145" t="str">
+        <v>Medio</v>
       </c>
       <c r="G145" t="str">
         <v>PAC-1143</v>
@@ -3739,7 +3739,7 @@
         <v>2026-01-15</v>
       </c>
       <c r="B146" t="str">
-        <v>UCI</v>
+        <v>Medicina</v>
       </c>
       <c r="C146" t="str">
         <v>Nocturno</v>
@@ -3748,10 +3748,10 @@
         <v>Valoración de riesgo</v>
       </c>
       <c r="E146" t="str">
-        <v>0</v>
-      </c>
-      <c r="F146" t="str">
-        <v>Alto</v>
+        <v>Sí</v>
+      </c>
+      <c r="F146">
+        <v>20</v>
       </c>
       <c r="G146" t="str">
         <v>PAC-1144</v>
@@ -3762,19 +3762,19 @@
         <v>2026-02-15</v>
       </c>
       <c r="B147" t="str">
-        <v>Cirugía</v>
+        <v>Urgencia</v>
       </c>
       <c r="C147" t="str">
         <v>Nocturno</v>
       </c>
       <c r="D147" t="str">
-        <v>Valoración de riesgo</v>
+        <v>Registro de escala</v>
       </c>
       <c r="E147" t="str">
-        <v>Cumple</v>
-      </c>
-      <c r="F147" t="str">
-        <v>Bajo</v>
+        <v>N/A</v>
+      </c>
+      <c r="F147">
+        <v>20</v>
       </c>
       <c r="G147" t="str">
         <v>PAC-1145</v>
@@ -3794,10 +3794,10 @@
         <v>Cambio de posición</v>
       </c>
       <c r="E148" t="str">
-        <v>Sí</v>
+        <v>Cumple</v>
       </c>
       <c r="F148" t="str">
-        <v>Alto</v>
+        <v>Medio</v>
       </c>
       <c r="G148" t="str">
         <v>PAC-1146</v>
@@ -3808,19 +3808,19 @@
         <v>2026-04-15</v>
       </c>
       <c r="B149" t="str">
-        <v>Medicina</v>
+        <v>Urgencia</v>
       </c>
       <c r="C149" t="str">
-        <v>Nocturno</v>
+        <v>Diurno</v>
       </c>
       <c r="D149" t="str">
-        <v>Registro de escala</v>
+        <v>Valoración de riesgo</v>
       </c>
       <c r="E149" t="str">
-        <v>0</v>
-      </c>
-      <c r="F149">
-        <v>11</v>
+        <v>No</v>
+      </c>
+      <c r="F149" t="str">
+        <v>Bajo</v>
       </c>
       <c r="G149" t="str">
         <v>PAC-1147</v>
@@ -3831,19 +3831,19 @@
         <v>2026-01-15</v>
       </c>
       <c r="B150" t="str">
-        <v>UCI</v>
+        <v>Cirugía</v>
       </c>
       <c r="C150" t="str">
         <v>Nocturno</v>
       </c>
       <c r="D150" t="str">
-        <v>Cambio de posición</v>
+        <v>Registro de escala</v>
       </c>
       <c r="E150" t="str">
         <v>Sí</v>
       </c>
       <c r="F150" t="str">
-        <v>Medio</v>
+        <v>Alto</v>
       </c>
       <c r="G150" t="str">
         <v>PAC-1148</v>
@@ -3854,19 +3854,19 @@
         <v>2026-02-15</v>
       </c>
       <c r="B151" t="str">
-        <v>Cirugía</v>
+        <v>Medicina</v>
       </c>
       <c r="C151" t="str">
         <v>Diurno</v>
       </c>
       <c r="D151" t="str">
-        <v>Cambio de posición</v>
+        <v>Uso de superficie</v>
       </c>
       <c r="E151" t="str">
-        <v>1</v>
-      </c>
-      <c r="F151" t="str">
-        <v>Alto</v>
+        <v>Cumple</v>
+      </c>
+      <c r="F151">
+        <v>20</v>
       </c>
       <c r="G151" t="str">
         <v>PAC-1149</v>
@@ -3877,19 +3877,19 @@
         <v>2026-03-15</v>
       </c>
       <c r="B152" t="str">
-        <v>Medicina</v>
+        <v>Urgencia</v>
       </c>
       <c r="C152" t="str">
         <v>Diurno</v>
       </c>
       <c r="D152" t="str">
-        <v>Uso de superficie</v>
+        <v>Valoración de riesgo</v>
       </c>
       <c r="E152" t="str">
         <v>Sí</v>
       </c>
-      <c r="F152" t="str">
-        <v>Bajo</v>
+      <c r="F152">
+        <v>20</v>
       </c>
       <c r="G152" t="str">
         <v>PAC-1150</v>
@@ -3906,13 +3906,13 @@
         <v>Nocturno</v>
       </c>
       <c r="D153" t="str">
-        <v>Cambio de posición</v>
+        <v>Valoración de riesgo</v>
       </c>
       <c r="E153" t="str">
-        <v>1</v>
-      </c>
-      <c r="F153" t="str">
-        <v>Medio</v>
+        <v>Sí</v>
+      </c>
+      <c r="F153">
+        <v>20</v>
       </c>
       <c r="G153" t="str">
         <v>PAC-1151</v>
@@ -3923,19 +3923,19 @@
         <v>2026-01-15</v>
       </c>
       <c r="B154" t="str">
-        <v>Medicina</v>
+        <v>Cirugía</v>
       </c>
       <c r="C154" t="str">
         <v>Diurno</v>
       </c>
       <c r="D154" t="str">
-        <v>Registro de escala</v>
+        <v>Cambio de posición</v>
       </c>
       <c r="E154" t="str">
         <v>1</v>
       </c>
-      <c r="F154" t="str">
-        <v>Bajo</v>
+      <c r="F154">
+        <v>11</v>
       </c>
       <c r="G154" t="str">
         <v>PAC-1152</v>
@@ -3946,19 +3946,19 @@
         <v>2026-02-15</v>
       </c>
       <c r="B155" t="str">
-        <v>Urgencia</v>
+        <v>Medicina</v>
       </c>
       <c r="C155" t="str">
         <v>Nocturno</v>
       </c>
       <c r="D155" t="str">
-        <v>Uso de superficie</v>
+        <v>Valoración de riesgo</v>
       </c>
       <c r="E155" t="str">
-        <v>NO</v>
-      </c>
-      <c r="F155">
-        <v>20</v>
+        <v>No aplica</v>
+      </c>
+      <c r="F155" t="str">
+        <v>Medio</v>
       </c>
       <c r="G155" t="str">
         <v>PAC-1153</v>
@@ -3969,19 +3969,19 @@
         <v>2026-03-15</v>
       </c>
       <c r="B156" t="str">
-        <v>Urgencia</v>
+        <v>UCI</v>
       </c>
       <c r="C156" t="str">
-        <v>Nocturno</v>
+        <v>Diurno</v>
       </c>
       <c r="D156" t="str">
         <v>Registro de escala</v>
       </c>
       <c r="E156" t="str">
-        <v>SI</v>
-      </c>
-      <c r="F156" t="str">
-        <v>Bajo</v>
+        <v>Cumple</v>
+      </c>
+      <c r="F156">
+        <v>20</v>
       </c>
       <c r="G156" t="str">
         <v>PAC-1154</v>
@@ -3992,19 +3992,19 @@
         <v>2026-04-15</v>
       </c>
       <c r="B157" t="str">
-        <v>Cirugía</v>
+        <v>UCI</v>
       </c>
       <c r="C157" t="str">
         <v>Nocturno</v>
       </c>
       <c r="D157" t="str">
-        <v>Uso de superficie</v>
+        <v>Cambio de posición</v>
       </c>
       <c r="E157" t="str">
-        <v>SI</v>
-      </c>
-      <c r="F157" t="str">
-        <v>Medio</v>
+        <v>No</v>
+      </c>
+      <c r="F157">
+        <v>11</v>
       </c>
       <c r="G157" t="str">
         <v>PAC-1155</v>
@@ -4015,19 +4015,19 @@
         <v>2026-01-15</v>
       </c>
       <c r="B158" t="str">
-        <v>Urgencia</v>
+        <v>UCI</v>
       </c>
       <c r="C158" t="str">
         <v>Nocturno</v>
       </c>
       <c r="D158" t="str">
-        <v>Registro de escala</v>
+        <v>Uso de superficie</v>
       </c>
       <c r="E158" t="str">
-        <v>Cumple</v>
-      </c>
-      <c r="F158">
-        <v>20</v>
+        <v>1</v>
+      </c>
+      <c r="F158" t="str">
+        <v>Medio</v>
       </c>
       <c r="G158" t="str">
         <v>PAC-1156</v>
@@ -4038,19 +4038,19 @@
         <v>2026-02-15</v>
       </c>
       <c r="B159" t="str">
-        <v>Cirugía</v>
+        <v>Urgencia</v>
       </c>
       <c r="C159" t="str">
         <v>Diurno</v>
       </c>
       <c r="D159" t="str">
-        <v>Uso de superficie</v>
+        <v>Valoración de riesgo</v>
       </c>
       <c r="E159" t="str">
         <v>SI</v>
       </c>
       <c r="F159" t="str">
-        <v>Medio</v>
+        <v>Alto</v>
       </c>
       <c r="G159" t="str">
         <v>PAC-1157</v>
@@ -4067,13 +4067,13 @@
         <v>Nocturno</v>
       </c>
       <c r="D160" t="str">
-        <v>Valoración de riesgo</v>
+        <v>Registro de escala</v>
       </c>
       <c r="E160" t="str">
-        <v>No cumple</v>
+        <v>SI</v>
       </c>
       <c r="F160" t="str">
-        <v>Medio</v>
+        <v>Alto</v>
       </c>
       <c r="G160" t="str">
         <v>PAC-1158</v>
@@ -4096,7 +4096,7 @@
         <v>1</v>
       </c>
       <c r="F161" t="str">
-        <v>Medio</v>
+        <v>Bajo</v>
       </c>
       <c r="G161" t="str">
         <v>PAC-1159</v>

--- a/examples/auditoria-ejemplo.xlsx
+++ b/examples/auditoria-ejemplo.xlsx
@@ -427,16 +427,16 @@
         <v>2026-01-15</v>
       </c>
       <c r="B2" t="str">
-        <v>Urgencia</v>
+        <v>Cirugía</v>
       </c>
       <c r="C2" t="str">
         <v>Nocturno</v>
       </c>
       <c r="D2" t="str">
-        <v>Uso de superficie</v>
+        <v>Cambio de posición</v>
       </c>
       <c r="E2" t="str">
-        <v>SI</v>
+        <v>No cumple</v>
       </c>
       <c r="F2" t="str">
         <v>Medio</v>
@@ -450,19 +450,19 @@
         <v>2026-02-15</v>
       </c>
       <c r="B3" t="str">
-        <v>Cirugía</v>
+        <v>Urgencia</v>
       </c>
       <c r="C3" t="str">
-        <v>Nocturno</v>
+        <v>Diurno</v>
       </c>
       <c r="D3" t="str">
-        <v>Registro de escala</v>
+        <v>Valoración de riesgo</v>
       </c>
       <c r="E3" t="str">
-        <v>Cumple</v>
-      </c>
-      <c r="F3" t="str">
-        <v>Alto</v>
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <v>11</v>
       </c>
       <c r="G3" t="str">
         <v>PAC-1001</v>
@@ -473,19 +473,19 @@
         <v>2026-03-15</v>
       </c>
       <c r="B4" t="str">
-        <v>Medicina</v>
+        <v>Urgencia</v>
       </c>
       <c r="C4" t="str">
-        <v>Nocturno</v>
+        <v>Diurno</v>
       </c>
       <c r="D4" t="str">
-        <v>Valoración de riesgo</v>
+        <v>Uso de superficie</v>
       </c>
       <c r="E4" t="str">
-        <v>Cumple</v>
+        <v>No</v>
       </c>
       <c r="F4" t="str">
-        <v>Bajo</v>
+        <v>Alto</v>
       </c>
       <c r="G4" t="str">
         <v>PAC-1002</v>
@@ -502,13 +502,13 @@
         <v>Nocturno</v>
       </c>
       <c r="D5" t="str">
-        <v>Cambio de posición</v>
+        <v>Uso de superficie</v>
       </c>
       <c r="E5" t="str">
-        <v>Sí</v>
+        <v>1</v>
       </c>
       <c r="F5" t="str">
-        <v>Alto</v>
+        <v>Medio</v>
       </c>
       <c r="G5" t="str">
         <v>PAC-1003</v>
@@ -519,19 +519,19 @@
         <v>2026-01-15</v>
       </c>
       <c r="B6" t="str">
-        <v>Urgencia</v>
+        <v>UCI</v>
       </c>
       <c r="C6" t="str">
         <v>Diurno</v>
       </c>
       <c r="D6" t="str">
-        <v>Valoración de riesgo</v>
+        <v>Cambio de posición</v>
       </c>
       <c r="E6" t="str">
-        <v>1</v>
-      </c>
-      <c r="F6" t="str">
-        <v>Bajo</v>
+        <v>NO</v>
+      </c>
+      <c r="F6">
+        <v>20</v>
       </c>
       <c r="G6" t="str">
         <v>PAC-1004</v>
@@ -545,16 +545,16 @@
         <v>Urgencia</v>
       </c>
       <c r="C7" t="str">
-        <v>Diurno</v>
+        <v>Nocturno</v>
       </c>
       <c r="D7" t="str">
-        <v>Uso de superficie</v>
+        <v>Cambio de posición</v>
       </c>
       <c r="E7" t="str">
-        <v>N/A</v>
-      </c>
-      <c r="F7">
-        <v>11</v>
+        <v>Cumple</v>
+      </c>
+      <c r="F7" t="str">
+        <v>Alto</v>
       </c>
       <c r="G7" t="str">
         <v>PAC-1005</v>
@@ -565,19 +565,19 @@
         <v>2026-03-15</v>
       </c>
       <c r="B8" t="str">
-        <v>Urgencia</v>
+        <v>UCI</v>
       </c>
       <c r="C8" t="str">
-        <v>Diurno</v>
+        <v>Nocturno</v>
       </c>
       <c r="D8" t="str">
-        <v>Valoración de riesgo</v>
+        <v>Registro de escala</v>
       </c>
       <c r="E8" t="str">
-        <v>1</v>
+        <v>Sí</v>
       </c>
       <c r="F8" t="str">
-        <v>Medio</v>
+        <v>Bajo</v>
       </c>
       <c r="G8" t="str">
         <v>PAC-1006</v>
@@ -588,19 +588,19 @@
         <v>2026-04-15</v>
       </c>
       <c r="B9" t="str">
-        <v>Medicina</v>
+        <v>Urgencia</v>
       </c>
       <c r="C9" t="str">
         <v>Diurno</v>
       </c>
       <c r="D9" t="str">
-        <v>Cambio de posición</v>
+        <v>Registro de escala</v>
       </c>
       <c r="E9" t="str">
-        <v>SI</v>
+        <v>0</v>
       </c>
       <c r="F9" t="str">
-        <v>Alto</v>
+        <v>Bajo</v>
       </c>
       <c r="G9" t="str">
         <v>PAC-1007</v>
@@ -611,19 +611,19 @@
         <v>2026-01-15</v>
       </c>
       <c r="B10" t="str">
-        <v>Cirugía</v>
+        <v>UCI</v>
       </c>
       <c r="C10" t="str">
-        <v>Nocturno</v>
+        <v>Diurno</v>
       </c>
       <c r="D10" t="str">
-        <v>Registro de escala</v>
+        <v>Uso de superficie</v>
       </c>
       <c r="E10" t="str">
         <v>1</v>
       </c>
-      <c r="F10">
-        <v>20</v>
+      <c r="F10" t="str">
+        <v>Medio</v>
       </c>
       <c r="G10" t="str">
         <v>PAC-1008</v>
@@ -634,19 +634,19 @@
         <v>2026-02-15</v>
       </c>
       <c r="B11" t="str">
-        <v>Cirugía</v>
+        <v>Urgencia</v>
       </c>
       <c r="C11" t="str">
-        <v>Nocturno</v>
+        <v>Diurno</v>
       </c>
       <c r="D11" t="str">
         <v>Valoración de riesgo</v>
       </c>
       <c r="E11" t="str">
-        <v>Sí</v>
+        <v>Cumple</v>
       </c>
       <c r="F11" t="str">
-        <v>Medio</v>
+        <v>Alto</v>
       </c>
       <c r="G11" t="str">
         <v>PAC-1009</v>
@@ -663,13 +663,13 @@
         <v>Nocturno</v>
       </c>
       <c r="D12" t="str">
-        <v>Cambio de posición</v>
+        <v>Valoración de riesgo</v>
       </c>
       <c r="E12" t="str">
-        <v>Sí</v>
-      </c>
-      <c r="F12" t="str">
-        <v>Alto</v>
+        <v>1</v>
+      </c>
+      <c r="F12">
+        <v>20</v>
       </c>
       <c r="G12" t="str">
         <v>PAC-1010</v>
@@ -680,19 +680,19 @@
         <v>2026-04-15</v>
       </c>
       <c r="B13" t="str">
-        <v>Medicina</v>
+        <v>UCI</v>
       </c>
       <c r="C13" t="str">
-        <v>Diurno</v>
+        <v>Nocturno</v>
       </c>
       <c r="D13" t="str">
-        <v>Registro de escala</v>
+        <v>Cambio de posición</v>
       </c>
       <c r="E13" t="str">
         <v>Cumple</v>
       </c>
       <c r="F13" t="str">
-        <v>Medio</v>
+        <v>Alto</v>
       </c>
       <c r="G13" t="str">
         <v>PAC-1011</v>
@@ -703,16 +703,16 @@
         <v>2026-01-15</v>
       </c>
       <c r="B14" t="str">
-        <v>Medicina</v>
+        <v>Cirugía</v>
       </c>
       <c r="C14" t="str">
         <v>Diurno</v>
       </c>
       <c r="D14" t="str">
-        <v>Uso de superficie</v>
+        <v>Valoración de riesgo</v>
       </c>
       <c r="E14" t="str">
-        <v>SI</v>
+        <v>Cumple</v>
       </c>
       <c r="F14" t="str">
         <v>Alto</v>
@@ -726,16 +726,16 @@
         <v>2026-02-15</v>
       </c>
       <c r="B15" t="str">
-        <v>UCI</v>
+        <v>Urgencia</v>
       </c>
       <c r="C15" t="str">
-        <v>Nocturno</v>
+        <v>Diurno</v>
       </c>
       <c r="D15" t="str">
         <v>Cambio de posición</v>
       </c>
       <c r="E15" t="str">
-        <v>N/A</v>
+        <v>1</v>
       </c>
       <c r="F15" t="str">
         <v>Bajo</v>
@@ -752,16 +752,16 @@
         <v>Urgencia</v>
       </c>
       <c r="C16" t="str">
-        <v>Diurno</v>
+        <v>Nocturno</v>
       </c>
       <c r="D16" t="str">
-        <v>Registro de escala</v>
+        <v>Cambio de posición</v>
       </c>
       <c r="E16" t="str">
-        <v>0</v>
+        <v>Sí</v>
       </c>
       <c r="F16">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="G16" t="str">
         <v>PAC-1014</v>
@@ -772,19 +772,19 @@
         <v>2026-04-15</v>
       </c>
       <c r="B17" t="str">
-        <v>Cirugía</v>
+        <v>Medicina</v>
       </c>
       <c r="C17" t="str">
-        <v>Nocturno</v>
+        <v>Diurno</v>
       </c>
       <c r="D17" t="str">
         <v>Cambio de posición</v>
       </c>
       <c r="E17" t="str">
-        <v>SI</v>
+        <v>Cumple</v>
       </c>
       <c r="F17" t="str">
-        <v>Alto</v>
+        <v>Medio</v>
       </c>
       <c r="G17" t="str">
         <v>PAC-1015</v>
@@ -795,19 +795,19 @@
         <v>2026-01-15</v>
       </c>
       <c r="B18" t="str">
-        <v>Medicina</v>
+        <v>UCI</v>
       </c>
       <c r="C18" t="str">
         <v>Nocturno</v>
       </c>
       <c r="D18" t="str">
-        <v>Cambio de posición</v>
+        <v>Uso de superficie</v>
       </c>
       <c r="E18" t="str">
-        <v>SI</v>
-      </c>
-      <c r="F18">
-        <v>11</v>
+        <v>No cumple</v>
+      </c>
+      <c r="F18" t="str">
+        <v>Alto</v>
       </c>
       <c r="G18" t="str">
         <v>PAC-1016</v>
@@ -818,19 +818,19 @@
         <v>2026-02-15</v>
       </c>
       <c r="B19" t="str">
-        <v>UCI</v>
+        <v>Cirugía</v>
       </c>
       <c r="C19" t="str">
-        <v>Nocturno</v>
+        <v>Diurno</v>
       </c>
       <c r="D19" t="str">
-        <v>Registro de escala</v>
+        <v>Uso de superficie</v>
       </c>
       <c r="E19" t="str">
         <v>Cumple</v>
       </c>
       <c r="F19" t="str">
-        <v>Bajo</v>
+        <v>Medio</v>
       </c>
       <c r="G19" t="str">
         <v>PAC-1017</v>
@@ -841,19 +841,19 @@
         <v>2026-03-15</v>
       </c>
       <c r="B20" t="str">
-        <v>Cirugía</v>
+        <v>Urgencia</v>
       </c>
       <c r="C20" t="str">
         <v>Diurno</v>
       </c>
       <c r="D20" t="str">
-        <v>Cambio de posición</v>
+        <v>Uso de superficie</v>
       </c>
       <c r="E20" t="str">
-        <v>1</v>
+        <v>SI</v>
       </c>
       <c r="F20" t="str">
-        <v>Medio</v>
+        <v>Bajo</v>
       </c>
       <c r="G20" t="str">
         <v>PAC-1018</v>
@@ -864,19 +864,19 @@
         <v>2026-04-15</v>
       </c>
       <c r="B21" t="str">
-        <v>Medicina</v>
+        <v>Urgencia</v>
       </c>
       <c r="C21" t="str">
-        <v>Nocturno</v>
+        <v>Diurno</v>
       </c>
       <c r="D21" t="str">
-        <v>Cambio de posición</v>
+        <v>Valoración de riesgo</v>
       </c>
       <c r="E21" t="str">
-        <v>Cumple</v>
+        <v>NO</v>
       </c>
       <c r="F21" t="str">
-        <v>Alto</v>
+        <v>Medio</v>
       </c>
       <c r="G21" t="str">
         <v>PAC-1019</v>
@@ -887,19 +887,19 @@
         <v>2026-01-15</v>
       </c>
       <c r="B22" t="str">
-        <v>Cirugía</v>
+        <v>Medicina</v>
       </c>
       <c r="C22" t="str">
-        <v>Diurno</v>
+        <v>Nocturno</v>
       </c>
       <c r="D22" t="str">
-        <v>Registro de escala</v>
+        <v>Valoración de riesgo</v>
       </c>
       <c r="E22" t="str">
-        <v>Cumple</v>
-      </c>
-      <c r="F22" t="str">
-        <v>Bajo</v>
+        <v>NO</v>
+      </c>
+      <c r="F22">
+        <v>20</v>
       </c>
       <c r="G22" t="str">
         <v>PAC-1020</v>
@@ -910,13 +910,13 @@
         <v>2026-02-15</v>
       </c>
       <c r="B23" t="str">
-        <v>Urgencia</v>
+        <v>UCI</v>
       </c>
       <c r="C23" t="str">
         <v>Nocturno</v>
       </c>
       <c r="D23" t="str">
-        <v>Valoración de riesgo</v>
+        <v>Cambio de posición</v>
       </c>
       <c r="E23" t="str">
         <v>SI</v>
@@ -936,13 +936,13 @@
         <v>UCI</v>
       </c>
       <c r="C24" t="str">
-        <v>Diurno</v>
+        <v>Nocturno</v>
       </c>
       <c r="D24" t="str">
-        <v>Valoración de riesgo</v>
+        <v>Cambio de posición</v>
       </c>
       <c r="E24" t="str">
-        <v>Sí</v>
+        <v>No aplica</v>
       </c>
       <c r="F24" t="str">
         <v>Medio</v>
@@ -956,19 +956,19 @@
         <v>2026-04-15</v>
       </c>
       <c r="B25" t="str">
-        <v>Medicina</v>
+        <v>UCI</v>
       </c>
       <c r="C25" t="str">
         <v>Nocturno</v>
       </c>
       <c r="D25" t="str">
-        <v>Cambio de posición</v>
+        <v>Uso de superficie</v>
       </c>
       <c r="E25" t="str">
-        <v>Sí</v>
+        <v>1</v>
       </c>
       <c r="F25" t="str">
-        <v>Bajo</v>
+        <v>Medio</v>
       </c>
       <c r="G25" t="str">
         <v>PAC-1023</v>
@@ -985,10 +985,10 @@
         <v>Diurno</v>
       </c>
       <c r="D26" t="str">
-        <v>Cambio de posición</v>
+        <v>Valoración de riesgo</v>
       </c>
       <c r="E26" t="str">
-        <v>1</v>
+        <v>NO</v>
       </c>
       <c r="F26">
         <v>11</v>
@@ -1002,7 +1002,7 @@
         <v>2026-02-15</v>
       </c>
       <c r="B27" t="str">
-        <v>Urgencia</v>
+        <v>Medicina</v>
       </c>
       <c r="C27" t="str">
         <v>Diurno</v>
@@ -1011,10 +1011,10 @@
         <v>Cambio de posición</v>
       </c>
       <c r="E27" t="str">
-        <v>Cumple</v>
-      </c>
-      <c r="F27" t="str">
-        <v>Bajo</v>
+        <v>1</v>
+      </c>
+      <c r="F27">
+        <v>11</v>
       </c>
       <c r="G27" t="str">
         <v>PAC-1025</v>
@@ -1025,19 +1025,19 @@
         <v>2026-03-15</v>
       </c>
       <c r="B28" t="str">
-        <v>UCI</v>
+        <v>Urgencia</v>
       </c>
       <c r="C28" t="str">
-        <v>Diurno</v>
+        <v>Nocturno</v>
       </c>
       <c r="D28" t="str">
-        <v>Uso de superficie</v>
+        <v>Registro de escala</v>
       </c>
       <c r="E28" t="str">
-        <v>1</v>
-      </c>
-      <c r="F28">
-        <v>20</v>
+        <v>NO</v>
+      </c>
+      <c r="F28" t="str">
+        <v>Bajo</v>
       </c>
       <c r="G28" t="str">
         <v>PAC-1026</v>
@@ -1051,16 +1051,16 @@
         <v>Cirugía</v>
       </c>
       <c r="C29" t="str">
-        <v>Nocturno</v>
+        <v>Diurno</v>
       </c>
       <c r="D29" t="str">
         <v>Cambio de posición</v>
       </c>
       <c r="E29" t="str">
-        <v>Sí</v>
-      </c>
-      <c r="F29">
-        <v>11</v>
+        <v>1</v>
+      </c>
+      <c r="F29" t="str">
+        <v>Medio</v>
       </c>
       <c r="G29" t="str">
         <v>PAC-1027</v>
@@ -1071,7 +1071,7 @@
         <v>2026-01-15</v>
       </c>
       <c r="B30" t="str">
-        <v>Cirugía</v>
+        <v>Medicina</v>
       </c>
       <c r="C30" t="str">
         <v>Nocturno</v>
@@ -1080,10 +1080,10 @@
         <v>Valoración de riesgo</v>
       </c>
       <c r="E30" t="str">
-        <v>0</v>
+        <v>Cumple</v>
       </c>
       <c r="F30">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="G30" t="str">
         <v>PAC-1028</v>
@@ -1100,13 +1100,13 @@
         <v>Diurno</v>
       </c>
       <c r="D31" t="str">
-        <v>Uso de superficie</v>
+        <v>Valoración de riesgo</v>
       </c>
       <c r="E31" t="str">
-        <v>Sí</v>
+        <v>SI</v>
       </c>
       <c r="F31">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="G31" t="str">
         <v>PAC-1029</v>
@@ -1117,19 +1117,19 @@
         <v>2026-03-15</v>
       </c>
       <c r="B32" t="str">
-        <v>Urgencia</v>
+        <v>Medicina</v>
       </c>
       <c r="C32" t="str">
-        <v>Diurno</v>
+        <v>Nocturno</v>
       </c>
       <c r="D32" t="str">
-        <v>Uso de superficie</v>
+        <v>Registro de escala</v>
       </c>
       <c r="E32" t="str">
         <v>Cumple</v>
       </c>
-      <c r="F32" t="str">
-        <v>Medio</v>
+      <c r="F32">
+        <v>11</v>
       </c>
       <c r="G32" t="str">
         <v>PAC-1030</v>
@@ -1140,7 +1140,7 @@
         <v>2026-04-15</v>
       </c>
       <c r="B33" t="str">
-        <v>Urgencia</v>
+        <v>UCI</v>
       </c>
       <c r="C33" t="str">
         <v>Diurno</v>
@@ -1149,10 +1149,10 @@
         <v>Valoración de riesgo</v>
       </c>
       <c r="E33" t="str">
-        <v>NO</v>
-      </c>
-      <c r="F33" t="str">
-        <v>Alto</v>
+        <v>Sí</v>
+      </c>
+      <c r="F33">
+        <v>20</v>
       </c>
       <c r="G33" t="str">
         <v>PAC-1031</v>
@@ -1163,19 +1163,19 @@
         <v>2026-01-15</v>
       </c>
       <c r="B34" t="str">
-        <v>Urgencia</v>
+        <v>Cirugía</v>
       </c>
       <c r="C34" t="str">
         <v>Diurno</v>
       </c>
       <c r="D34" t="str">
-        <v>Cambio de posición</v>
+        <v>Valoración de riesgo</v>
       </c>
       <c r="E34" t="str">
-        <v>No</v>
+        <v>1</v>
       </c>
       <c r="F34">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="G34" t="str">
         <v>PAC-1032</v>
@@ -1186,16 +1186,16 @@
         <v>2026-02-15</v>
       </c>
       <c r="B35" t="str">
-        <v>UCI</v>
+        <v>Urgencia</v>
       </c>
       <c r="C35" t="str">
-        <v>Diurno</v>
+        <v>Nocturno</v>
       </c>
       <c r="D35" t="str">
-        <v>Uso de superficie</v>
+        <v>Cambio de posición</v>
       </c>
       <c r="E35" t="str">
-        <v>NO</v>
+        <v>Cumple</v>
       </c>
       <c r="F35" t="str">
         <v>Bajo</v>
@@ -1209,19 +1209,19 @@
         <v>2026-03-15</v>
       </c>
       <c r="B36" t="str">
-        <v>Urgencia</v>
+        <v>Cirugía</v>
       </c>
       <c r="C36" t="str">
-        <v>Diurno</v>
+        <v>Nocturno</v>
       </c>
       <c r="D36" t="str">
-        <v>Valoración de riesgo</v>
+        <v>Uso de superficie</v>
       </c>
       <c r="E36" t="str">
-        <v>Sí</v>
+        <v>No aplica</v>
       </c>
       <c r="F36" t="str">
-        <v>Bajo</v>
+        <v>Medio</v>
       </c>
       <c r="G36" t="str">
         <v>PAC-1034</v>
@@ -1232,16 +1232,16 @@
         <v>2026-04-15</v>
       </c>
       <c r="B37" t="str">
-        <v>Urgencia</v>
+        <v>Medicina</v>
       </c>
       <c r="C37" t="str">
         <v>Nocturno</v>
       </c>
       <c r="D37" t="str">
-        <v>Valoración de riesgo</v>
+        <v>Cambio de posición</v>
       </c>
       <c r="E37" t="str">
-        <v>NO</v>
+        <v>Cumple</v>
       </c>
       <c r="F37" t="str">
         <v>Medio</v>
@@ -1264,10 +1264,10 @@
         <v>Cambio de posición</v>
       </c>
       <c r="E38" t="str">
-        <v>No aplica</v>
-      </c>
-      <c r="F38" t="str">
-        <v>Medio</v>
+        <v>Cumple</v>
+      </c>
+      <c r="F38">
+        <v>11</v>
       </c>
       <c r="G38" t="str">
         <v>PAC-1036</v>
@@ -1278,19 +1278,19 @@
         <v>2026-02-15</v>
       </c>
       <c r="B39" t="str">
-        <v>Medicina</v>
+        <v>Cirugía</v>
       </c>
       <c r="C39" t="str">
-        <v>Nocturno</v>
+        <v>Diurno</v>
       </c>
       <c r="D39" t="str">
-        <v>Valoración de riesgo</v>
+        <v>Registro de escala</v>
       </c>
       <c r="E39" t="str">
         <v>1</v>
       </c>
-      <c r="F39" t="str">
-        <v>Bajo</v>
+      <c r="F39">
+        <v>20</v>
       </c>
       <c r="G39" t="str">
         <v>PAC-1037</v>
@@ -1301,19 +1301,19 @@
         <v>2026-03-15</v>
       </c>
       <c r="B40" t="str">
-        <v>Cirugía</v>
+        <v>Urgencia</v>
       </c>
       <c r="C40" t="str">
         <v>Diurno</v>
       </c>
       <c r="D40" t="str">
-        <v>Valoración de riesgo</v>
+        <v>Uso de superficie</v>
       </c>
       <c r="E40" t="str">
-        <v>Sí</v>
+        <v>No cumple</v>
       </c>
       <c r="F40" t="str">
-        <v>Bajo</v>
+        <v>Alto</v>
       </c>
       <c r="G40" t="str">
         <v>PAC-1038</v>
@@ -1324,16 +1324,16 @@
         <v>2026-04-15</v>
       </c>
       <c r="B41" t="str">
-        <v>Medicina</v>
+        <v>Urgencia</v>
       </c>
       <c r="C41" t="str">
         <v>Nocturno</v>
       </c>
       <c r="D41" t="str">
-        <v>Registro de escala</v>
+        <v>Valoración de riesgo</v>
       </c>
       <c r="E41" t="str">
-        <v>Sí</v>
+        <v>Cumple</v>
       </c>
       <c r="F41" t="str">
         <v>Bajo</v>
@@ -1347,16 +1347,16 @@
         <v>2026-01-15</v>
       </c>
       <c r="B42" t="str">
-        <v>Medicina</v>
+        <v>Urgencia</v>
       </c>
       <c r="C42" t="str">
         <v>Nocturno</v>
       </c>
       <c r="D42" t="str">
-        <v>Registro de escala</v>
+        <v>Uso de superficie</v>
       </c>
       <c r="E42" t="str">
-        <v>NO</v>
+        <v>0</v>
       </c>
       <c r="F42" t="str">
         <v>Alto</v>
@@ -1370,19 +1370,19 @@
         <v>2026-02-15</v>
       </c>
       <c r="B43" t="str">
-        <v>UCI</v>
+        <v>Cirugía</v>
       </c>
       <c r="C43" t="str">
         <v>Diurno</v>
       </c>
       <c r="D43" t="str">
-        <v>Valoración de riesgo</v>
+        <v>Cambio de posición</v>
       </c>
       <c r="E43" t="str">
-        <v>No aplica</v>
-      </c>
-      <c r="F43" t="str">
-        <v>Medio</v>
+        <v>1</v>
+      </c>
+      <c r="F43">
+        <v>20</v>
       </c>
       <c r="G43" t="str">
         <v>PAC-1041</v>
@@ -1393,19 +1393,19 @@
         <v>2026-03-15</v>
       </c>
       <c r="B44" t="str">
-        <v>Medicina</v>
+        <v>UCI</v>
       </c>
       <c r="C44" t="str">
         <v>Diurno</v>
       </c>
       <c r="D44" t="str">
-        <v>Uso de superficie</v>
+        <v>Registro de escala</v>
       </c>
       <c r="E44" t="str">
-        <v>NO</v>
+        <v>Cumple</v>
       </c>
       <c r="F44" t="str">
-        <v>Medio</v>
+        <v>Alto</v>
       </c>
       <c r="G44" t="str">
         <v>PAC-1042</v>
@@ -1422,7 +1422,7 @@
         <v>Diurno</v>
       </c>
       <c r="D45" t="str">
-        <v>Registro de escala</v>
+        <v>Cambio de posición</v>
       </c>
       <c r="E45" t="str">
         <v>1</v>
@@ -1442,13 +1442,13 @@
         <v>Medicina</v>
       </c>
       <c r="C46" t="str">
-        <v>Diurno</v>
+        <v>Nocturno</v>
       </c>
       <c r="D46" t="str">
         <v>Uso de superficie</v>
       </c>
       <c r="E46" t="str">
-        <v>1</v>
+        <v>SI</v>
       </c>
       <c r="F46" t="str">
         <v>Alto</v>
@@ -1462,19 +1462,19 @@
         <v>2026-02-15</v>
       </c>
       <c r="B47" t="str">
-        <v>Medicina</v>
+        <v>Cirugía</v>
       </c>
       <c r="C47" t="str">
-        <v>Nocturno</v>
+        <v>Diurno</v>
       </c>
       <c r="D47" t="str">
-        <v>Uso de superficie</v>
+        <v>Valoración de riesgo</v>
       </c>
       <c r="E47" t="str">
-        <v>Sí</v>
-      </c>
-      <c r="F47">
-        <v>20</v>
+        <v>NO</v>
+      </c>
+      <c r="F47" t="str">
+        <v>Bajo</v>
       </c>
       <c r="G47" t="str">
         <v>PAC-1045</v>
@@ -1485,19 +1485,19 @@
         <v>2026-03-15</v>
       </c>
       <c r="B48" t="str">
-        <v>Urgencia</v>
+        <v>Cirugía</v>
       </c>
       <c r="C48" t="str">
         <v>Diurno</v>
       </c>
       <c r="D48" t="str">
-        <v>Valoración de riesgo</v>
+        <v>Registro de escala</v>
       </c>
       <c r="E48" t="str">
-        <v>No aplica</v>
-      </c>
-      <c r="F48">
-        <v>11</v>
+        <v>NO</v>
+      </c>
+      <c r="F48" t="str">
+        <v>Alto</v>
       </c>
       <c r="G48" t="str">
         <v>PAC-1046</v>
@@ -1508,16 +1508,16 @@
         <v>2026-04-15</v>
       </c>
       <c r="B49" t="str">
-        <v>Cirugía</v>
+        <v>Urgencia</v>
       </c>
       <c r="C49" t="str">
-        <v>Diurno</v>
+        <v>Nocturno</v>
       </c>
       <c r="D49" t="str">
-        <v>Valoración de riesgo</v>
+        <v>Registro de escala</v>
       </c>
       <c r="E49" t="str">
-        <v>Sí</v>
+        <v>No cumple</v>
       </c>
       <c r="F49" t="str">
         <v>Alto</v>
@@ -1537,13 +1537,13 @@
         <v>Nocturno</v>
       </c>
       <c r="D50" t="str">
-        <v>Cambio de posición</v>
+        <v>Valoración de riesgo</v>
       </c>
       <c r="E50" t="str">
-        <v>Cumple</v>
-      </c>
-      <c r="F50" t="str">
-        <v>Medio</v>
+        <v>Sí</v>
+      </c>
+      <c r="F50">
+        <v>20</v>
       </c>
       <c r="G50" t="str">
         <v>PAC-1048</v>
@@ -1554,19 +1554,19 @@
         <v>2026-02-15</v>
       </c>
       <c r="B51" t="str">
-        <v>UCI</v>
+        <v>Urgencia</v>
       </c>
       <c r="C51" t="str">
-        <v>Nocturno</v>
+        <v>Diurno</v>
       </c>
       <c r="D51" t="str">
-        <v>Uso de superficie</v>
+        <v>Valoración de riesgo</v>
       </c>
       <c r="E51" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F51" t="str">
-        <v>Alto</v>
+        <v>Bajo</v>
       </c>
       <c r="G51" t="str">
         <v>PAC-1049</v>
@@ -1580,13 +1580,13 @@
         <v>Urgencia</v>
       </c>
       <c r="C52" t="str">
-        <v>Nocturno</v>
+        <v>Diurno</v>
       </c>
       <c r="D52" t="str">
-        <v>Valoración de riesgo</v>
+        <v>Cambio de posición</v>
       </c>
       <c r="E52" t="str">
-        <v>0</v>
+        <v>Sí</v>
       </c>
       <c r="F52">
         <v>11</v>
@@ -1600,16 +1600,16 @@
         <v>2026-04-15</v>
       </c>
       <c r="B53" t="str">
-        <v>Urgencia</v>
+        <v>Cirugía</v>
       </c>
       <c r="C53" t="str">
-        <v>Diurno</v>
+        <v>Nocturno</v>
       </c>
       <c r="D53" t="str">
-        <v>Cambio de posición</v>
+        <v>Uso de superficie</v>
       </c>
       <c r="E53" t="str">
-        <v>Cumple</v>
+        <v>1</v>
       </c>
       <c r="F53">
         <v>20</v>
@@ -1623,16 +1623,16 @@
         <v>2026-01-15</v>
       </c>
       <c r="B54" t="str">
-        <v>Urgencia</v>
+        <v>Medicina</v>
       </c>
       <c r="C54" t="str">
         <v>Nocturno</v>
       </c>
       <c r="D54" t="str">
-        <v>Cambio de posición</v>
+        <v>Valoración de riesgo</v>
       </c>
       <c r="E54" t="str">
-        <v>N/A</v>
+        <v>Sí</v>
       </c>
       <c r="F54" t="str">
         <v>Alto</v>
@@ -1646,19 +1646,19 @@
         <v>2026-02-15</v>
       </c>
       <c r="B55" t="str">
-        <v>Cirugía</v>
+        <v>Medicina</v>
       </c>
       <c r="C55" t="str">
-        <v>Nocturno</v>
+        <v>Diurno</v>
       </c>
       <c r="D55" t="str">
-        <v>Valoración de riesgo</v>
+        <v>Uso de superficie</v>
       </c>
       <c r="E55" t="str">
-        <v>No</v>
-      </c>
-      <c r="F55">
-        <v>11</v>
+        <v>1</v>
+      </c>
+      <c r="F55" t="str">
+        <v>Bajo</v>
       </c>
       <c r="G55" t="str">
         <v>PAC-1053</v>
@@ -1669,19 +1669,19 @@
         <v>2026-03-15</v>
       </c>
       <c r="B56" t="str">
-        <v>UCI</v>
+        <v>Medicina</v>
       </c>
       <c r="C56" t="str">
         <v>Nocturno</v>
       </c>
       <c r="D56" t="str">
-        <v>Uso de superficie</v>
+        <v>Registro de escala</v>
       </c>
       <c r="E56" t="str">
-        <v>N/A</v>
+        <v>1</v>
       </c>
       <c r="F56">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="G56" t="str">
         <v>PAC-1054</v>
@@ -1695,16 +1695,16 @@
         <v>UCI</v>
       </c>
       <c r="C57" t="str">
-        <v>Diurno</v>
+        <v>Nocturno</v>
       </c>
       <c r="D57" t="str">
-        <v>Valoración de riesgo</v>
+        <v>Cambio de posición</v>
       </c>
       <c r="E57" t="str">
-        <v>Cumple</v>
-      </c>
-      <c r="F57" t="str">
-        <v>Medio</v>
+        <v>0</v>
+      </c>
+      <c r="F57">
+        <v>11</v>
       </c>
       <c r="G57" t="str">
         <v>PAC-1055</v>
@@ -1715,19 +1715,19 @@
         <v>2026-01-15</v>
       </c>
       <c r="B58" t="str">
-        <v>Urgencia</v>
+        <v>Cirugía</v>
       </c>
       <c r="C58" t="str">
         <v>Diurno</v>
       </c>
       <c r="D58" t="str">
-        <v>Registro de escala</v>
+        <v>Valoración de riesgo</v>
       </c>
       <c r="E58" t="str">
-        <v>SI</v>
-      </c>
-      <c r="F58">
-        <v>20</v>
+        <v>No aplica</v>
+      </c>
+      <c r="F58" t="str">
+        <v>Bajo</v>
       </c>
       <c r="G58" t="str">
         <v>PAC-1056</v>
@@ -1738,19 +1738,19 @@
         <v>2026-02-15</v>
       </c>
       <c r="B59" t="str">
-        <v>Medicina</v>
+        <v>Urgencia</v>
       </c>
       <c r="C59" t="str">
         <v>Nocturno</v>
       </c>
       <c r="D59" t="str">
-        <v>Uso de superficie</v>
+        <v>Valoración de riesgo</v>
       </c>
       <c r="E59" t="str">
-        <v>SI</v>
+        <v>No</v>
       </c>
       <c r="F59" t="str">
-        <v>Bajo</v>
+        <v>Alto</v>
       </c>
       <c r="G59" t="str">
         <v>PAC-1057</v>
@@ -1767,13 +1767,13 @@
         <v>Diurno</v>
       </c>
       <c r="D60" t="str">
-        <v>Valoración de riesgo</v>
+        <v>Uso de superficie</v>
       </c>
       <c r="E60" t="str">
-        <v>N/A</v>
+        <v>1</v>
       </c>
       <c r="F60" t="str">
-        <v>Alto</v>
+        <v>Bajo</v>
       </c>
       <c r="G60" t="str">
         <v>PAC-1058</v>
@@ -1784,19 +1784,19 @@
         <v>2026-04-15</v>
       </c>
       <c r="B61" t="str">
-        <v>Medicina</v>
+        <v>UCI</v>
       </c>
       <c r="C61" t="str">
-        <v>Diurno</v>
+        <v>Nocturno</v>
       </c>
       <c r="D61" t="str">
-        <v>Registro de escala</v>
+        <v>Uso de superficie</v>
       </c>
       <c r="E61" t="str">
-        <v>No</v>
+        <v>No aplica</v>
       </c>
       <c r="F61" t="str">
-        <v>Medio</v>
+        <v>Alto</v>
       </c>
       <c r="G61" t="str">
         <v>PAC-1059</v>
@@ -1807,16 +1807,16 @@
         <v>2026-01-15</v>
       </c>
       <c r="B62" t="str">
-        <v>UCI</v>
+        <v>Medicina</v>
       </c>
       <c r="C62" t="str">
-        <v>Nocturno</v>
+        <v>Diurno</v>
       </c>
       <c r="D62" t="str">
         <v>Uso de superficie</v>
       </c>
       <c r="E62" t="str">
-        <v>Sí</v>
+        <v>No cumple</v>
       </c>
       <c r="F62">
         <v>20</v>
@@ -1830,19 +1830,19 @@
         <v>2026-02-15</v>
       </c>
       <c r="B63" t="str">
-        <v>Cirugía</v>
+        <v>Urgencia</v>
       </c>
       <c r="C63" t="str">
-        <v>Diurno</v>
+        <v>Nocturno</v>
       </c>
       <c r="D63" t="str">
         <v>Cambio de posición</v>
       </c>
       <c r="E63" t="str">
-        <v>No</v>
+        <v>Sí</v>
       </c>
       <c r="F63" t="str">
-        <v>Medio</v>
+        <v>Alto</v>
       </c>
       <c r="G63" t="str">
         <v>PAC-1061</v>
@@ -1853,7 +1853,7 @@
         <v>2026-03-15</v>
       </c>
       <c r="B64" t="str">
-        <v>UCI</v>
+        <v>Medicina</v>
       </c>
       <c r="C64" t="str">
         <v>Nocturno</v>
@@ -1862,10 +1862,10 @@
         <v>Registro de escala</v>
       </c>
       <c r="E64" t="str">
-        <v>Cumple</v>
-      </c>
-      <c r="F64">
-        <v>11</v>
+        <v>Sí</v>
+      </c>
+      <c r="F64" t="str">
+        <v>Bajo</v>
       </c>
       <c r="G64" t="str">
         <v>PAC-1062</v>
@@ -1876,13 +1876,13 @@
         <v>2026-04-15</v>
       </c>
       <c r="B65" t="str">
-        <v>Urgencia</v>
+        <v>Medicina</v>
       </c>
       <c r="C65" t="str">
-        <v>Nocturno</v>
+        <v>Diurno</v>
       </c>
       <c r="D65" t="str">
-        <v>Cambio de posición</v>
+        <v>Valoración de riesgo</v>
       </c>
       <c r="E65" t="str">
         <v>No</v>
@@ -1899,19 +1899,19 @@
         <v>2026-01-15</v>
       </c>
       <c r="B66" t="str">
-        <v>Urgencia</v>
+        <v>Medicina</v>
       </c>
       <c r="C66" t="str">
-        <v>Diurno</v>
+        <v>Nocturno</v>
       </c>
       <c r="D66" t="str">
-        <v>Cambio de posición</v>
+        <v>Uso de superficie</v>
       </c>
       <c r="E66" t="str">
-        <v>1</v>
-      </c>
-      <c r="F66">
-        <v>11</v>
+        <v>SI</v>
+      </c>
+      <c r="F66" t="str">
+        <v>Medio</v>
       </c>
       <c r="G66" t="str">
         <v>PAC-1064</v>
@@ -1922,19 +1922,19 @@
         <v>2026-02-15</v>
       </c>
       <c r="B67" t="str">
-        <v>UCI</v>
+        <v>Urgencia</v>
       </c>
       <c r="C67" t="str">
-        <v>Diurno</v>
+        <v>Nocturno</v>
       </c>
       <c r="D67" t="str">
-        <v>Valoración de riesgo</v>
+        <v>Registro de escala</v>
       </c>
       <c r="E67" t="str">
-        <v>Sí</v>
+        <v>Cumple</v>
       </c>
       <c r="F67" t="str">
-        <v>Alto</v>
+        <v>Medio</v>
       </c>
       <c r="G67" t="str">
         <v>PAC-1065</v>
@@ -1945,19 +1945,19 @@
         <v>2026-03-15</v>
       </c>
       <c r="B68" t="str">
-        <v>Urgencia</v>
+        <v>Medicina</v>
       </c>
       <c r="C68" t="str">
         <v>Diurno</v>
       </c>
       <c r="D68" t="str">
-        <v>Registro de escala</v>
+        <v>Valoración de riesgo</v>
       </c>
       <c r="E68" t="str">
-        <v>Sí</v>
-      </c>
-      <c r="F68">
-        <v>20</v>
+        <v>1</v>
+      </c>
+      <c r="F68" t="str">
+        <v>Bajo</v>
       </c>
       <c r="G68" t="str">
         <v>PAC-1066</v>
@@ -1968,19 +1968,19 @@
         <v>2026-04-15</v>
       </c>
       <c r="B69" t="str">
-        <v>Medicina</v>
+        <v>Urgencia</v>
       </c>
       <c r="C69" t="str">
         <v>Nocturno</v>
       </c>
       <c r="D69" t="str">
-        <v>Cambio de posición</v>
+        <v>Valoración de riesgo</v>
       </c>
       <c r="E69" t="str">
-        <v>Sí</v>
-      </c>
-      <c r="F69" t="str">
-        <v>Alto</v>
+        <v>Cumple</v>
+      </c>
+      <c r="F69">
+        <v>20</v>
       </c>
       <c r="G69" t="str">
         <v>PAC-1067</v>
@@ -1991,19 +1991,19 @@
         <v>2026-01-15</v>
       </c>
       <c r="B70" t="str">
-        <v>Medicina</v>
+        <v>Cirugía</v>
       </c>
       <c r="C70" t="str">
-        <v>Diurno</v>
+        <v>Nocturno</v>
       </c>
       <c r="D70" t="str">
-        <v>Valoración de riesgo</v>
+        <v>Registro de escala</v>
       </c>
       <c r="E70" t="str">
-        <v>Cumple</v>
-      </c>
-      <c r="F70">
-        <v>11</v>
+        <v>1</v>
+      </c>
+      <c r="F70" t="str">
+        <v>Alto</v>
       </c>
       <c r="G70" t="str">
         <v>PAC-1068</v>
@@ -2014,19 +2014,19 @@
         <v>2026-02-15</v>
       </c>
       <c r="B71" t="str">
-        <v>Medicina</v>
+        <v>UCI</v>
       </c>
       <c r="C71" t="str">
-        <v>Diurno</v>
+        <v>Nocturno</v>
       </c>
       <c r="D71" t="str">
         <v>Cambio de posición</v>
       </c>
       <c r="E71" t="str">
-        <v>Cumple</v>
-      </c>
-      <c r="F71">
-        <v>20</v>
+        <v>No</v>
+      </c>
+      <c r="F71" t="str">
+        <v>Medio</v>
       </c>
       <c r="G71" t="str">
         <v>PAC-1069</v>
@@ -2037,19 +2037,19 @@
         <v>2026-03-15</v>
       </c>
       <c r="B72" t="str">
-        <v>Urgencia</v>
+        <v>Medicina</v>
       </c>
       <c r="C72" t="str">
         <v>Nocturno</v>
       </c>
       <c r="D72" t="str">
-        <v>Uso de superficie</v>
+        <v>Cambio de posición</v>
       </c>
       <c r="E72" t="str">
-        <v>Cumple</v>
-      </c>
-      <c r="F72">
-        <v>11</v>
+        <v>1</v>
+      </c>
+      <c r="F72" t="str">
+        <v>Bajo</v>
       </c>
       <c r="G72" t="str">
         <v>PAC-1070</v>
@@ -2060,19 +2060,19 @@
         <v>2026-04-15</v>
       </c>
       <c r="B73" t="str">
-        <v>UCI</v>
+        <v>Cirugía</v>
       </c>
       <c r="C73" t="str">
         <v>Diurno</v>
       </c>
       <c r="D73" t="str">
-        <v>Registro de escala</v>
+        <v>Cambio de posición</v>
       </c>
       <c r="E73" t="str">
         <v>1</v>
       </c>
-      <c r="F73">
-        <v>20</v>
+      <c r="F73" t="str">
+        <v>Medio</v>
       </c>
       <c r="G73" t="str">
         <v>PAC-1071</v>
@@ -2086,16 +2086,16 @@
         <v>Urgencia</v>
       </c>
       <c r="C74" t="str">
-        <v>Diurno</v>
+        <v>Nocturno</v>
       </c>
       <c r="D74" t="str">
-        <v>Valoración de riesgo</v>
+        <v>Cambio de posición</v>
       </c>
       <c r="E74" t="str">
-        <v>1</v>
+        <v>SI</v>
       </c>
       <c r="F74" t="str">
-        <v>Alto</v>
+        <v>Medio</v>
       </c>
       <c r="G74" t="str">
         <v>PAC-1072</v>
@@ -2112,13 +2112,13 @@
         <v>Nocturno</v>
       </c>
       <c r="D75" t="str">
-        <v>Cambio de posición</v>
+        <v>Registro de escala</v>
       </c>
       <c r="E75" t="str">
-        <v>Sí</v>
-      </c>
-      <c r="F75" t="str">
-        <v>Alto</v>
+        <v>No</v>
+      </c>
+      <c r="F75">
+        <v>11</v>
       </c>
       <c r="G75" t="str">
         <v>PAC-1073</v>
@@ -2129,7 +2129,7 @@
         <v>2026-03-15</v>
       </c>
       <c r="B76" t="str">
-        <v>UCI</v>
+        <v>Urgencia</v>
       </c>
       <c r="C76" t="str">
         <v>Diurno</v>
@@ -2138,10 +2138,10 @@
         <v>Registro de escala</v>
       </c>
       <c r="E76" t="str">
-        <v>Sí</v>
+        <v>1</v>
       </c>
       <c r="F76" t="str">
-        <v>Medio</v>
+        <v>Bajo</v>
       </c>
       <c r="G76" t="str">
         <v>PAC-1074</v>
@@ -2152,19 +2152,19 @@
         <v>2026-04-15</v>
       </c>
       <c r="B77" t="str">
-        <v>Medicina</v>
+        <v>UCI</v>
       </c>
       <c r="C77" t="str">
-        <v>Diurno</v>
+        <v>Nocturno</v>
       </c>
       <c r="D77" t="str">
-        <v>Registro de escala</v>
+        <v>Valoración de riesgo</v>
       </c>
       <c r="E77" t="str">
-        <v>Sí</v>
+        <v>Cumple</v>
       </c>
       <c r="F77">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="G77" t="str">
         <v>PAC-1075</v>
@@ -2175,19 +2175,19 @@
         <v>2026-01-15</v>
       </c>
       <c r="B78" t="str">
-        <v>UCI</v>
+        <v>Urgencia</v>
       </c>
       <c r="C78" t="str">
-        <v>Diurno</v>
+        <v>Nocturno</v>
       </c>
       <c r="D78" t="str">
-        <v>Valoración de riesgo</v>
+        <v>Uso de superficie</v>
       </c>
       <c r="E78" t="str">
-        <v>SI</v>
-      </c>
-      <c r="F78" t="str">
-        <v>Medio</v>
+        <v>Cumple</v>
+      </c>
+      <c r="F78">
+        <v>20</v>
       </c>
       <c r="G78" t="str">
         <v>PAC-1076</v>
@@ -2198,19 +2198,19 @@
         <v>2026-02-15</v>
       </c>
       <c r="B79" t="str">
-        <v>Cirugía</v>
+        <v>UCI</v>
       </c>
       <c r="C79" t="str">
-        <v>Nocturno</v>
+        <v>Diurno</v>
       </c>
       <c r="D79" t="str">
-        <v>Cambio de posición</v>
+        <v>Uso de superficie</v>
       </c>
       <c r="E79" t="str">
-        <v>1</v>
-      </c>
-      <c r="F79" t="str">
-        <v>Bajo</v>
+        <v>N/A</v>
+      </c>
+      <c r="F79">
+        <v>11</v>
       </c>
       <c r="G79" t="str">
         <v>PAC-1077</v>
@@ -2221,7 +2221,7 @@
         <v>2026-03-15</v>
       </c>
       <c r="B80" t="str">
-        <v>Urgencia</v>
+        <v>Medicina</v>
       </c>
       <c r="C80" t="str">
         <v>Nocturno</v>
@@ -2244,19 +2244,19 @@
         <v>2026-04-15</v>
       </c>
       <c r="B81" t="str">
-        <v>Medicina</v>
+        <v>Urgencia</v>
       </c>
       <c r="C81" t="str">
-        <v>Diurno</v>
+        <v>Nocturno</v>
       </c>
       <c r="D81" t="str">
         <v>Uso de superficie</v>
       </c>
       <c r="E81" t="str">
-        <v>Sí</v>
-      </c>
-      <c r="F81">
-        <v>11</v>
+        <v>SI</v>
+      </c>
+      <c r="F81" t="str">
+        <v>Bajo</v>
       </c>
       <c r="G81" t="str">
         <v>PAC-1079</v>
@@ -2270,13 +2270,13 @@
         <v>Medicina</v>
       </c>
       <c r="C82" t="str">
-        <v>Diurno</v>
+        <v>Nocturno</v>
       </c>
       <c r="D82" t="str">
         <v>Uso de superficie</v>
       </c>
       <c r="E82" t="str">
-        <v>No cumple</v>
+        <v>N/A</v>
       </c>
       <c r="F82" t="str">
         <v>Bajo</v>
@@ -2290,19 +2290,19 @@
         <v>2026-02-15</v>
       </c>
       <c r="B83" t="str">
-        <v>Urgencia</v>
+        <v>UCI</v>
       </c>
       <c r="C83" t="str">
         <v>Nocturno</v>
       </c>
       <c r="D83" t="str">
-        <v>Valoración de riesgo</v>
+        <v>Registro de escala</v>
       </c>
       <c r="E83" t="str">
-        <v>No</v>
-      </c>
-      <c r="F83" t="str">
-        <v>Medio</v>
+        <v>SI</v>
+      </c>
+      <c r="F83">
+        <v>20</v>
       </c>
       <c r="G83" t="str">
         <v>PAC-1081</v>
@@ -2316,16 +2316,16 @@
         <v>Urgencia</v>
       </c>
       <c r="C84" t="str">
-        <v>Diurno</v>
+        <v>Nocturno</v>
       </c>
       <c r="D84" t="str">
         <v>Registro de escala</v>
       </c>
       <c r="E84" t="str">
-        <v>1</v>
+        <v>Sí</v>
       </c>
       <c r="F84">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="G84" t="str">
         <v>PAC-1082</v>
@@ -2336,16 +2336,16 @@
         <v>2026-04-15</v>
       </c>
       <c r="B85" t="str">
-        <v>Urgencia</v>
+        <v>Medicina</v>
       </c>
       <c r="C85" t="str">
-        <v>Diurno</v>
+        <v>Nocturno</v>
       </c>
       <c r="D85" t="str">
         <v>Valoración de riesgo</v>
       </c>
       <c r="E85" t="str">
-        <v>No cumple</v>
+        <v>Cumple</v>
       </c>
       <c r="F85">
         <v>20</v>
@@ -2362,16 +2362,16 @@
         <v>UCI</v>
       </c>
       <c r="C86" t="str">
-        <v>Diurno</v>
+        <v>Nocturno</v>
       </c>
       <c r="D86" t="str">
-        <v>Registro de escala</v>
+        <v>Uso de superficie</v>
       </c>
       <c r="E86" t="str">
-        <v>SI</v>
-      </c>
-      <c r="F86">
-        <v>11</v>
+        <v>Cumple</v>
+      </c>
+      <c r="F86" t="str">
+        <v>Alto</v>
       </c>
       <c r="G86" t="str">
         <v>PAC-1084</v>
@@ -2382,19 +2382,19 @@
         <v>2026-02-15</v>
       </c>
       <c r="B87" t="str">
-        <v>Urgencia</v>
+        <v>Medicina</v>
       </c>
       <c r="C87" t="str">
         <v>Nocturno</v>
       </c>
       <c r="D87" t="str">
-        <v>Uso de superficie</v>
+        <v>Valoración de riesgo</v>
       </c>
       <c r="E87" t="str">
-        <v>1</v>
-      </c>
-      <c r="F87">
-        <v>11</v>
+        <v>SI</v>
+      </c>
+      <c r="F87" t="str">
+        <v>Medio</v>
       </c>
       <c r="G87" t="str">
         <v>PAC-1085</v>
@@ -2408,13 +2408,13 @@
         <v>Medicina</v>
       </c>
       <c r="C88" t="str">
-        <v>Nocturno</v>
+        <v>Diurno</v>
       </c>
       <c r="D88" t="str">
-        <v>Registro de escala</v>
+        <v>Cambio de posición</v>
       </c>
       <c r="E88" t="str">
-        <v>Cumple</v>
+        <v>Sí</v>
       </c>
       <c r="F88">
         <v>11</v>
@@ -2437,7 +2437,7 @@
         <v>Registro de escala</v>
       </c>
       <c r="E89" t="str">
-        <v>No aplica</v>
+        <v>Cumple</v>
       </c>
       <c r="F89">
         <v>20</v>
@@ -2451,19 +2451,19 @@
         <v>2026-01-15</v>
       </c>
       <c r="B90" t="str">
-        <v>Urgencia</v>
+        <v>UCI</v>
       </c>
       <c r="C90" t="str">
         <v>Nocturno</v>
       </c>
       <c r="D90" t="str">
-        <v>Valoración de riesgo</v>
+        <v>Registro de escala</v>
       </c>
       <c r="E90" t="str">
-        <v>1</v>
-      </c>
-      <c r="F90" t="str">
-        <v>Bajo</v>
+        <v>SI</v>
+      </c>
+      <c r="F90">
+        <v>20</v>
       </c>
       <c r="G90" t="str">
         <v>PAC-1088</v>
@@ -2474,19 +2474,19 @@
         <v>2026-02-15</v>
       </c>
       <c r="B91" t="str">
-        <v>Urgencia</v>
+        <v>Cirugía</v>
       </c>
       <c r="C91" t="str">
-        <v>Diurno</v>
+        <v>Nocturno</v>
       </c>
       <c r="D91" t="str">
         <v>Valoración de riesgo</v>
       </c>
       <c r="E91" t="str">
-        <v>Sí</v>
-      </c>
-      <c r="F91" t="str">
-        <v>Medio</v>
+        <v>No</v>
+      </c>
+      <c r="F91">
+        <v>11</v>
       </c>
       <c r="G91" t="str">
         <v>PAC-1089</v>
@@ -2497,19 +2497,19 @@
         <v>2026-03-15</v>
       </c>
       <c r="B92" t="str">
-        <v>Medicina</v>
+        <v>Urgencia</v>
       </c>
       <c r="C92" t="str">
-        <v>Diurno</v>
+        <v>Nocturno</v>
       </c>
       <c r="D92" t="str">
-        <v>Registro de escala</v>
+        <v>Uso de superficie</v>
       </c>
       <c r="E92" t="str">
-        <v>SI</v>
+        <v>NO</v>
       </c>
       <c r="F92" t="str">
-        <v>Alto</v>
+        <v>Bajo</v>
       </c>
       <c r="G92" t="str">
         <v>PAC-1090</v>
@@ -2520,19 +2520,19 @@
         <v>2026-04-15</v>
       </c>
       <c r="B93" t="str">
-        <v>Cirugía</v>
+        <v>UCI</v>
       </c>
       <c r="C93" t="str">
-        <v>Nocturno</v>
+        <v>Diurno</v>
       </c>
       <c r="D93" t="str">
-        <v>Cambio de posición</v>
+        <v>Registro de escala</v>
       </c>
       <c r="E93" t="str">
-        <v>No aplica</v>
+        <v>Sí</v>
       </c>
       <c r="F93" t="str">
-        <v>Alto</v>
+        <v>Bajo</v>
       </c>
       <c r="G93" t="str">
         <v>PAC-1091</v>
@@ -2543,19 +2543,19 @@
         <v>2026-01-15</v>
       </c>
       <c r="B94" t="str">
-        <v>Cirugía</v>
+        <v>Medicina</v>
       </c>
       <c r="C94" t="str">
-        <v>Diurno</v>
+        <v>Nocturno</v>
       </c>
       <c r="D94" t="str">
-        <v>Cambio de posición</v>
+        <v>Uso de superficie</v>
       </c>
       <c r="E94" t="str">
-        <v>Cumple</v>
-      </c>
-      <c r="F94" t="str">
-        <v>Medio</v>
+        <v>SI</v>
+      </c>
+      <c r="F94">
+        <v>20</v>
       </c>
       <c r="G94" t="str">
         <v>PAC-1092</v>
@@ -2569,16 +2569,16 @@
         <v>Cirugía</v>
       </c>
       <c r="C95" t="str">
-        <v>Nocturno</v>
+        <v>Diurno</v>
       </c>
       <c r="D95" t="str">
         <v>Registro de escala</v>
       </c>
       <c r="E95" t="str">
-        <v>SI</v>
-      </c>
-      <c r="F95" t="str">
-        <v>Bajo</v>
+        <v>1</v>
+      </c>
+      <c r="F95">
+        <v>11</v>
       </c>
       <c r="G95" t="str">
         <v>PAC-1093</v>
@@ -2595,13 +2595,13 @@
         <v>Nocturno</v>
       </c>
       <c r="D96" t="str">
-        <v>Cambio de posición</v>
+        <v>Valoración de riesgo</v>
       </c>
       <c r="E96" t="str">
-        <v>Cumple</v>
-      </c>
-      <c r="F96" t="str">
-        <v>Medio</v>
+        <v>SI</v>
+      </c>
+      <c r="F96">
+        <v>11</v>
       </c>
       <c r="G96" t="str">
         <v>PAC-1094</v>
@@ -2612,19 +2612,19 @@
         <v>2026-04-15</v>
       </c>
       <c r="B97" t="str">
-        <v>Urgencia</v>
+        <v>Cirugía</v>
       </c>
       <c r="C97" t="str">
-        <v>Diurno</v>
+        <v>Nocturno</v>
       </c>
       <c r="D97" t="str">
-        <v>Cambio de posición</v>
+        <v>Valoración de riesgo</v>
       </c>
       <c r="E97" t="str">
-        <v>No cumple</v>
+        <v>Sí</v>
       </c>
       <c r="F97" t="str">
-        <v>Medio</v>
+        <v>Bajo</v>
       </c>
       <c r="G97" t="str">
         <v>PAC-1095</v>
@@ -2635,19 +2635,19 @@
         <v>2026-01-15</v>
       </c>
       <c r="B98" t="str">
-        <v>UCI</v>
+        <v>Medicina</v>
       </c>
       <c r="C98" t="str">
-        <v>Nocturno</v>
+        <v>Diurno</v>
       </c>
       <c r="D98" t="str">
-        <v>Valoración de riesgo</v>
+        <v>Cambio de posición</v>
       </c>
       <c r="E98" t="str">
-        <v>SI</v>
-      </c>
-      <c r="F98">
-        <v>20</v>
+        <v>Cumple</v>
+      </c>
+      <c r="F98" t="str">
+        <v>Alto</v>
       </c>
       <c r="G98" t="str">
         <v>PAC-1096</v>
@@ -2658,19 +2658,19 @@
         <v>2026-02-15</v>
       </c>
       <c r="B99" t="str">
-        <v>Urgencia</v>
+        <v>UCI</v>
       </c>
       <c r="C99" t="str">
-        <v>Diurno</v>
+        <v>Nocturno</v>
       </c>
       <c r="D99" t="str">
-        <v>Registro de escala</v>
+        <v>Uso de superficie</v>
       </c>
       <c r="E99" t="str">
-        <v>N/A</v>
-      </c>
-      <c r="F99">
-        <v>11</v>
+        <v>Cumple</v>
+      </c>
+      <c r="F99" t="str">
+        <v>Medio</v>
       </c>
       <c r="G99" t="str">
         <v>PAC-1097</v>
@@ -2687,10 +2687,10 @@
         <v>Diurno</v>
       </c>
       <c r="D100" t="str">
-        <v>Registro de escala</v>
+        <v>Valoración de riesgo</v>
       </c>
       <c r="E100" t="str">
-        <v>No aplica</v>
+        <v>N/A</v>
       </c>
       <c r="F100" t="str">
         <v>Alto</v>
@@ -2704,19 +2704,19 @@
         <v>2026-04-15</v>
       </c>
       <c r="B101" t="str">
-        <v>Urgencia</v>
+        <v>Cirugía</v>
       </c>
       <c r="C101" t="str">
-        <v>Diurno</v>
+        <v>Nocturno</v>
       </c>
       <c r="D101" t="str">
-        <v>Valoración de riesgo</v>
+        <v>Registro de escala</v>
       </c>
       <c r="E101" t="str">
-        <v>1</v>
-      </c>
-      <c r="F101" t="str">
-        <v>Medio</v>
+        <v>Sí</v>
+      </c>
+      <c r="F101">
+        <v>11</v>
       </c>
       <c r="G101" t="str">
         <v>PAC-1099</v>
@@ -2727,19 +2727,19 @@
         <v>2026-01-15</v>
       </c>
       <c r="B102" t="str">
-        <v>Cirugía</v>
+        <v>UCI</v>
       </c>
       <c r="C102" t="str">
-        <v>Diurno</v>
+        <v>Nocturno</v>
       </c>
       <c r="D102" t="str">
         <v>Registro de escala</v>
       </c>
       <c r="E102" t="str">
-        <v>Cumple</v>
+        <v>No aplica</v>
       </c>
       <c r="F102" t="str">
-        <v>Medio</v>
+        <v>Alto</v>
       </c>
       <c r="G102" t="str">
         <v>PAC-1100</v>
@@ -2750,19 +2750,19 @@
         <v>2026-02-15</v>
       </c>
       <c r="B103" t="str">
-        <v>Urgencia</v>
+        <v>Cirugía</v>
       </c>
       <c r="C103" t="str">
-        <v>Nocturno</v>
+        <v>Diurno</v>
       </c>
       <c r="D103" t="str">
         <v>Uso de superficie</v>
       </c>
       <c r="E103" t="str">
-        <v>No aplica</v>
-      </c>
-      <c r="F103" t="str">
-        <v>Alto</v>
+        <v>0</v>
+      </c>
+      <c r="F103">
+        <v>11</v>
       </c>
       <c r="G103" t="str">
         <v>PAC-1101</v>
@@ -2773,19 +2773,19 @@
         <v>2026-03-15</v>
       </c>
       <c r="B104" t="str">
-        <v>Urgencia</v>
+        <v>Medicina</v>
       </c>
       <c r="C104" t="str">
-        <v>Diurno</v>
+        <v>Nocturno</v>
       </c>
       <c r="D104" t="str">
-        <v>Cambio de posición</v>
+        <v>Valoración de riesgo</v>
       </c>
       <c r="E104" t="str">
-        <v>Cumple</v>
+        <v>Sí</v>
       </c>
       <c r="F104" t="str">
-        <v>Alto</v>
+        <v>Bajo</v>
       </c>
       <c r="G104" t="str">
         <v>PAC-1102</v>
@@ -2796,19 +2796,19 @@
         <v>2026-04-15</v>
       </c>
       <c r="B105" t="str">
-        <v>Urgencia</v>
+        <v>Medicina</v>
       </c>
       <c r="C105" t="str">
         <v>Nocturno</v>
       </c>
       <c r="D105" t="str">
-        <v>Uso de superficie</v>
+        <v>Registro de escala</v>
       </c>
       <c r="E105" t="str">
         <v>Cumple</v>
       </c>
-      <c r="F105" t="str">
-        <v>Bajo</v>
+      <c r="F105">
+        <v>20</v>
       </c>
       <c r="G105" t="str">
         <v>PAC-1103</v>
@@ -2819,19 +2819,19 @@
         <v>2026-01-15</v>
       </c>
       <c r="B106" t="str">
-        <v>Cirugía</v>
+        <v>Urgencia</v>
       </c>
       <c r="C106" t="str">
-        <v>Nocturno</v>
+        <v>Diurno</v>
       </c>
       <c r="D106" t="str">
-        <v>Uso de superficie</v>
+        <v>Registro de escala</v>
       </c>
       <c r="E106" t="str">
-        <v>SI</v>
-      </c>
-      <c r="F106">
-        <v>11</v>
+        <v>No aplica</v>
+      </c>
+      <c r="F106" t="str">
+        <v>Medio</v>
       </c>
       <c r="G106" t="str">
         <v>PAC-1104</v>
@@ -2842,19 +2842,19 @@
         <v>2026-02-15</v>
       </c>
       <c r="B107" t="str">
-        <v>Urgencia</v>
+        <v>UCI</v>
       </c>
       <c r="C107" t="str">
         <v>Nocturno</v>
       </c>
       <c r="D107" t="str">
-        <v>Uso de superficie</v>
+        <v>Valoración de riesgo</v>
       </c>
       <c r="E107" t="str">
-        <v>NO</v>
-      </c>
-      <c r="F107">
-        <v>11</v>
+        <v>Cumple</v>
+      </c>
+      <c r="F107" t="str">
+        <v>Alto</v>
       </c>
       <c r="G107" t="str">
         <v>PAC-1105</v>
@@ -2865,19 +2865,19 @@
         <v>2026-03-15</v>
       </c>
       <c r="B108" t="str">
-        <v>UCI</v>
+        <v>Medicina</v>
       </c>
       <c r="C108" t="str">
         <v>Nocturno</v>
       </c>
       <c r="D108" t="str">
-        <v>Registro de escala</v>
+        <v>Valoración de riesgo</v>
       </c>
       <c r="E108" t="str">
-        <v>0</v>
-      </c>
-      <c r="F108">
-        <v>20</v>
+        <v>SI</v>
+      </c>
+      <c r="F108" t="str">
+        <v>Bajo</v>
       </c>
       <c r="G108" t="str">
         <v>PAC-1106</v>
@@ -2891,16 +2891,16 @@
         <v>Medicina</v>
       </c>
       <c r="C109" t="str">
-        <v>Diurno</v>
+        <v>Nocturno</v>
       </c>
       <c r="D109" t="str">
         <v>Uso de superficie</v>
       </c>
       <c r="E109" t="str">
-        <v>N/A</v>
-      </c>
-      <c r="F109">
-        <v>20</v>
+        <v>Sí</v>
+      </c>
+      <c r="F109" t="str">
+        <v>Alto</v>
       </c>
       <c r="G109" t="str">
         <v>PAC-1107</v>
@@ -2911,19 +2911,19 @@
         <v>2026-01-15</v>
       </c>
       <c r="B110" t="str">
-        <v>UCI</v>
+        <v>Urgencia</v>
       </c>
       <c r="C110" t="str">
         <v>Nocturno</v>
       </c>
       <c r="D110" t="str">
-        <v>Registro de escala</v>
+        <v>Cambio de posición</v>
       </c>
       <c r="E110" t="str">
-        <v>Sí</v>
+        <v>Cumple</v>
       </c>
       <c r="F110">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="G110" t="str">
         <v>PAC-1108</v>
@@ -2934,16 +2934,16 @@
         <v>2026-02-15</v>
       </c>
       <c r="B111" t="str">
-        <v>Cirugía</v>
+        <v>UCI</v>
       </c>
       <c r="C111" t="str">
         <v>Nocturno</v>
       </c>
       <c r="D111" t="str">
-        <v>Uso de superficie</v>
+        <v>Registro de escala</v>
       </c>
       <c r="E111" t="str">
-        <v>No</v>
+        <v>NO</v>
       </c>
       <c r="F111" t="str">
         <v>Alto</v>
@@ -2960,16 +2960,16 @@
         <v>Medicina</v>
       </c>
       <c r="C112" t="str">
-        <v>Nocturno</v>
+        <v>Diurno</v>
       </c>
       <c r="D112" t="str">
         <v>Registro de escala</v>
       </c>
       <c r="E112" t="str">
-        <v>1</v>
-      </c>
-      <c r="F112" t="str">
-        <v>Medio</v>
+        <v>No cumple</v>
+      </c>
+      <c r="F112">
+        <v>11</v>
       </c>
       <c r="G112" t="str">
         <v>PAC-1110</v>
@@ -2980,19 +2980,19 @@
         <v>2026-04-15</v>
       </c>
       <c r="B113" t="str">
-        <v>Urgencia</v>
+        <v>UCI</v>
       </c>
       <c r="C113" t="str">
-        <v>Diurno</v>
+        <v>Nocturno</v>
       </c>
       <c r="D113" t="str">
-        <v>Registro de escala</v>
+        <v>Uso de superficie</v>
       </c>
       <c r="E113" t="str">
-        <v>NO</v>
+        <v>SI</v>
       </c>
       <c r="F113">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="G113" t="str">
         <v>PAC-1111</v>
@@ -3003,19 +3003,19 @@
         <v>2026-01-15</v>
       </c>
       <c r="B114" t="str">
-        <v>UCI</v>
+        <v>Cirugía</v>
       </c>
       <c r="C114" t="str">
         <v>Diurno</v>
       </c>
       <c r="D114" t="str">
-        <v>Valoración de riesgo</v>
+        <v>Cambio de posición</v>
       </c>
       <c r="E114" t="str">
-        <v>No aplica</v>
+        <v>Cumple</v>
       </c>
       <c r="F114">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="G114" t="str">
         <v>PAC-1112</v>
@@ -3026,19 +3026,19 @@
         <v>2026-02-15</v>
       </c>
       <c r="B115" t="str">
-        <v>Urgencia</v>
+        <v>UCI</v>
       </c>
       <c r="C115" t="str">
         <v>Nocturno</v>
       </c>
       <c r="D115" t="str">
-        <v>Uso de superficie</v>
+        <v>Registro de escala</v>
       </c>
       <c r="E115" t="str">
-        <v>Cumple</v>
-      </c>
-      <c r="F115">
-        <v>11</v>
+        <v>No</v>
+      </c>
+      <c r="F115" t="str">
+        <v>Alto</v>
       </c>
       <c r="G115" t="str">
         <v>PAC-1113</v>
@@ -3049,19 +3049,19 @@
         <v>2026-03-15</v>
       </c>
       <c r="B116" t="str">
-        <v>Medicina</v>
+        <v>Cirugía</v>
       </c>
       <c r="C116" t="str">
         <v>Nocturno</v>
       </c>
       <c r="D116" t="str">
-        <v>Valoración de riesgo</v>
+        <v>Registro de escala</v>
       </c>
       <c r="E116" t="str">
-        <v>NO</v>
-      </c>
-      <c r="F116" t="str">
-        <v>Medio</v>
+        <v>Cumple</v>
+      </c>
+      <c r="F116">
+        <v>20</v>
       </c>
       <c r="G116" t="str">
         <v>PAC-1114</v>
@@ -3072,19 +3072,19 @@
         <v>2026-04-15</v>
       </c>
       <c r="B117" t="str">
-        <v>Urgencia</v>
+        <v>Medicina</v>
       </c>
       <c r="C117" t="str">
         <v>Nocturno</v>
       </c>
       <c r="D117" t="str">
-        <v>Registro de escala</v>
+        <v>Cambio de posición</v>
       </c>
       <c r="E117" t="str">
-        <v>1</v>
-      </c>
-      <c r="F117">
-        <v>20</v>
+        <v>SI</v>
+      </c>
+      <c r="F117" t="str">
+        <v>Alto</v>
       </c>
       <c r="G117" t="str">
         <v>PAC-1115</v>
@@ -3101,13 +3101,13 @@
         <v>Nocturno</v>
       </c>
       <c r="D118" t="str">
-        <v>Registro de escala</v>
+        <v>Valoración de riesgo</v>
       </c>
       <c r="E118" t="str">
-        <v>SI</v>
-      </c>
-      <c r="F118" t="str">
-        <v>Bajo</v>
+        <v>1</v>
+      </c>
+      <c r="F118">
+        <v>11</v>
       </c>
       <c r="G118" t="str">
         <v>PAC-1116</v>
@@ -3118,19 +3118,19 @@
         <v>2026-02-15</v>
       </c>
       <c r="B119" t="str">
-        <v>Medicina</v>
+        <v>Urgencia</v>
       </c>
       <c r="C119" t="str">
-        <v>Diurno</v>
+        <v>Nocturno</v>
       </c>
       <c r="D119" t="str">
         <v>Registro de escala</v>
       </c>
       <c r="E119" t="str">
-        <v>Cumple</v>
+        <v>1</v>
       </c>
       <c r="F119" t="str">
-        <v>Medio</v>
+        <v>Alto</v>
       </c>
       <c r="G119" t="str">
         <v>PAC-1117</v>
@@ -3141,19 +3141,19 @@
         <v>2026-03-15</v>
       </c>
       <c r="B120" t="str">
-        <v>Urgencia</v>
+        <v>Cirugía</v>
       </c>
       <c r="C120" t="str">
-        <v>Nocturno</v>
+        <v>Diurno</v>
       </c>
       <c r="D120" t="str">
         <v>Uso de superficie</v>
       </c>
       <c r="E120" t="str">
-        <v>No cumple</v>
+        <v>SI</v>
       </c>
       <c r="F120">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="G120" t="str">
         <v>PAC-1118</v>
@@ -3167,16 +3167,16 @@
         <v>Cirugía</v>
       </c>
       <c r="C121" t="str">
-        <v>Nocturno</v>
+        <v>Diurno</v>
       </c>
       <c r="D121" t="str">
-        <v>Valoración de riesgo</v>
+        <v>Uso de superficie</v>
       </c>
       <c r="E121" t="str">
-        <v>Cumple</v>
-      </c>
-      <c r="F121" t="str">
-        <v>Medio</v>
+        <v>1</v>
+      </c>
+      <c r="F121">
+        <v>20</v>
       </c>
       <c r="G121" t="str">
         <v>PAC-1119</v>
@@ -3187,19 +3187,19 @@
         <v>2026-01-15</v>
       </c>
       <c r="B122" t="str">
-        <v>UCI</v>
+        <v>Medicina</v>
       </c>
       <c r="C122" t="str">
         <v>Diurno</v>
       </c>
       <c r="D122" t="str">
-        <v>Cambio de posición</v>
+        <v>Valoración de riesgo</v>
       </c>
       <c r="E122" t="str">
-        <v>Sí</v>
-      </c>
-      <c r="F122" t="str">
-        <v>Alto</v>
+        <v>Cumple</v>
+      </c>
+      <c r="F122">
+        <v>11</v>
       </c>
       <c r="G122" t="str">
         <v>PAC-1120</v>
@@ -3210,19 +3210,19 @@
         <v>2026-02-15</v>
       </c>
       <c r="B123" t="str">
-        <v>UCI</v>
+        <v>Urgencia</v>
       </c>
       <c r="C123" t="str">
-        <v>Diurno</v>
+        <v>Nocturno</v>
       </c>
       <c r="D123" t="str">
-        <v>Uso de superficie</v>
+        <v>Cambio de posición</v>
       </c>
       <c r="E123" t="str">
-        <v>No</v>
+        <v>No aplica</v>
       </c>
       <c r="F123" t="str">
-        <v>Alto</v>
+        <v>Medio</v>
       </c>
       <c r="G123" t="str">
         <v>PAC-1121</v>
@@ -3233,19 +3233,19 @@
         <v>2026-03-15</v>
       </c>
       <c r="B124" t="str">
-        <v>UCI</v>
+        <v>Urgencia</v>
       </c>
       <c r="C124" t="str">
         <v>Diurno</v>
       </c>
       <c r="D124" t="str">
-        <v>Cambio de posición</v>
+        <v>Valoración de riesgo</v>
       </c>
       <c r="E124" t="str">
-        <v>N/A</v>
+        <v>No cumple</v>
       </c>
       <c r="F124" t="str">
-        <v>Medio</v>
+        <v>Alto</v>
       </c>
       <c r="G124" t="str">
         <v>PAC-1122</v>
@@ -3256,7 +3256,7 @@
         <v>2026-04-15</v>
       </c>
       <c r="B125" t="str">
-        <v>Cirugía</v>
+        <v>Medicina</v>
       </c>
       <c r="C125" t="str">
         <v>Diurno</v>
@@ -3265,10 +3265,10 @@
         <v>Registro de escala</v>
       </c>
       <c r="E125" t="str">
-        <v>SI</v>
-      </c>
-      <c r="F125" t="str">
-        <v>Medio</v>
+        <v>No aplica</v>
+      </c>
+      <c r="F125">
+        <v>20</v>
       </c>
       <c r="G125" t="str">
         <v>PAC-1123</v>
@@ -3285,13 +3285,13 @@
         <v>Diurno</v>
       </c>
       <c r="D126" t="str">
-        <v>Registro de escala</v>
+        <v>Uso de superficie</v>
       </c>
       <c r="E126" t="str">
-        <v>N/A</v>
+        <v>No</v>
       </c>
       <c r="F126" t="str">
-        <v>Alto</v>
+        <v>Bajo</v>
       </c>
       <c r="G126" t="str">
         <v>PAC-1124</v>
@@ -3302,19 +3302,19 @@
         <v>2026-02-15</v>
       </c>
       <c r="B127" t="str">
-        <v>Medicina</v>
+        <v>UCI</v>
       </c>
       <c r="C127" t="str">
-        <v>Diurno</v>
+        <v>Nocturno</v>
       </c>
       <c r="D127" t="str">
         <v>Cambio de posición</v>
       </c>
       <c r="E127" t="str">
-        <v>SI</v>
+        <v>No aplica</v>
       </c>
       <c r="F127" t="str">
-        <v>Alto</v>
+        <v>Bajo</v>
       </c>
       <c r="G127" t="str">
         <v>PAC-1125</v>
@@ -3325,19 +3325,19 @@
         <v>2026-03-15</v>
       </c>
       <c r="B128" t="str">
-        <v>Medicina</v>
+        <v>Urgencia</v>
       </c>
       <c r="C128" t="str">
         <v>Nocturno</v>
       </c>
       <c r="D128" t="str">
-        <v>Cambio de posición</v>
+        <v>Uso de superficie</v>
       </c>
       <c r="E128" t="str">
-        <v>Cumple</v>
+        <v>1</v>
       </c>
       <c r="F128" t="str">
-        <v>Alto</v>
+        <v>Medio</v>
       </c>
       <c r="G128" t="str">
         <v>PAC-1126</v>
@@ -3348,19 +3348,19 @@
         <v>2026-04-15</v>
       </c>
       <c r="B129" t="str">
-        <v>Cirugía</v>
+        <v>Urgencia</v>
       </c>
       <c r="C129" t="str">
-        <v>Diurno</v>
+        <v>Nocturno</v>
       </c>
       <c r="D129" t="str">
         <v>Registro de escala</v>
       </c>
       <c r="E129" t="str">
-        <v>SI</v>
-      </c>
-      <c r="F129" t="str">
-        <v>Medio</v>
+        <v>Sí</v>
+      </c>
+      <c r="F129">
+        <v>20</v>
       </c>
       <c r="G129" t="str">
         <v>PAC-1127</v>
@@ -3371,19 +3371,19 @@
         <v>2026-01-15</v>
       </c>
       <c r="B130" t="str">
-        <v>Cirugía</v>
+        <v>Urgencia</v>
       </c>
       <c r="C130" t="str">
-        <v>Diurno</v>
+        <v>Nocturno</v>
       </c>
       <c r="D130" t="str">
-        <v>Valoración de riesgo</v>
+        <v>Cambio de posición</v>
       </c>
       <c r="E130" t="str">
-        <v>Cumple</v>
-      </c>
-      <c r="F130" t="str">
-        <v>Alto</v>
+        <v>Sí</v>
+      </c>
+      <c r="F130">
+        <v>20</v>
       </c>
       <c r="G130" t="str">
         <v>PAC-1128</v>
@@ -3394,19 +3394,19 @@
         <v>2026-02-15</v>
       </c>
       <c r="B131" t="str">
-        <v>Urgencia</v>
+        <v>UCI</v>
       </c>
       <c r="C131" t="str">
-        <v>Nocturno</v>
+        <v>Diurno</v>
       </c>
       <c r="D131" t="str">
-        <v>Valoración de riesgo</v>
+        <v>Registro de escala</v>
       </c>
       <c r="E131" t="str">
-        <v>SI</v>
-      </c>
-      <c r="F131">
-        <v>20</v>
+        <v>0</v>
+      </c>
+      <c r="F131" t="str">
+        <v>Bajo</v>
       </c>
       <c r="G131" t="str">
         <v>PAC-1129</v>
@@ -3417,19 +3417,19 @@
         <v>2026-03-15</v>
       </c>
       <c r="B132" t="str">
-        <v>Urgencia</v>
+        <v>Cirugía</v>
       </c>
       <c r="C132" t="str">
-        <v>Nocturno</v>
+        <v>Diurno</v>
       </c>
       <c r="D132" t="str">
-        <v>Cambio de posición</v>
+        <v>Valoración de riesgo</v>
       </c>
       <c r="E132" t="str">
         <v>Cumple</v>
       </c>
       <c r="F132" t="str">
-        <v>Alto</v>
+        <v>Bajo</v>
       </c>
       <c r="G132" t="str">
         <v>PAC-1130</v>
@@ -3440,19 +3440,19 @@
         <v>2026-04-15</v>
       </c>
       <c r="B133" t="str">
-        <v>Medicina</v>
+        <v>Cirugía</v>
       </c>
       <c r="C133" t="str">
-        <v>Nocturno</v>
+        <v>Diurno</v>
       </c>
       <c r="D133" t="str">
-        <v>Uso de superficie</v>
+        <v>Registro de escala</v>
       </c>
       <c r="E133" t="str">
-        <v>Cumple</v>
-      </c>
-      <c r="F133">
-        <v>20</v>
+        <v>No</v>
+      </c>
+      <c r="F133" t="str">
+        <v>Alto</v>
       </c>
       <c r="G133" t="str">
         <v>PAC-1131</v>
@@ -3469,10 +3469,10 @@
         <v>Nocturno</v>
       </c>
       <c r="D134" t="str">
-        <v>Uso de superficie</v>
+        <v>Cambio de posición</v>
       </c>
       <c r="E134" t="str">
-        <v>0</v>
+        <v>Sí</v>
       </c>
       <c r="F134">
         <v>11</v>
@@ -3489,10 +3489,10 @@
         <v>Urgencia</v>
       </c>
       <c r="C135" t="str">
-        <v>Nocturno</v>
+        <v>Diurno</v>
       </c>
       <c r="D135" t="str">
-        <v>Valoración de riesgo</v>
+        <v>Uso de superficie</v>
       </c>
       <c r="E135" t="str">
         <v>Sí</v>
@@ -3509,7 +3509,7 @@
         <v>2026-03-15</v>
       </c>
       <c r="B136" t="str">
-        <v>Cirugía</v>
+        <v>Medicina</v>
       </c>
       <c r="C136" t="str">
         <v>Diurno</v>
@@ -3520,8 +3520,8 @@
       <c r="E136" t="str">
         <v>Cumple</v>
       </c>
-      <c r="F136">
-        <v>20</v>
+      <c r="F136" t="str">
+        <v>Medio</v>
       </c>
       <c r="G136" t="str">
         <v>PAC-1134</v>
@@ -3532,19 +3532,19 @@
         <v>2026-04-15</v>
       </c>
       <c r="B137" t="str">
-        <v>Urgencia</v>
+        <v>UCI</v>
       </c>
       <c r="C137" t="str">
-        <v>Diurno</v>
+        <v>Nocturno</v>
       </c>
       <c r="D137" t="str">
         <v>Uso de superficie</v>
       </c>
       <c r="E137" t="str">
-        <v>Cumple</v>
-      </c>
-      <c r="F137" t="str">
-        <v>Bajo</v>
+        <v>Sí</v>
+      </c>
+      <c r="F137">
+        <v>20</v>
       </c>
       <c r="G137" t="str">
         <v>PAC-1135</v>
@@ -3561,13 +3561,13 @@
         <v>Nocturno</v>
       </c>
       <c r="D138" t="str">
-        <v>Registro de escala</v>
+        <v>Valoración de riesgo</v>
       </c>
       <c r="E138" t="str">
-        <v>SI</v>
+        <v>No</v>
       </c>
       <c r="F138" t="str">
-        <v>Medio</v>
+        <v>Bajo</v>
       </c>
       <c r="G138" t="str">
         <v>PAC-1136</v>
@@ -3578,16 +3578,16 @@
         <v>2026-02-15</v>
       </c>
       <c r="B139" t="str">
-        <v>Urgencia</v>
+        <v>Cirugía</v>
       </c>
       <c r="C139" t="str">
         <v>Nocturno</v>
       </c>
       <c r="D139" t="str">
-        <v>Cambio de posición</v>
+        <v>Uso de superficie</v>
       </c>
       <c r="E139" t="str">
-        <v>1</v>
+        <v>NO</v>
       </c>
       <c r="F139" t="str">
         <v>Alto</v>
@@ -3604,16 +3604,16 @@
         <v>Urgencia</v>
       </c>
       <c r="C140" t="str">
-        <v>Nocturno</v>
+        <v>Diurno</v>
       </c>
       <c r="D140" t="str">
-        <v>Valoración de riesgo</v>
+        <v>Cambio de posición</v>
       </c>
       <c r="E140" t="str">
-        <v>NO</v>
-      </c>
-      <c r="F140" t="str">
-        <v>Medio</v>
+        <v>Sí</v>
+      </c>
+      <c r="F140">
+        <v>11</v>
       </c>
       <c r="G140" t="str">
         <v>PAC-1138</v>
@@ -3624,19 +3624,19 @@
         <v>2026-04-15</v>
       </c>
       <c r="B141" t="str">
-        <v>Medicina</v>
+        <v>Urgencia</v>
       </c>
       <c r="C141" t="str">
         <v>Nocturno</v>
       </c>
       <c r="D141" t="str">
-        <v>Uso de superficie</v>
+        <v>Cambio de posición</v>
       </c>
       <c r="E141" t="str">
-        <v>1</v>
+        <v>No cumple</v>
       </c>
       <c r="F141">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="G141" t="str">
         <v>PAC-1139</v>
@@ -3647,19 +3647,19 @@
         <v>2026-01-15</v>
       </c>
       <c r="B142" t="str">
-        <v>Medicina</v>
+        <v>Urgencia</v>
       </c>
       <c r="C142" t="str">
         <v>Diurno</v>
       </c>
       <c r="D142" t="str">
-        <v>Uso de superficie</v>
+        <v>Registro de escala</v>
       </c>
       <c r="E142" t="str">
         <v>Sí</v>
       </c>
       <c r="F142">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="G142" t="str">
         <v>PAC-1140</v>
@@ -3673,16 +3673,16 @@
         <v>Cirugía</v>
       </c>
       <c r="C143" t="str">
-        <v>Nocturno</v>
+        <v>Diurno</v>
       </c>
       <c r="D143" t="str">
-        <v>Uso de superficie</v>
+        <v>Registro de escala</v>
       </c>
       <c r="E143" t="str">
-        <v>NO</v>
+        <v>Sí</v>
       </c>
       <c r="F143" t="str">
-        <v>Bajo</v>
+        <v>Medio</v>
       </c>
       <c r="G143" t="str">
         <v>PAC-1141</v>
@@ -3693,19 +3693,19 @@
         <v>2026-03-15</v>
       </c>
       <c r="B144" t="str">
-        <v>Medicina</v>
+        <v>Cirugía</v>
       </c>
       <c r="C144" t="str">
-        <v>Nocturno</v>
+        <v>Diurno</v>
       </c>
       <c r="D144" t="str">
-        <v>Uso de superficie</v>
+        <v>Cambio de posición</v>
       </c>
       <c r="E144" t="str">
-        <v>Sí</v>
-      </c>
-      <c r="F144" t="str">
-        <v>Alto</v>
+        <v>1</v>
+      </c>
+      <c r="F144">
+        <v>11</v>
       </c>
       <c r="G144" t="str">
         <v>PAC-1142</v>
@@ -3722,13 +3722,13 @@
         <v>Nocturno</v>
       </c>
       <c r="D145" t="str">
-        <v>Cambio de posición</v>
+        <v>Valoración de riesgo</v>
       </c>
       <c r="E145" t="str">
         <v>1</v>
       </c>
-      <c r="F145" t="str">
-        <v>Medio</v>
+      <c r="F145">
+        <v>11</v>
       </c>
       <c r="G145" t="str">
         <v>PAC-1143</v>
@@ -3739,16 +3739,16 @@
         <v>2026-01-15</v>
       </c>
       <c r="B146" t="str">
-        <v>Medicina</v>
+        <v>UCI</v>
       </c>
       <c r="C146" t="str">
         <v>Nocturno</v>
       </c>
       <c r="D146" t="str">
-        <v>Valoración de riesgo</v>
+        <v>Registro de escala</v>
       </c>
       <c r="E146" t="str">
-        <v>Sí</v>
+        <v>SI</v>
       </c>
       <c r="F146">
         <v>20</v>
@@ -3762,16 +3762,16 @@
         <v>2026-02-15</v>
       </c>
       <c r="B147" t="str">
-        <v>Urgencia</v>
+        <v>Cirugía</v>
       </c>
       <c r="C147" t="str">
-        <v>Nocturno</v>
+        <v>Diurno</v>
       </c>
       <c r="D147" t="str">
-        <v>Registro de escala</v>
+        <v>Valoración de riesgo</v>
       </c>
       <c r="E147" t="str">
-        <v>N/A</v>
+        <v>0</v>
       </c>
       <c r="F147">
         <v>20</v>
@@ -3785,19 +3785,19 @@
         <v>2026-03-15</v>
       </c>
       <c r="B148" t="str">
-        <v>UCI</v>
+        <v>Medicina</v>
       </c>
       <c r="C148" t="str">
         <v>Diurno</v>
       </c>
       <c r="D148" t="str">
-        <v>Cambio de posición</v>
+        <v>Valoración de riesgo</v>
       </c>
       <c r="E148" t="str">
         <v>Cumple</v>
       </c>
       <c r="F148" t="str">
-        <v>Medio</v>
+        <v>Alto</v>
       </c>
       <c r="G148" t="str">
         <v>PAC-1146</v>
@@ -3808,10 +3808,10 @@
         <v>2026-04-15</v>
       </c>
       <c r="B149" t="str">
-        <v>Urgencia</v>
+        <v>Medicina</v>
       </c>
       <c r="C149" t="str">
-        <v>Diurno</v>
+        <v>Nocturno</v>
       </c>
       <c r="D149" t="str">
         <v>Valoración de riesgo</v>
@@ -3820,7 +3820,7 @@
         <v>No</v>
       </c>
       <c r="F149" t="str">
-        <v>Bajo</v>
+        <v>Alto</v>
       </c>
       <c r="G149" t="str">
         <v>PAC-1147</v>
@@ -3831,19 +3831,19 @@
         <v>2026-01-15</v>
       </c>
       <c r="B150" t="str">
-        <v>Cirugía</v>
+        <v>UCI</v>
       </c>
       <c r="C150" t="str">
         <v>Nocturno</v>
       </c>
       <c r="D150" t="str">
-        <v>Registro de escala</v>
+        <v>Valoración de riesgo</v>
       </c>
       <c r="E150" t="str">
         <v>Sí</v>
       </c>
-      <c r="F150" t="str">
-        <v>Alto</v>
+      <c r="F150">
+        <v>20</v>
       </c>
       <c r="G150" t="str">
         <v>PAC-1148</v>
@@ -3854,19 +3854,19 @@
         <v>2026-02-15</v>
       </c>
       <c r="B151" t="str">
-        <v>Medicina</v>
+        <v>UCI</v>
       </c>
       <c r="C151" t="str">
         <v>Diurno</v>
       </c>
       <c r="D151" t="str">
-        <v>Uso de superficie</v>
+        <v>Registro de escala</v>
       </c>
       <c r="E151" t="str">
-        <v>Cumple</v>
+        <v>1</v>
       </c>
       <c r="F151">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="G151" t="str">
         <v>PAC-1149</v>
@@ -3877,16 +3877,16 @@
         <v>2026-03-15</v>
       </c>
       <c r="B152" t="str">
-        <v>Urgencia</v>
+        <v>UCI</v>
       </c>
       <c r="C152" t="str">
         <v>Diurno</v>
       </c>
       <c r="D152" t="str">
-        <v>Valoración de riesgo</v>
+        <v>Cambio de posición</v>
       </c>
       <c r="E152" t="str">
-        <v>Sí</v>
+        <v>Cumple</v>
       </c>
       <c r="F152">
         <v>20</v>
@@ -3903,16 +3903,16 @@
         <v>UCI</v>
       </c>
       <c r="C153" t="str">
-        <v>Nocturno</v>
+        <v>Diurno</v>
       </c>
       <c r="D153" t="str">
         <v>Valoración de riesgo</v>
       </c>
       <c r="E153" t="str">
-        <v>Sí</v>
+        <v>SI</v>
       </c>
       <c r="F153">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="G153" t="str">
         <v>PAC-1151</v>
@@ -3923,19 +3923,19 @@
         <v>2026-01-15</v>
       </c>
       <c r="B154" t="str">
-        <v>Cirugía</v>
+        <v>UCI</v>
       </c>
       <c r="C154" t="str">
         <v>Diurno</v>
       </c>
       <c r="D154" t="str">
-        <v>Cambio de posición</v>
+        <v>Uso de superficie</v>
       </c>
       <c r="E154" t="str">
-        <v>1</v>
+        <v>No aplica</v>
       </c>
       <c r="F154">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="G154" t="str">
         <v>PAC-1152</v>
@@ -3952,10 +3952,10 @@
         <v>Nocturno</v>
       </c>
       <c r="D155" t="str">
-        <v>Valoración de riesgo</v>
+        <v>Registro de escala</v>
       </c>
       <c r="E155" t="str">
-        <v>No aplica</v>
+        <v>Sí</v>
       </c>
       <c r="F155" t="str">
         <v>Medio</v>
@@ -3975,10 +3975,10 @@
         <v>Diurno</v>
       </c>
       <c r="D156" t="str">
-        <v>Registro de escala</v>
+        <v>Uso de superficie</v>
       </c>
       <c r="E156" t="str">
-        <v>Cumple</v>
+        <v>SI</v>
       </c>
       <c r="F156">
         <v>20</v>
@@ -3992,16 +3992,16 @@
         <v>2026-04-15</v>
       </c>
       <c r="B157" t="str">
-        <v>UCI</v>
+        <v>Urgencia</v>
       </c>
       <c r="C157" t="str">
-        <v>Nocturno</v>
+        <v>Diurno</v>
       </c>
       <c r="D157" t="str">
         <v>Cambio de posición</v>
       </c>
       <c r="E157" t="str">
-        <v>No</v>
+        <v>SI</v>
       </c>
       <c r="F157">
         <v>11</v>
@@ -4015,19 +4015,19 @@
         <v>2026-01-15</v>
       </c>
       <c r="B158" t="str">
-        <v>UCI</v>
+        <v>Cirugía</v>
       </c>
       <c r="C158" t="str">
         <v>Nocturno</v>
       </c>
       <c r="D158" t="str">
-        <v>Uso de superficie</v>
+        <v>Registro de escala</v>
       </c>
       <c r="E158" t="str">
-        <v>1</v>
+        <v>Cumple</v>
       </c>
       <c r="F158" t="str">
-        <v>Medio</v>
+        <v>Bajo</v>
       </c>
       <c r="G158" t="str">
         <v>PAC-1156</v>
@@ -4038,19 +4038,19 @@
         <v>2026-02-15</v>
       </c>
       <c r="B159" t="str">
-        <v>Urgencia</v>
+        <v>Medicina</v>
       </c>
       <c r="C159" t="str">
         <v>Diurno</v>
       </c>
       <c r="D159" t="str">
-        <v>Valoración de riesgo</v>
+        <v>Registro de escala</v>
       </c>
       <c r="E159" t="str">
-        <v>SI</v>
-      </c>
-      <c r="F159" t="str">
-        <v>Alto</v>
+        <v>Sí</v>
+      </c>
+      <c r="F159">
+        <v>20</v>
       </c>
       <c r="G159" t="str">
         <v>PAC-1157</v>
@@ -4061,7 +4061,7 @@
         <v>2026-03-15</v>
       </c>
       <c r="B160" t="str">
-        <v>Cirugía</v>
+        <v>UCI</v>
       </c>
       <c r="C160" t="str">
         <v>Nocturno</v>
@@ -4073,7 +4073,7 @@
         <v>SI</v>
       </c>
       <c r="F160" t="str">
-        <v>Alto</v>
+        <v>Bajo</v>
       </c>
       <c r="G160" t="str">
         <v>PAC-1158</v>
@@ -4087,16 +4087,16 @@
         <v>Urgencia</v>
       </c>
       <c r="C161" t="str">
-        <v>Diurno</v>
+        <v>Nocturno</v>
       </c>
       <c r="D161" t="str">
         <v>Valoración de riesgo</v>
       </c>
       <c r="E161" t="str">
-        <v>1</v>
+        <v>Cumple</v>
       </c>
       <c r="F161" t="str">
-        <v>Bajo</v>
+        <v>Alto</v>
       </c>
       <c r="G161" t="str">
         <v>PAC-1159</v>
